--- a/declara.xlsx
+++ b/declara.xlsx
@@ -5810,13 +5810,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="MS Sans Serif"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5836,16 +5840,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>

--- a/declara.xlsx
+++ b/declara.xlsx
@@ -410,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -469,6 +469,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -768,6 +772,7 @@
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" ht="39" thickBot="1">
@@ -831,7 +836,7 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="20" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="2" t="s">

--- a/declara.xlsx
+++ b/declara.xlsx
@@ -3651,7 +3651,9 @@
       <c r="AT2" s="32">
         <v>57206994</v>
       </c>
-      <c r="AU2" s="36"/>
+      <c r="AU2" s="36">
+        <v>280</v>
+      </c>
       <c r="AV2" s="5"/>
       <c r="AW2" s="5"/>
       <c r="AX2" s="5"/>

--- a/declara.xlsx
+++ b/declara.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="883">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -1183,9 +1183,6 @@
     <t>Cajera</t>
   </si>
   <si>
-    <t>Georgina Autino</t>
-  </si>
-  <si>
     <t>Autino Tobias</t>
   </si>
   <si>
@@ -2257,9 +2254,6 @@
     <t>ivancabrera384@gmail.com</t>
   </si>
   <si>
-    <t>Canrera Sergio ivan</t>
-  </si>
-  <si>
     <t>Benito bianco 11</t>
   </si>
   <si>
@@ -2666,6 +2660,9 @@
   </si>
   <si>
     <t>Abogacia</t>
+  </si>
+  <si>
+    <t>Cabrera Sergio ivan</t>
   </si>
 </sst>
 </file>
@@ -6485,17 +6482,11 @@
       <c r="S27" s="23">
         <v>36</v>
       </c>
-      <c r="T27" s="22" t="s">
+      <c r="T27" s="22"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="22" t="s">
         <v>389</v>
-      </c>
-      <c r="U27" s="25">
-        <v>30557</v>
-      </c>
-      <c r="V27" s="23">
-        <v>30399454</v>
-      </c>
-      <c r="W27" s="22" t="s">
-        <v>390</v>
       </c>
       <c r="X27" s="25">
         <v>38247</v>
@@ -6530,20 +6521,12 @@
         <v>389</v>
       </c>
       <c r="AP27" s="23">
-        <v>30399454</v>
-      </c>
-      <c r="AQ27" s="22" t="s">
-        <v>389</v>
-      </c>
-      <c r="AR27" s="23">
-        <v>30399454</v>
-      </c>
-      <c r="AS27" s="22" t="s">
-        <v>389</v>
-      </c>
-      <c r="AT27" s="23">
-        <v>30399454</v>
-      </c>
+        <v>46220849</v>
+      </c>
+      <c r="AQ27" s="22"/>
+      <c r="AR27" s="23"/>
+      <c r="AS27" s="22"/>
+      <c r="AT27" s="23"/>
       <c r="AU27" s="27">
         <v>149</v>
       </c>
@@ -6580,16 +6563,16 @@
         <v>32</v>
       </c>
       <c r="K28" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="L28" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="L28" s="7" t="s">
+      <c r="M28" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="M28" s="7" t="s">
+      <c r="N28" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>394</v>
       </c>
       <c r="O28" s="10">
         <v>38460</v>
@@ -6610,25 +6593,25 @@
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
       <c r="W28" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="X28" s="10">
         <v>33108</v>
       </c>
       <c r="Y28" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="Z28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB28" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="Z28" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA28" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB28" s="7" t="s">
+      <c r="AC28" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="AC28" s="7" t="s">
-        <v>398</v>
       </c>
       <c r="AD28" s="10">
         <v>33702</v>
@@ -6643,10 +6626,10 @@
         <v>40</v>
       </c>
       <c r="AH28" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="AI28" s="7" t="s">
         <v>399</v>
-      </c>
-      <c r="AI28" s="7" t="s">
-        <v>400</v>
       </c>
       <c r="AJ28" s="10">
         <v>34098</v>
@@ -6662,19 +6645,19 @@
       </c>
       <c r="AN28" s="11"/>
       <c r="AO28" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AP28" s="8">
         <v>44810214</v>
       </c>
       <c r="AQ28" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AR28" s="8">
         <v>44810215</v>
       </c>
       <c r="AS28" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AT28" s="8">
         <v>39662207</v>
@@ -6715,16 +6698,16 @@
         <v>59</v>
       </c>
       <c r="K29" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="L29" s="22" t="s">
         <v>404</v>
       </c>
-      <c r="L29" s="22" t="s">
+      <c r="M29" s="22" t="s">
         <v>405</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="N29" s="22" t="s">
         <v>406</v>
-      </c>
-      <c r="N29" s="22" t="s">
-        <v>407</v>
       </c>
       <c r="O29" s="25">
         <v>38353</v>
@@ -6742,7 +6725,7 @@
         <v>39</v>
       </c>
       <c r="T29" s="22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="U29" s="25">
         <v>16053</v>
@@ -6751,7 +6734,7 @@
         <v>6134509</v>
       </c>
       <c r="W29" s="22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="X29" s="25">
         <v>39016</v>
@@ -6766,7 +6749,7 @@
         <v>40</v>
       </c>
       <c r="AB29" s="22" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AC29" s="26"/>
       <c r="AD29" s="26"/>
@@ -6781,13 +6764,13 @@
       <c r="AM29" s="26"/>
       <c r="AN29" s="26"/>
       <c r="AO29" s="22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AP29" s="23">
         <v>47329429</v>
       </c>
       <c r="AQ29" s="22" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AR29" s="23">
         <v>38458565</v>
@@ -6830,25 +6813,25 @@
         <v>32</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>34</v>
       </c>
       <c r="M30" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="N30" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>415</v>
       </c>
       <c r="O30" s="10">
         <v>41091</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R30" s="8">
         <v>38</v>
@@ -6860,7 +6843,7 @@
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
       <c r="W30" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="X30" s="10">
         <v>41723</v>
@@ -6874,7 +6857,7 @@
       <c r="AA30" s="11"/>
       <c r="AB30" s="11"/>
       <c r="AC30" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AD30" s="10">
         <v>43087</v>
@@ -6894,13 +6877,13 @@
       <c r="AM30" s="11"/>
       <c r="AN30" s="11"/>
       <c r="AO30" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AP30" s="8">
         <v>56624106</v>
       </c>
       <c r="AQ30" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AR30" s="8">
         <v>56624106</v>
@@ -6949,10 +6932,10 @@
         <v>266</v>
       </c>
       <c r="M31" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="N31" s="22" t="s">
         <v>420</v>
-      </c>
-      <c r="N31" s="22" t="s">
-        <v>421</v>
       </c>
       <c r="O31" s="25">
         <v>44896</v>
@@ -6970,7 +6953,7 @@
         <v>35</v>
       </c>
       <c r="T31" s="22" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="U31" s="25">
         <v>35942</v>
@@ -6979,7 +6962,7 @@
         <v>40959364</v>
       </c>
       <c r="W31" s="22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="X31" s="25">
         <v>45818</v>
@@ -7009,13 +6992,13 @@
       <c r="AM31" s="26"/>
       <c r="AN31" s="26"/>
       <c r="AO31" s="22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AP31" s="23">
         <v>14093869</v>
       </c>
       <c r="AQ31" s="22" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AR31" s="23">
         <v>20233051</v>
@@ -7058,16 +7041,16 @@
         <v>32</v>
       </c>
       <c r="K32" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="L32" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="M32" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="N32" s="7" t="s">
         <v>428</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>429</v>
       </c>
       <c r="O32" s="10">
         <v>43282</v>
@@ -7085,12 +7068,12 @@
         <v>40</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U32" s="11"/>
       <c r="V32" s="11"/>
       <c r="W32" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="X32" s="10">
         <v>46266</v>
@@ -7104,7 +7087,7 @@
       <c r="AA32" s="11"/>
       <c r="AB32" s="11"/>
       <c r="AC32" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AD32" s="10">
         <v>43732</v>
@@ -7124,22 +7107,22 @@
       <c r="AM32" s="11"/>
       <c r="AN32" s="11"/>
       <c r="AO32" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP32" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ32" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR32" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS32" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT32" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU32" s="28">
         <v>452</v>
@@ -7177,16 +7160,16 @@
         <v>32</v>
       </c>
       <c r="K33" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L33" s="22" t="s">
         <v>231</v>
       </c>
       <c r="M33" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="N33" s="22" t="s">
         <v>434</v>
-      </c>
-      <c r="N33" s="22" t="s">
-        <v>435</v>
       </c>
       <c r="O33" s="25">
         <v>40695</v>
@@ -7207,7 +7190,7 @@
       <c r="U33" s="26"/>
       <c r="V33" s="26"/>
       <c r="W33" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="X33" s="25">
         <v>37094</v>
@@ -7222,10 +7205,10 @@
         <v>40</v>
       </c>
       <c r="AB33" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="AC33" s="22" t="s">
         <v>437</v>
-      </c>
-      <c r="AC33" s="22" t="s">
-        <v>438</v>
       </c>
       <c r="AD33" s="25">
         <v>40074</v>
@@ -7241,7 +7224,7 @@
       </c>
       <c r="AH33" s="26"/>
       <c r="AI33" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AJ33" s="25">
         <v>41021</v>
@@ -7254,22 +7237,22 @@
       </c>
       <c r="AM33" s="26"/>
       <c r="AN33" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="AO33" s="22" t="s">
         <v>440</v>
-      </c>
-      <c r="AO33" s="22" t="s">
-        <v>441</v>
       </c>
       <c r="AP33" s="23">
         <v>43284900</v>
       </c>
       <c r="AQ33" s="22" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AR33" s="23">
         <v>49638247</v>
       </c>
       <c r="AS33" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AT33" s="23">
         <v>52361786</v>
@@ -7310,16 +7293,16 @@
         <v>59</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>231</v>
       </c>
       <c r="M34" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="N34" s="7" t="s">
         <v>443</v>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>444</v>
       </c>
       <c r="O34" s="10">
         <v>38412</v>
@@ -7340,13 +7323,13 @@
       <c r="U34" s="11"/>
       <c r="V34" s="11"/>
       <c r="W34" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="X34" s="10">
         <v>40418</v>
       </c>
       <c r="Y34" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Z34" s="7" t="s">
         <v>40</v>
@@ -7356,13 +7339,13 @@
       </c>
       <c r="AB34" s="11"/>
       <c r="AC34" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AD34" s="10">
         <v>37507</v>
       </c>
       <c r="AE34" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AF34" s="7" t="s">
         <v>40</v>
@@ -7380,16 +7363,16 @@
       <c r="AM34" s="11"/>
       <c r="AN34" s="11"/>
       <c r="AO34" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="AP34" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="AQ34" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="AP34" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="AQ34" s="7" t="s">
+      <c r="AR34" s="8" t="s">
         <v>450</v>
-      </c>
-      <c r="AR34" s="8" t="s">
-        <v>451</v>
       </c>
       <c r="AS34" s="11"/>
       <c r="AT34" s="11"/>
@@ -7429,16 +7412,16 @@
         <v>83</v>
       </c>
       <c r="K35" s="22" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L35" s="22" t="s">
         <v>34</v>
       </c>
       <c r="M35" s="22" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N35" s="22" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O35" s="25">
         <v>44896</v>
@@ -7459,7 +7442,7 @@
       <c r="U35" s="26"/>
       <c r="V35" s="26"/>
       <c r="W35" s="22" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="X35" s="25">
         <v>37736</v>
@@ -7473,7 +7456,7 @@
       </c>
       <c r="AB35" s="26"/>
       <c r="AC35" s="22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AD35" s="25">
         <v>39932</v>
@@ -7493,13 +7476,13 @@
       <c r="AM35" s="26"/>
       <c r="AN35" s="26"/>
       <c r="AO35" s="22" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AP35" s="23">
         <v>44773340</v>
       </c>
       <c r="AQ35" s="22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AR35" s="23">
         <v>49448476</v>
@@ -7542,16 +7525,16 @@
         <v>59</v>
       </c>
       <c r="K36" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="L36" s="7" t="s">
         <v>457</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>458</v>
       </c>
       <c r="M36" s="7" t="s">
         <v>387</v>
       </c>
       <c r="N36" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O36" s="10">
         <v>36395</v>
@@ -7569,7 +7552,7 @@
         <v>46</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="U36" s="10">
         <v>31555</v>
@@ -7578,7 +7561,7 @@
         <v>32171639</v>
       </c>
       <c r="W36" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X36" s="10">
         <v>39734</v>
@@ -7592,7 +7575,7 @@
       </c>
       <c r="AB36" s="11"/>
       <c r="AC36" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AD36" s="10">
         <v>41218</v>
@@ -7612,19 +7595,19 @@
       <c r="AM36" s="11"/>
       <c r="AN36" s="11"/>
       <c r="AO36" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AP36" s="8">
         <v>32171639</v>
       </c>
       <c r="AQ36" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AR36" s="8">
         <v>49042426</v>
       </c>
       <c r="AS36" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AT36" s="8">
         <v>52562767</v>
@@ -7668,22 +7651,22 @@
         <v>265</v>
       </c>
       <c r="L37" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="M37" s="22" t="s">
         <v>464</v>
       </c>
-      <c r="M37" s="22" t="s">
-        <v>465</v>
-      </c>
       <c r="N37" s="22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O37" s="25">
         <v>43282</v>
       </c>
       <c r="P37" s="22" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q37" s="22" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R37" s="23">
         <v>38</v>
@@ -7692,7 +7675,7 @@
         <v>36</v>
       </c>
       <c r="T37" s="22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="U37" s="25">
         <v>31711</v>
@@ -7701,7 +7684,7 @@
         <v>32348188</v>
       </c>
       <c r="W37" s="22" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="X37" s="25">
         <v>43284</v>
@@ -7715,7 +7698,7 @@
       <c r="AA37" s="26"/>
       <c r="AB37" s="26"/>
       <c r="AC37" s="22" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AD37" s="25">
         <v>38942</v>
@@ -7727,7 +7710,7 @@
       <c r="AG37" s="26"/>
       <c r="AH37" s="26"/>
       <c r="AI37" s="22" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AJ37" s="25">
         <v>39484</v>
@@ -7739,19 +7722,19 @@
       <c r="AM37" s="26"/>
       <c r="AN37" s="26"/>
       <c r="AO37" s="22" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AP37" s="23">
         <v>47107378</v>
       </c>
       <c r="AQ37" s="22" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AR37" s="23">
         <v>48063708</v>
       </c>
       <c r="AS37" s="22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AT37" s="23">
         <v>32348188</v>
@@ -7792,16 +7775,16 @@
         <v>32</v>
       </c>
       <c r="K38" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="L38" s="7" t="s">
         <v>472</v>
-      </c>
-      <c r="L38" s="7" t="s">
-        <v>473</v>
       </c>
       <c r="M38" s="7" t="s">
         <v>232</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O38" s="10">
         <v>39995</v>
@@ -7819,16 +7802,16 @@
         <v>43</v>
       </c>
       <c r="T38" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="U38" s="10">
         <v>29722</v>
       </c>
       <c r="V38" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="W38" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="W38" s="7" t="s">
-        <v>477</v>
       </c>
       <c r="X38" s="10">
         <v>36349</v>
@@ -7842,7 +7825,7 @@
       </c>
       <c r="AB38" s="11"/>
       <c r="AC38" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AD38" s="10">
         <v>38056</v>
@@ -7856,7 +7839,7 @@
       </c>
       <c r="AH38" s="11"/>
       <c r="AI38" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AJ38" s="10">
         <v>45132</v>
@@ -7911,16 +7894,16 @@
         <v>32</v>
       </c>
       <c r="K39" s="22" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L39" s="22" t="s">
         <v>34</v>
       </c>
       <c r="M39" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="N39" s="22" t="s">
         <v>481</v>
-      </c>
-      <c r="N39" s="22" t="s">
-        <v>482</v>
       </c>
       <c r="O39" s="25">
         <v>38412</v>
@@ -7938,7 +7921,7 @@
         <v>38</v>
       </c>
       <c r="T39" s="22" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="U39" s="25">
         <v>30876</v>
@@ -7947,7 +7930,7 @@
         <v>30623263</v>
       </c>
       <c r="W39" s="22" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X39" s="25">
         <v>38904</v>
@@ -7965,7 +7948,7 @@
         <v>40</v>
       </c>
       <c r="AC39" s="22" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AD39" s="25">
         <v>39786</v>
@@ -7983,7 +7966,7 @@
         <v>231</v>
       </c>
       <c r="AI39" s="22" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AJ39" s="25">
         <v>40542</v>
@@ -8001,19 +7984,19 @@
         <v>231</v>
       </c>
       <c r="AO39" s="22" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AP39" s="23">
         <v>50642518</v>
       </c>
       <c r="AQ39" s="22" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AR39" s="23">
         <v>47209928</v>
       </c>
       <c r="AS39" s="22" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AT39" s="23">
         <v>49042474</v>
@@ -8054,13 +8037,13 @@
         <v>59</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>231</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N40" s="7" t="s">
         <v>233</v>
@@ -8081,7 +8064,7 @@
         <v>39</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="U40" s="10">
         <v>36424</v>
@@ -8090,7 +8073,7 @@
         <v>41654860</v>
       </c>
       <c r="W40" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="X40" s="10">
         <v>43322</v>
@@ -8103,7 +8086,7 @@
       </c>
       <c r="AA40" s="11"/>
       <c r="AB40" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AC40" s="11"/>
       <c r="AD40" s="11"/>
@@ -8176,10 +8159,10 @@
         <v>43282</v>
       </c>
       <c r="P41" s="22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q41" s="22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="R41" s="23">
         <v>50</v>
@@ -8188,22 +8171,22 @@
         <v>39</v>
       </c>
       <c r="T41" s="22" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U41" s="25">
         <v>30360</v>
       </c>
       <c r="V41" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="W41" s="22" t="s">
         <v>496</v>
-      </c>
-      <c r="W41" s="22" t="s">
-        <v>497</v>
       </c>
       <c r="X41" s="25">
         <v>37466</v>
       </c>
       <c r="Y41" s="23" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z41" s="22" t="s">
         <v>40</v>
@@ -8215,22 +8198,22 @@
         <v>231</v>
       </c>
       <c r="AC41" s="22" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AD41" s="25">
         <v>38719</v>
       </c>
       <c r="AE41" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="AF41" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG41" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH41" s="22" t="s">
         <v>500</v>
-      </c>
-      <c r="AF41" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG41" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH41" s="22" t="s">
-        <v>501</v>
       </c>
       <c r="AI41" s="26"/>
       <c r="AJ41" s="26"/>
@@ -8239,22 +8222,22 @@
       <c r="AM41" s="26"/>
       <c r="AN41" s="26"/>
       <c r="AO41" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="AP41" s="23" t="s">
         <v>497</v>
       </c>
-      <c r="AP41" s="23" t="s">
+      <c r="AQ41" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="AQ41" s="22" t="s">
+      <c r="AR41" s="23" t="s">
         <v>499</v>
       </c>
-      <c r="AR41" s="23" t="s">
-        <v>500</v>
-      </c>
       <c r="AS41" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="AT41" s="23" t="s">
         <v>495</v>
-      </c>
-      <c r="AT41" s="23" t="s">
-        <v>496</v>
       </c>
       <c r="AU41" s="27">
         <v>437</v>
@@ -8292,16 +8275,16 @@
         <v>32</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L42" s="8">
         <v>0</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="O42" s="10">
         <v>38761</v>
@@ -8322,7 +8305,7 @@
       <c r="U42" s="11"/>
       <c r="V42" s="11"/>
       <c r="W42" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X42" s="10">
         <v>39732</v>
@@ -8338,7 +8321,7 @@
       </c>
       <c r="AB42" s="11"/>
       <c r="AC42" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AD42" s="10">
         <v>41550</v>
@@ -8358,16 +8341,16 @@
       <c r="AM42" s="11"/>
       <c r="AN42" s="11"/>
       <c r="AO42" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="AP42" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="AP42" s="8" t="s">
+      <c r="AQ42" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="AR42" s="8" t="s">
         <v>507</v>
-      </c>
-      <c r="AQ42" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="AR42" s="8" t="s">
-        <v>508</v>
       </c>
       <c r="AS42" s="11"/>
       <c r="AT42" s="11"/>
@@ -8407,16 +8390,16 @@
         <v>59</v>
       </c>
       <c r="K43" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="L43" s="22" t="s">
         <v>509</v>
-      </c>
-      <c r="L43" s="22" t="s">
-        <v>510</v>
       </c>
       <c r="M43" s="22" t="s">
         <v>328</v>
       </c>
       <c r="N43" s="22" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O43" s="25">
         <v>44927</v>
@@ -8434,12 +8417,12 @@
         <v>40</v>
       </c>
       <c r="T43" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U43" s="26"/>
       <c r="V43" s="26"/>
       <c r="W43" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="X43" s="26"/>
       <c r="Y43" s="26"/>
@@ -8450,10 +8433,10 @@
         <v>231</v>
       </c>
       <c r="AB43" s="22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AC43" s="22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AD43" s="26"/>
       <c r="AE43" s="26"/>
@@ -8464,10 +8447,10 @@
         <v>231</v>
       </c>
       <c r="AH43" s="22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AI43" s="22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AJ43" s="26"/>
       <c r="AK43" s="26"/>
@@ -8478,22 +8461,22 @@
         <v>231</v>
       </c>
       <c r="AN43" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="AO43" s="22" t="s">
         <v>514</v>
-      </c>
-      <c r="AO43" s="22" t="s">
-        <v>515</v>
       </c>
       <c r="AP43" s="23">
         <v>29007087</v>
       </c>
       <c r="AQ43" s="22" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AR43" s="23">
         <v>29007087</v>
       </c>
       <c r="AS43" s="22" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AT43" s="23">
         <v>29007087</v>
@@ -8534,16 +8517,16 @@
         <v>32</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>34</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="O44" s="10">
         <v>44531</v>
@@ -8564,7 +8547,7 @@
       <c r="U44" s="11"/>
       <c r="V44" s="11"/>
       <c r="W44" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="X44" s="10">
         <v>38729</v>
@@ -8579,10 +8562,10 @@
         <v>40</v>
       </c>
       <c r="AB44" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="AC44" s="7" t="s">
         <v>519</v>
-      </c>
-      <c r="AC44" s="7" t="s">
-        <v>520</v>
       </c>
       <c r="AD44" s="10">
         <v>41687</v>
@@ -8648,7 +8631,7 @@
       </c>
       <c r="K45" s="26"/>
       <c r="L45" s="22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M45" s="22" t="s">
         <v>258</v>
@@ -8672,7 +8655,7 @@
         <v>41</v>
       </c>
       <c r="T45" s="22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="U45" s="25">
         <v>28897</v>
@@ -8699,7 +8682,7 @@
       <c r="AM45" s="26"/>
       <c r="AN45" s="26"/>
       <c r="AO45" s="22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AP45" s="23">
         <v>26974472</v>
@@ -8744,16 +8727,16 @@
         <v>59</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>34</v>
       </c>
       <c r="M46" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="N46" s="7" t="s">
         <v>524</v>
-      </c>
-      <c r="N46" s="7" t="s">
-        <v>525</v>
       </c>
       <c r="O46" s="10">
         <v>39029</v>
@@ -8771,7 +8754,7 @@
         <v>38</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="U46" s="10">
         <v>30396</v>
@@ -8780,7 +8763,7 @@
         <v>31116825</v>
       </c>
       <c r="W46" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="X46" s="10">
         <v>40190</v>
@@ -8796,7 +8779,7 @@
       </c>
       <c r="AB46" s="11"/>
       <c r="AC46" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AD46" s="10">
         <v>42397</v>
@@ -8816,7 +8799,7 @@
       <c r="AM46" s="11"/>
       <c r="AN46" s="11"/>
       <c r="AO46" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AP46" s="8">
         <v>6500573</v>
@@ -8861,16 +8844,16 @@
         <v>59</v>
       </c>
       <c r="K47" s="22" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L47" s="22" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M47" s="22" t="s">
         <v>328</v>
       </c>
       <c r="N47" s="22" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="O47" s="25">
         <v>37926</v>
@@ -8954,13 +8937,13 @@
         <v>32</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>231</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N48" s="7" t="s">
         <v>244</v>
@@ -8981,7 +8964,7 @@
         <v>40</v>
       </c>
       <c r="T48" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="U48" s="10">
         <v>28322</v>
@@ -8990,7 +8973,7 @@
         <v>26074101</v>
       </c>
       <c r="W48" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="X48" s="10">
         <v>39693</v>
@@ -9006,7 +8989,7 @@
       </c>
       <c r="AB48" s="11"/>
       <c r="AC48" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AD48" s="10">
         <v>35807</v>
@@ -9021,7 +9004,7 @@
         <v>40</v>
       </c>
       <c r="AH48" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AI48" s="11"/>
       <c r="AJ48" s="11"/>
@@ -9030,22 +9013,22 @@
       <c r="AM48" s="11"/>
       <c r="AN48" s="11"/>
       <c r="AO48" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP48" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ48" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR48" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS48" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT48" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU48" s="28">
         <v>262</v>
@@ -9083,16 +9066,16 @@
         <v>59</v>
       </c>
       <c r="K49" s="22" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L49" s="22" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="M49" s="22" t="s">
         <v>317</v>
       </c>
       <c r="N49" s="22" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="O49" s="25">
         <v>43288</v>
@@ -9110,7 +9093,7 @@
         <v>42</v>
       </c>
       <c r="T49" s="22" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="U49" s="25">
         <v>35782</v>
@@ -9119,7 +9102,7 @@
         <v>40277726</v>
       </c>
       <c r="W49" s="22" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="X49" s="25">
         <v>44862</v>
@@ -9135,7 +9118,7 @@
       </c>
       <c r="AB49" s="26"/>
       <c r="AC49" s="22" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AD49" s="25">
         <v>42934</v>
@@ -9157,13 +9140,13 @@
       <c r="AM49" s="26"/>
       <c r="AN49" s="26"/>
       <c r="AO49" s="22" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AP49" s="23">
         <v>40277726</v>
       </c>
       <c r="AQ49" s="22" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AR49" s="23">
         <v>59624403</v>
@@ -9206,10 +9189,10 @@
         <v>32</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M50" s="7" t="s">
         <v>243</v>
@@ -9221,19 +9204,19 @@
         <v>44896</v>
       </c>
       <c r="P50" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="R50" s="7" t="s">
         <v>544</v>
-      </c>
-      <c r="Q50" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="R50" s="7" t="s">
-        <v>545</v>
       </c>
       <c r="S50" s="8">
         <v>37</v>
       </c>
       <c r="T50" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="U50" s="10">
         <v>30842</v>
@@ -9242,7 +9225,7 @@
         <v>30623222</v>
       </c>
       <c r="W50" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X50" s="10">
         <v>41863</v>
@@ -9258,7 +9241,7 @@
       </c>
       <c r="AB50" s="11"/>
       <c r="AC50" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AD50" s="10">
         <v>42886</v>
@@ -9280,7 +9263,7 @@
       <c r="AM50" s="11"/>
       <c r="AN50" s="11"/>
       <c r="AO50" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AP50" s="8">
         <v>30623222</v>
@@ -9326,13 +9309,13 @@
       </c>
       <c r="K51" s="26"/>
       <c r="L51" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="M51" s="22" t="s">
         <v>549</v>
       </c>
-      <c r="M51" s="22" t="s">
-        <v>550</v>
-      </c>
       <c r="N51" s="22" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O51" s="25">
         <v>37926</v>
@@ -9350,7 +9333,7 @@
         <v>43</v>
       </c>
       <c r="T51" s="22" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U51" s="25">
         <v>22905</v>
@@ -9359,7 +9342,7 @@
         <v>16110608</v>
       </c>
       <c r="W51" s="22" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X51" s="25">
         <v>35688</v>
@@ -9374,7 +9357,7 @@
         <v>40</v>
       </c>
       <c r="AB51" s="22" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AC51" s="26"/>
       <c r="AD51" s="26"/>
@@ -9389,7 +9372,7 @@
       <c r="AM51" s="26"/>
       <c r="AN51" s="26"/>
       <c r="AO51" s="22" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AP51" s="23">
         <v>16110608</v>
@@ -9434,16 +9417,16 @@
         <v>32</v>
       </c>
       <c r="K52" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="L52" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="L52" s="7" t="s">
+      <c r="M52" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="N52" s="7" t="s">
         <v>556</v>
-      </c>
-      <c r="M52" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="N52" s="7" t="s">
-        <v>557</v>
       </c>
       <c r="O52" s="10">
         <v>40980</v>
@@ -9461,7 +9444,7 @@
         <v>37</v>
       </c>
       <c r="T52" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="U52" s="10">
         <v>21333</v>
@@ -9470,7 +9453,7 @@
         <v>11923198</v>
       </c>
       <c r="W52" s="7" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="X52" s="10">
         <v>41744</v>
@@ -9498,13 +9481,13 @@
       <c r="AM52" s="11"/>
       <c r="AN52" s="11"/>
       <c r="AO52" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AP52" s="8">
         <v>53920106</v>
       </c>
       <c r="AQ52" s="7" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AR52" s="8">
         <v>11923198</v>
@@ -9520,10 +9503,10 @@
         <v>46266.539976851855</v>
       </c>
       <c r="B53" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="C53" s="22" t="s">
         <v>561</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>562</v>
       </c>
       <c r="D53" s="23">
         <v>27696966</v>
@@ -9532,13 +9515,13 @@
         <v>29218</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G53" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I53" s="22" t="s">
         <v>31</v>
@@ -9547,16 +9530,16 @@
         <v>83</v>
       </c>
       <c r="K53" s="22" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L53" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="M53" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="M53" s="22" t="s">
-        <v>566</v>
-      </c>
       <c r="N53" s="22" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O53" s="25">
         <v>38322</v>
@@ -9574,7 +9557,7 @@
         <v>43</v>
       </c>
       <c r="T53" s="22" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="U53" s="25">
         <v>30483</v>
@@ -9583,7 +9566,7 @@
         <v>29961923</v>
       </c>
       <c r="W53" s="22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="X53" s="25">
         <v>39511</v>
@@ -9598,10 +9581,10 @@
         <v>40</v>
       </c>
       <c r="AB53" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="AC53" s="22" t="s">
         <v>569</v>
-      </c>
-      <c r="AC53" s="22" t="s">
-        <v>570</v>
       </c>
       <c r="AD53" s="25">
         <v>40976</v>
@@ -9623,19 +9606,19 @@
       <c r="AM53" s="26"/>
       <c r="AN53" s="26"/>
       <c r="AO53" s="22" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AP53" s="23">
         <v>29961923</v>
       </c>
       <c r="AQ53" s="22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AR53" s="23">
         <v>48063721</v>
       </c>
       <c r="AS53" s="22" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AT53" s="23">
         <v>52361749</v>
@@ -9649,10 +9632,10 @@
         <v>46266.544583333336</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>571</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>572</v>
       </c>
       <c r="D54" s="8">
         <v>31116867</v>
@@ -9661,7 +9644,7 @@
         <v>30978</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>30</v>
@@ -9676,7 +9659,7 @@
         <v>32</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>34</v>
@@ -9703,7 +9686,7 @@
         <v>40</v>
       </c>
       <c r="T54" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="U54" s="10">
         <v>35325</v>
@@ -9712,13 +9695,13 @@
         <v>39688026</v>
       </c>
       <c r="W54" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="X54" s="10">
         <v>42301</v>
       </c>
       <c r="Y54" s="8" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="Z54" s="7" t="s">
         <v>40</v>
@@ -9726,13 +9709,13 @@
       <c r="AA54" s="11"/>
       <c r="AB54" s="11"/>
       <c r="AC54" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AD54" s="10">
         <v>43573</v>
       </c>
       <c r="AE54" s="8" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AF54" s="7" t="s">
         <v>40</v>
@@ -9746,10 +9729,10 @@
       <c r="AM54" s="11"/>
       <c r="AN54" s="11"/>
       <c r="AO54" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP54" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ54" s="11"/>
       <c r="AR54" s="11"/>
@@ -9764,10 +9747,10 @@
         <v>46266.544629629629</v>
       </c>
       <c r="B55" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="C55" s="22" t="s">
         <v>580</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>581</v>
       </c>
       <c r="D55" s="23">
         <v>32381359</v>
@@ -9776,7 +9759,7 @@
         <v>31549</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G55" s="22" t="s">
         <v>30</v>
@@ -9797,10 +9780,10 @@
         <v>231</v>
       </c>
       <c r="M55" s="22" t="s">
+        <v>582</v>
+      </c>
+      <c r="N55" s="22" t="s">
         <v>583</v>
-      </c>
-      <c r="N55" s="22" t="s">
-        <v>584</v>
       </c>
       <c r="O55" s="25">
         <v>43800</v>
@@ -9839,7 +9822,7 @@
       <c r="AM55" s="26"/>
       <c r="AN55" s="26"/>
       <c r="AO55" s="22" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AP55" s="23">
         <v>32381359</v>
@@ -9857,10 +9840,10 @@
         <v>46266.548125000001</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>586</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>587</v>
       </c>
       <c r="D56" s="8">
         <v>33363882</v>
@@ -9869,7 +9852,7 @@
         <v>32208</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>30</v>
@@ -9891,7 +9874,7 @@
         <v>243</v>
       </c>
       <c r="N56" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="O56" s="10">
         <v>40695</v>
@@ -9909,7 +9892,7 @@
         <v>39</v>
       </c>
       <c r="T56" s="7" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="U56" s="10">
         <v>30926</v>
@@ -9918,7 +9901,7 @@
         <v>30623284</v>
       </c>
       <c r="W56" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="X56" s="10">
         <v>41750</v>
@@ -9934,7 +9917,7 @@
       </c>
       <c r="AB56" s="11"/>
       <c r="AC56" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AD56" s="10">
         <v>43531</v>
@@ -9958,10 +9941,10 @@
       <c r="AM56" s="11"/>
       <c r="AN56" s="11"/>
       <c r="AO56" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AP56" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AQ56" s="11"/>
       <c r="AR56" s="11"/>
@@ -9976,10 +9959,10 @@
         <v>46266.559074074074</v>
       </c>
       <c r="B57" s="22" t="s">
+        <v>593</v>
+      </c>
+      <c r="C57" s="22" t="s">
         <v>594</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>595</v>
       </c>
       <c r="D57" s="23">
         <v>28242038</v>
@@ -9988,7 +9971,7 @@
         <v>29443</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G57" s="22" t="s">
         <v>30</v>
@@ -10003,25 +9986,25 @@
         <v>32</v>
       </c>
       <c r="K57" s="22" t="s">
+        <v>596</v>
+      </c>
+      <c r="L57" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="L57" s="22" t="s">
+      <c r="M57" s="22" t="s">
         <v>598</v>
       </c>
-      <c r="M57" s="22" t="s">
+      <c r="N57" s="22" t="s">
         <v>599</v>
-      </c>
-      <c r="N57" s="22" t="s">
-        <v>600</v>
       </c>
       <c r="O57" s="25">
         <v>44896</v>
       </c>
       <c r="P57" s="22" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q57" s="22" t="s">
         <v>601</v>
-      </c>
-      <c r="Q57" s="22" t="s">
-        <v>602</v>
       </c>
       <c r="R57" s="23">
         <v>48</v>
@@ -10030,12 +10013,12 @@
         <v>40</v>
       </c>
       <c r="T57" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U57" s="26"/>
       <c r="V57" s="26"/>
       <c r="W57" s="22" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="X57" s="25">
         <v>36719</v>
@@ -10050,10 +10033,10 @@
         <v>40</v>
       </c>
       <c r="AB57" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="AC57" s="22" t="s">
         <v>604</v>
-      </c>
-      <c r="AC57" s="22" t="s">
-        <v>605</v>
       </c>
       <c r="AD57" s="25">
         <v>37943</v>
@@ -10069,7 +10052,7 @@
       </c>
       <c r="AH57" s="26"/>
       <c r="AI57" s="22" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AJ57" s="25">
         <v>42171</v>
@@ -10083,22 +10066,22 @@
       <c r="AM57" s="26"/>
       <c r="AN57" s="26"/>
       <c r="AO57" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP57" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ57" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR57" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS57" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT57" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU57" s="27">
         <v>516</v>
@@ -10109,10 +10092,10 @@
         <v>46266.565613425926</v>
       </c>
       <c r="B58" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>607</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>608</v>
       </c>
       <c r="D58" s="8">
         <v>27419838</v>
@@ -10121,7 +10104,7 @@
         <v>28985</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>30</v>
@@ -10136,16 +10119,16 @@
         <v>59</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>34</v>
       </c>
       <c r="M58" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="N58" s="7" t="s">
         <v>611</v>
-      </c>
-      <c r="N58" s="7" t="s">
-        <v>612</v>
       </c>
       <c r="O58" s="10">
         <v>37926</v>
@@ -10154,7 +10137,7 @@
         <v>46</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="R58" s="8">
         <v>50</v>
@@ -10163,7 +10146,7 @@
         <v>43</v>
       </c>
       <c r="T58" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="U58" s="10">
         <v>29106</v>
@@ -10172,7 +10155,7 @@
         <v>27419961</v>
       </c>
       <c r="W58" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="X58" s="10">
         <v>40109</v>
@@ -10200,19 +10183,19 @@
       <c r="AM58" s="11"/>
       <c r="AN58" s="11"/>
       <c r="AO58" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AP58" s="8">
         <v>27419838</v>
       </c>
       <c r="AQ58" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AR58" s="8">
         <v>27419961</v>
       </c>
       <c r="AS58" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AT58" s="8">
         <v>49638278</v>
@@ -10226,10 +10209,10 @@
         <v>46266.572627314818</v>
       </c>
       <c r="B59" s="22" t="s">
+        <v>615</v>
+      </c>
+      <c r="C59" s="22" t="s">
         <v>616</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>617</v>
       </c>
       <c r="D59" s="23">
         <v>36566409</v>
@@ -10238,7 +10221,7 @@
         <v>33597</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G59" s="22" t="s">
         <v>30</v>
@@ -10259,10 +10242,10 @@
         <v>231</v>
       </c>
       <c r="M59" s="22" t="s">
+        <v>618</v>
+      </c>
+      <c r="N59" s="22" t="s">
         <v>619</v>
-      </c>
-      <c r="N59" s="22" t="s">
-        <v>620</v>
       </c>
       <c r="O59" s="25">
         <v>44896</v>
@@ -10283,7 +10266,7 @@
       <c r="U59" s="26"/>
       <c r="V59" s="26"/>
       <c r="W59" s="22" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="X59" s="25">
         <v>39951</v>
@@ -10301,7 +10284,7 @@
         <v>231</v>
       </c>
       <c r="AC59" s="22" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AD59" s="25">
         <v>41324</v>
@@ -10343,10 +10326,10 @@
         <v>46266.579097222224</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>623</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>624</v>
       </c>
       <c r="D60" s="8">
         <v>14308336</v>
@@ -10355,13 +10338,13 @@
         <v>22515</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>31</v>
@@ -10370,16 +10353,16 @@
         <v>59</v>
       </c>
       <c r="K60" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="L60" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="L60" s="7" t="s">
+      <c r="M60" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="M60" s="7" t="s">
+      <c r="N60" s="7" t="s">
         <v>629</v>
-      </c>
-      <c r="N60" s="7" t="s">
-        <v>630</v>
       </c>
       <c r="O60" s="10">
         <v>44531</v>
@@ -10397,7 +10380,7 @@
         <v>45</v>
       </c>
       <c r="T60" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="U60" s="10">
         <v>21225</v>
@@ -10406,7 +10389,7 @@
         <v>12134755</v>
       </c>
       <c r="W60" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="X60" s="10">
         <v>32679</v>
@@ -10421,7 +10404,7 @@
         <v>40</v>
       </c>
       <c r="AB60" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AC60" s="11"/>
       <c r="AD60" s="11"/>
@@ -10436,13 +10419,13 @@
       <c r="AM60" s="11"/>
       <c r="AN60" s="11"/>
       <c r="AO60" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AP60" s="8">
         <v>14308336</v>
       </c>
       <c r="AQ60" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AR60" s="8">
         <v>12134755</v>
@@ -10458,10 +10441,10 @@
         <v>46266.585925925923</v>
       </c>
       <c r="B61" s="22" t="s">
+        <v>634</v>
+      </c>
+      <c r="C61" s="22" t="s">
         <v>635</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>636</v>
       </c>
       <c r="D61" s="23">
         <v>31592200</v>
@@ -10470,10 +10453,10 @@
         <v>31331</v>
       </c>
       <c r="F61" s="22" t="s">
+        <v>636</v>
+      </c>
+      <c r="G61" s="22" t="s">
         <v>637</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>638</v>
       </c>
       <c r="H61" s="23">
         <v>3382417139</v>
@@ -10485,16 +10468,16 @@
         <v>59</v>
       </c>
       <c r="K61" s="22" t="s">
+        <v>638</v>
+      </c>
+      <c r="L61" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="M61" s="22" t="s">
         <v>639</v>
       </c>
-      <c r="L61" s="22" t="s">
-        <v>598</v>
-      </c>
-      <c r="M61" s="22" t="s">
+      <c r="N61" s="22" t="s">
         <v>640</v>
-      </c>
-      <c r="N61" s="22" t="s">
-        <v>641</v>
       </c>
       <c r="O61" s="25">
         <v>40483</v>
@@ -10503,7 +10486,7 @@
         <v>48</v>
       </c>
       <c r="Q61" s="22" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="R61" s="23">
         <v>48</v>
@@ -10512,7 +10495,7 @@
         <v>39</v>
       </c>
       <c r="T61" s="22" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="U61" s="25">
         <v>32961</v>
@@ -10521,7 +10504,7 @@
         <v>34408674</v>
       </c>
       <c r="W61" s="22" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="X61" s="25">
         <v>40494</v>
@@ -10536,10 +10519,10 @@
         <v>40</v>
       </c>
       <c r="AB61" s="22" t="s">
+        <v>644</v>
+      </c>
+      <c r="AC61" s="22" t="s">
         <v>645</v>
-      </c>
-      <c r="AC61" s="22" t="s">
-        <v>646</v>
       </c>
       <c r="AD61" s="25">
         <v>39387</v>
@@ -10554,10 +10537,10 @@
         <v>40</v>
       </c>
       <c r="AH61" s="22" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AI61" s="22" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AJ61" s="25">
         <v>46085</v>
@@ -10573,7 +10556,7 @@
       </c>
       <c r="AN61" s="26"/>
       <c r="AO61" s="22" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AP61" s="23">
         <v>34408674</v>
@@ -10591,10 +10574,10 @@
         <v>46266.592083333337</v>
       </c>
       <c r="B62" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>648</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>649</v>
       </c>
       <c r="D62" s="8">
         <v>21767314</v>
@@ -10603,13 +10586,13 @@
         <v>26336</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>145</v>
@@ -10624,10 +10607,10 @@
         <v>231</v>
       </c>
       <c r="M62" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="N62" s="7" t="s">
         <v>652</v>
-      </c>
-      <c r="N62" s="7" t="s">
-        <v>653</v>
       </c>
       <c r="O62" s="10">
         <v>37926</v>
@@ -10645,7 +10628,7 @@
         <v>43</v>
       </c>
       <c r="T62" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="U62" s="10">
         <v>29241</v>
@@ -10654,7 +10637,7 @@
         <v>27696982</v>
       </c>
       <c r="W62" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="X62" s="10">
         <v>36231</v>
@@ -10672,7 +10655,7 @@
         <v>231</v>
       </c>
       <c r="AC62" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AD62" s="10">
         <v>42558</v>
@@ -10696,19 +10679,19 @@
       <c r="AM62" s="11"/>
       <c r="AN62" s="11"/>
       <c r="AO62" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AP62" s="8">
         <v>27696982</v>
       </c>
       <c r="AQ62" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AR62" s="8">
         <v>41493795</v>
       </c>
       <c r="AS62" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AT62" s="8">
         <v>55651735</v>
@@ -10722,10 +10705,10 @@
         <v>46266.609479166669</v>
       </c>
       <c r="B63" s="22" t="s">
+        <v>657</v>
+      </c>
+      <c r="C63" s="22" t="s">
         <v>658</v>
-      </c>
-      <c r="C63" s="22" t="s">
-        <v>659</v>
       </c>
       <c r="D63" s="23">
         <v>25292978</v>
@@ -10734,7 +10717,7 @@
         <v>28106</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G63" s="22" t="s">
         <v>30</v>
@@ -10749,16 +10732,16 @@
         <v>59</v>
       </c>
       <c r="K63" s="22" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L63" s="22" t="s">
         <v>34</v>
       </c>
       <c r="M63" s="22" t="s">
+        <v>661</v>
+      </c>
+      <c r="N63" s="22" t="s">
         <v>662</v>
-      </c>
-      <c r="N63" s="22" t="s">
-        <v>663</v>
       </c>
       <c r="O63" s="25">
         <v>36074</v>
@@ -10776,7 +10759,7 @@
         <v>43</v>
       </c>
       <c r="T63" s="22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="U63" s="25">
         <v>34249</v>
@@ -10785,7 +10768,7 @@
         <v>37295613</v>
       </c>
       <c r="W63" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="X63" s="25">
         <v>42394</v>
@@ -10815,7 +10798,7 @@
       <c r="AM63" s="26"/>
       <c r="AN63" s="26"/>
       <c r="AO63" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AP63" s="23">
         <v>55214161</v>
@@ -10833,10 +10816,10 @@
         <v>46266.610266203701</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>666</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>667</v>
       </c>
       <c r="D64" s="8">
         <v>37295613</v>
@@ -10845,7 +10828,7 @@
         <v>34249</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>30</v>
@@ -10860,16 +10843,16 @@
         <v>59</v>
       </c>
       <c r="K64" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="L64" s="7" t="s">
         <v>669</v>
-      </c>
-      <c r="L64" s="7" t="s">
-        <v>670</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>328</v>
       </c>
       <c r="N64" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="O64" s="10">
         <v>44896</v>
@@ -10887,7 +10870,7 @@
         <v>37</v>
       </c>
       <c r="T64" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="U64" s="10">
         <v>28106</v>
@@ -10896,7 +10879,7 @@
         <v>25292978</v>
       </c>
       <c r="W64" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="X64" s="10">
         <v>42394</v>
@@ -10926,22 +10909,22 @@
       <c r="AM64" s="11"/>
       <c r="AN64" s="11"/>
       <c r="AO64" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AP64" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AQ64" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AR64" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AS64" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AT64" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AU64" s="28">
         <v>555</v>
@@ -10952,10 +10935,10 @@
         <v>46266.650995370372</v>
       </c>
       <c r="B65" s="22" t="s">
+        <v>673</v>
+      </c>
+      <c r="C65" s="22" t="s">
         <v>674</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>675</v>
       </c>
       <c r="D65" s="23">
         <v>34175455</v>
@@ -10964,7 +10947,7 @@
         <v>32630</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G65" s="22" t="s">
         <v>30</v>
@@ -10980,13 +10963,13 @@
       </c>
       <c r="K65" s="26"/>
       <c r="L65" s="22" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="M65" s="22" t="s">
         <v>243</v>
       </c>
       <c r="N65" s="22" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O65" s="25">
         <v>43282</v>
@@ -10995,7 +10978,7 @@
         <v>50</v>
       </c>
       <c r="Q65" s="22" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="R65" s="23">
         <v>50</v>
@@ -11004,7 +10987,7 @@
         <v>40</v>
       </c>
       <c r="T65" s="22" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="U65" s="25">
         <v>27657</v>
@@ -11013,7 +10996,7 @@
         <v>24918009</v>
       </c>
       <c r="W65" s="22" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="X65" s="25">
         <v>39478</v>
@@ -11028,10 +11011,10 @@
         <v>40</v>
       </c>
       <c r="AB65" s="22" t="s">
+        <v>680</v>
+      </c>
+      <c r="AC65" s="22" t="s">
         <v>681</v>
-      </c>
-      <c r="AC65" s="22" t="s">
-        <v>682</v>
       </c>
       <c r="AD65" s="25">
         <v>40837</v>
@@ -11047,7 +11030,7 @@
       </c>
       <c r="AH65" s="26"/>
       <c r="AI65" s="22" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AJ65" s="25">
         <v>46071</v>
@@ -11061,10 +11044,10 @@
       <c r="AM65" s="26"/>
       <c r="AN65" s="26"/>
       <c r="AO65" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP65" s="22" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AQ65" s="26"/>
       <c r="AR65" s="26"/>
@@ -11079,10 +11062,10 @@
         <v>46266.67082175926</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>685</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>686</v>
       </c>
       <c r="D66" s="8">
         <v>25773814</v>
@@ -11091,7 +11074,7 @@
         <v>28147</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>30</v>
@@ -11112,10 +11095,10 @@
         <v>34</v>
       </c>
       <c r="M66" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="N66" s="7" t="s">
         <v>688</v>
-      </c>
-      <c r="N66" s="7" t="s">
-        <v>689</v>
       </c>
       <c r="O66" s="10">
         <v>37653</v>
@@ -11133,7 +11116,7 @@
         <v>42</v>
       </c>
       <c r="T66" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="U66" s="10">
         <v>26701</v>
@@ -11142,7 +11125,7 @@
         <v>21910948</v>
       </c>
       <c r="W66" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="X66" s="10">
         <v>38765</v>
@@ -11157,7 +11140,7 @@
         <v>40</v>
       </c>
       <c r="AB66" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AC66" s="11"/>
       <c r="AD66" s="11"/>
@@ -11172,13 +11155,13 @@
       <c r="AM66" s="11"/>
       <c r="AN66" s="11"/>
       <c r="AO66" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AP66" s="8">
         <v>46998244</v>
       </c>
       <c r="AQ66" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AR66" s="8">
         <v>21910948</v>
@@ -11194,10 +11177,10 @@
         <v>46266.705428240741</v>
       </c>
       <c r="B67" s="22" t="s">
+        <v>693</v>
+      </c>
+      <c r="C67" s="22" t="s">
         <v>694</v>
-      </c>
-      <c r="C67" s="22" t="s">
-        <v>695</v>
       </c>
       <c r="D67" s="23">
         <v>29931732</v>
@@ -11206,7 +11189,7 @@
         <v>30460</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G67" s="22" t="s">
         <v>30</v>
@@ -11221,13 +11204,13 @@
         <v>32</v>
       </c>
       <c r="K67" s="22" t="s">
+        <v>696</v>
+      </c>
+      <c r="L67" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="M67" s="22" t="s">
         <v>697</v>
-      </c>
-      <c r="L67" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="M67" s="22" t="s">
-        <v>698</v>
       </c>
       <c r="N67" s="22" t="s">
         <v>244</v>
@@ -11251,7 +11234,7 @@
       <c r="U67" s="26"/>
       <c r="V67" s="26"/>
       <c r="W67" s="22" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="X67" s="25">
         <v>44247</v>
@@ -11265,7 +11248,7 @@
       <c r="AA67" s="26"/>
       <c r="AB67" s="26"/>
       <c r="AC67" s="22" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AD67" s="25">
         <v>44247</v>
@@ -11285,22 +11268,22 @@
       <c r="AM67" s="26"/>
       <c r="AN67" s="26"/>
       <c r="AO67" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AP67" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ67" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AR67" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AS67" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AT67" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU67" s="27">
         <v>430</v>
@@ -11311,19 +11294,19 @@
         <v>46266.711944444447</v>
       </c>
       <c r="B68" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>701</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="D68" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="E68" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="F68" s="7" t="s">
         <v>704</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>705</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>30</v>
@@ -11338,7 +11321,7 @@
         <v>32</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L68" s="7" t="s">
         <v>34</v>
@@ -11370,13 +11353,13 @@
       <c r="U68" s="11"/>
       <c r="V68" s="11"/>
       <c r="W68" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="X68" s="10">
         <v>41697</v>
       </c>
       <c r="Y68" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="Z68" s="7" t="s">
         <v>40</v>
@@ -11385,7 +11368,7 @@
         <v>231</v>
       </c>
       <c r="AB68" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AC68" s="11"/>
       <c r="AD68" s="11"/>
@@ -11420,10 +11403,10 @@
         <v>46266.739756944444</v>
       </c>
       <c r="B69" s="22" t="s">
+        <v>708</v>
+      </c>
+      <c r="C69" s="22" t="s">
         <v>709</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>710</v>
       </c>
       <c r="D69" s="23">
         <v>20703873</v>
@@ -11432,7 +11415,7 @@
         <v>25536</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G69" s="22" t="s">
         <v>30</v>
@@ -11447,16 +11430,16 @@
         <v>83</v>
       </c>
       <c r="K69" s="22" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L69" s="22" t="s">
         <v>231</v>
       </c>
       <c r="M69" s="22" t="s">
+        <v>711</v>
+      </c>
+      <c r="N69" s="22" t="s">
         <v>712</v>
-      </c>
-      <c r="N69" s="22" t="s">
-        <v>713</v>
       </c>
       <c r="O69" s="25">
         <v>39239</v>
@@ -11465,7 +11448,7 @@
         <v>48</v>
       </c>
       <c r="Q69" s="22" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="R69" s="23">
         <v>48</v>
@@ -11479,7 +11462,7 @@
       <c r="U69" s="26"/>
       <c r="V69" s="26"/>
       <c r="W69" s="22" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="X69" s="25">
         <v>39050</v>
@@ -11497,7 +11480,7 @@
         <v>237</v>
       </c>
       <c r="AC69" s="22" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AD69" s="25">
         <v>40091</v>
@@ -11512,10 +11495,10 @@
         <v>40</v>
       </c>
       <c r="AH69" s="22" t="s">
+        <v>716</v>
+      </c>
+      <c r="AI69" s="22" t="s">
         <v>717</v>
-      </c>
-      <c r="AI69" s="22" t="s">
-        <v>718</v>
       </c>
       <c r="AJ69" s="25">
         <v>35864</v>
@@ -11530,10 +11513,10 @@
         <v>231</v>
       </c>
       <c r="AN69" s="22" t="s">
+        <v>718</v>
+      </c>
+      <c r="AO69" s="22" t="s">
         <v>719</v>
-      </c>
-      <c r="AO69" s="22" t="s">
-        <v>720</v>
       </c>
       <c r="AP69" s="23">
         <v>20703873</v>
@@ -11559,10 +11542,10 @@
         <v>46266.754699074074</v>
       </c>
       <c r="B70" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>721</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>722</v>
       </c>
       <c r="D70" s="8">
         <v>18663470</v>
@@ -11571,7 +11554,7 @@
         <v>24097</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>30</v>
@@ -11583,17 +11566,17 @@
         <v>145</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="K70" s="11"/>
       <c r="L70" s="7" t="s">
         <v>231</v>
       </c>
       <c r="M70" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="O70" s="10">
         <v>44896</v>
@@ -11632,19 +11615,19 @@
       <c r="AM70" s="11"/>
       <c r="AN70" s="11"/>
       <c r="AO70" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AP70" s="8">
         <v>18663470</v>
       </c>
       <c r="AQ70" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AR70" s="8">
         <v>18663470</v>
       </c>
       <c r="AS70" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AT70" s="8">
         <v>19663470</v>
@@ -11658,19 +11641,19 @@
         <v>46266.771493055552</v>
       </c>
       <c r="B71" s="22" t="s">
+        <v>725</v>
+      </c>
+      <c r="C71" s="22" t="s">
         <v>726</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>727</v>
       </c>
       <c r="D71" s="23">
         <v>17301624</v>
       </c>
       <c r="E71" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="F71" s="22" t="s">
         <v>728</v>
-      </c>
-      <c r="F71" s="22" t="s">
-        <v>729</v>
       </c>
       <c r="G71" s="22" t="s">
         <v>30</v>
@@ -11685,16 +11668,16 @@
         <v>59</v>
       </c>
       <c r="K71" s="22" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L71" s="22" t="s">
         <v>231</v>
       </c>
       <c r="M71" s="22" t="s">
+        <v>730</v>
+      </c>
+      <c r="N71" s="22" t="s">
         <v>731</v>
-      </c>
-      <c r="N71" s="22" t="s">
-        <v>732</v>
       </c>
       <c r="O71" s="25">
         <v>37960</v>
@@ -11712,7 +11695,7 @@
         <v>40</v>
       </c>
       <c r="T71" s="22" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="U71" s="25">
         <v>25910</v>
@@ -11721,7 +11704,7 @@
         <v>21534288</v>
       </c>
       <c r="W71" s="22" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="X71" s="25">
         <v>32294</v>
@@ -11739,7 +11722,7 @@
         <v>231</v>
       </c>
       <c r="AC71" s="22" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AD71" s="25">
         <v>33802</v>
@@ -11757,7 +11740,7 @@
         <v>40</v>
       </c>
       <c r="AI71" s="22" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AJ71" s="25">
         <v>34745</v>
@@ -11775,13 +11758,13 @@
         <v>231</v>
       </c>
       <c r="AO71" s="22" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AP71" s="23">
         <v>40277651</v>
       </c>
       <c r="AQ71" s="22" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AR71" s="23">
         <v>42532472</v>
@@ -11797,10 +11780,10 @@
         <v>46266.782002314816</v>
       </c>
       <c r="B72" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>739</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>740</v>
       </c>
       <c r="D72" s="8">
         <v>36997405</v>
@@ -11809,7 +11792,7 @@
         <v>34027</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>30</v>
@@ -11830,10 +11813,10 @@
         <v>34</v>
       </c>
       <c r="M72" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="N72" s="7" t="s">
         <v>742</v>
-      </c>
-      <c r="N72" s="7" t="s">
-        <v>743</v>
       </c>
       <c r="O72" s="10">
         <v>44561</v>
@@ -11851,7 +11834,7 @@
         <v>40</v>
       </c>
       <c r="T72" s="7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="U72" s="10">
         <v>29234</v>
@@ -11878,7 +11861,7 @@
       <c r="AM72" s="11"/>
       <c r="AN72" s="11"/>
       <c r="AO72" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AP72" s="8">
         <v>36997405</v>
@@ -11896,10 +11879,10 @@
         <v>46266.787592592591</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>747</v>
+        <v>882</v>
       </c>
       <c r="D73" s="23">
         <v>27180064</v>
@@ -11908,7 +11891,7 @@
         <v>28935</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G73" s="22" t="s">
         <v>30</v>
@@ -11923,7 +11906,7 @@
         <v>59</v>
       </c>
       <c r="K73" s="22" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="L73" s="22" t="s">
         <v>34</v>
@@ -11950,7 +11933,7 @@
         <v>37</v>
       </c>
       <c r="T73" s="22" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="U73" s="25">
         <v>28907</v>
@@ -11959,7 +11942,7 @@
         <v>27322108</v>
       </c>
       <c r="W73" s="22" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="X73" s="25">
         <v>37324</v>
@@ -11974,10 +11957,10 @@
         <v>40</v>
       </c>
       <c r="AB73" s="22" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="AC73" s="22" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="AD73" s="25">
         <v>41320</v>
@@ -12001,13 +11984,13 @@
       <c r="AM73" s="26"/>
       <c r="AN73" s="26"/>
       <c r="AO73" s="22" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="AP73" s="23">
         <v>27322108</v>
       </c>
       <c r="AQ73" s="22" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="AR73" s="23">
         <v>43647798</v>
@@ -12023,10 +12006,10 @@
         <v>46266.796875</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D74" s="8">
         <v>37903016</v>
@@ -12035,7 +12018,7 @@
         <v>34803</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>30</v>
@@ -12050,16 +12033,16 @@
         <v>32</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L74" s="7" t="s">
         <v>34</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N74" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O74" s="10">
         <v>44531</v>
@@ -12086,7 +12069,7 @@
         <v>0</v>
       </c>
       <c r="W74" s="7" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="X74" s="10">
         <v>42984</v>
@@ -12134,10 +12117,10 @@
         <v>46266.804722222223</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D75" s="23">
         <v>41654641</v>
@@ -12146,7 +12129,7 @@
         <v>36270</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G75" s="22" t="s">
         <v>30</v>
@@ -12167,7 +12150,7 @@
         <v>34</v>
       </c>
       <c r="M75" s="22" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N75" s="22" t="s">
         <v>272</v>
@@ -12188,7 +12171,7 @@
         <v>44</v>
       </c>
       <c r="T75" s="22" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="U75" s="25">
         <v>38043</v>
@@ -12197,7 +12180,7 @@
         <v>45508101</v>
       </c>
       <c r="W75" s="22" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="X75" s="25">
         <v>44210</v>
@@ -12211,7 +12194,7 @@
       <c r="AA75" s="26"/>
       <c r="AB75" s="26"/>
       <c r="AC75" s="22" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="AD75" s="25">
         <v>46189</v>
@@ -12229,19 +12212,19 @@
       <c r="AM75" s="26"/>
       <c r="AN75" s="26"/>
       <c r="AO75" s="22" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="AP75" s="23">
         <v>41654641</v>
       </c>
       <c r="AQ75" s="22" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AR75" s="23">
         <v>45508101</v>
       </c>
       <c r="AS75" s="22" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="AT75" s="23">
         <v>58328389</v>
@@ -12255,19 +12238,19 @@
         <v>46266.811111111114</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D76" s="8">
         <v>23255185</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>30</v>
@@ -12286,10 +12269,10 @@
         <v>231</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="N76" s="7" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="O76" s="10">
         <v>37960</v>
@@ -12307,7 +12290,7 @@
         <v>41</v>
       </c>
       <c r="T76" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="U76" s="10">
         <v>28626</v>
@@ -12316,7 +12299,7 @@
         <v>26590227</v>
       </c>
       <c r="W76" s="7" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="X76" s="10">
         <v>36711</v>
@@ -12332,7 +12315,7 @@
       </c>
       <c r="AB76" s="11"/>
       <c r="AC76" s="7" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="AD76" s="10">
         <v>37545</v>
@@ -12354,13 +12337,13 @@
       <c r="AM76" s="11"/>
       <c r="AN76" s="11"/>
       <c r="AO76" s="7" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AP76" s="8">
         <v>23255185</v>
       </c>
       <c r="AQ76" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="AR76" s="8">
         <v>26590227</v>
@@ -12376,10 +12359,10 @@
         <v>46266.812395833331</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D77" s="23">
         <v>27419925</v>
@@ -12388,13 +12371,13 @@
         <v>29076</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G77" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="I77" s="22" t="s">
         <v>63</v>
@@ -12403,16 +12386,16 @@
         <v>59</v>
       </c>
       <c r="K77" s="22" t="s">
+        <v>778</v>
+      </c>
+      <c r="L77" s="22" t="s">
+        <v>779</v>
+      </c>
+      <c r="M77" s="22" t="s">
         <v>780</v>
       </c>
-      <c r="L77" s="22" t="s">
+      <c r="N77" s="22" t="s">
         <v>781</v>
-      </c>
-      <c r="M77" s="22" t="s">
-        <v>782</v>
-      </c>
-      <c r="N77" s="22" t="s">
-        <v>783</v>
       </c>
       <c r="O77" s="25">
         <v>36101</v>
@@ -12430,7 +12413,7 @@
         <v>44</v>
       </c>
       <c r="T77" s="22" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="U77" s="25">
         <v>31613</v>
@@ -12439,7 +12422,7 @@
         <v>32348195</v>
       </c>
       <c r="W77" s="22" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="X77" s="25">
         <v>42087</v>
@@ -12457,7 +12440,7 @@
         <v>231</v>
       </c>
       <c r="AC77" s="22" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AD77" s="25">
         <v>44973</v>
@@ -12481,19 +12464,19 @@
       <c r="AM77" s="26"/>
       <c r="AN77" s="26"/>
       <c r="AO77" s="22" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AP77" s="23">
         <v>32348195</v>
       </c>
       <c r="AQ77" s="22" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AR77" s="23">
         <v>54615931</v>
       </c>
       <c r="AS77" s="22" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AT77" s="23">
         <v>59654188</v>
@@ -12507,19 +12490,19 @@
         <v>46266.867777777778</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D78" s="8">
         <v>29931700</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>30</v>
@@ -12543,7 +12526,7 @@
         <v>317</v>
       </c>
       <c r="N78" s="7" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="O78" s="10">
         <v>38853</v>
@@ -12564,7 +12547,7 @@
       <c r="U78" s="11"/>
       <c r="V78" s="11"/>
       <c r="W78" s="7" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="X78" s="10">
         <v>39932</v>
@@ -12579,10 +12562,10 @@
         <v>40</v>
       </c>
       <c r="AB78" s="7" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="AC78" s="7" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="AD78" s="10">
         <v>43980</v>
@@ -12602,13 +12585,13 @@
       <c r="AM78" s="11"/>
       <c r="AN78" s="11"/>
       <c r="AO78" s="7" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="AP78" s="8">
         <v>49448476</v>
       </c>
       <c r="AQ78" s="7" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="AR78" s="8">
         <v>58328238</v>
@@ -12624,10 +12607,10 @@
         <v>46266.874803240738</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D79" s="23">
         <v>21767045</v>
@@ -12636,7 +12619,7 @@
         <v>25967</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="G79" s="22" t="s">
         <v>96</v>
@@ -12652,19 +12635,19 @@
       </c>
       <c r="K79" s="26"/>
       <c r="L79" s="22" t="s">
+        <v>798</v>
+      </c>
+      <c r="M79" s="22" t="s">
+        <v>799</v>
+      </c>
+      <c r="N79" s="22" t="s">
         <v>800</v>
-      </c>
-      <c r="M79" s="22" t="s">
-        <v>801</v>
-      </c>
-      <c r="N79" s="22" t="s">
-        <v>802</v>
       </c>
       <c r="O79" s="25">
         <v>43800</v>
       </c>
       <c r="P79" s="22" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="Q79" s="23">
         <v>10</v>
@@ -12676,7 +12659,7 @@
         <v>41</v>
       </c>
       <c r="T79" s="22" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="U79" s="25">
         <v>25856</v>
@@ -12685,7 +12668,7 @@
         <v>21534233</v>
       </c>
       <c r="W79" s="22" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="X79" s="25">
         <v>37329</v>
@@ -12700,7 +12683,7 @@
         <v>40</v>
       </c>
       <c r="AB79" s="22" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="AC79" s="26"/>
       <c r="AD79" s="26"/>
@@ -12715,19 +12698,19 @@
       <c r="AM79" s="26"/>
       <c r="AN79" s="26"/>
       <c r="AO79" s="22" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="AP79" s="23">
         <v>21767045</v>
       </c>
       <c r="AQ79" s="22" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="AR79" s="23">
         <v>21534233</v>
       </c>
       <c r="AS79" s="22" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AT79" s="23">
         <v>43843221</v>
@@ -12741,10 +12724,10 @@
         <v>46266.874895833331</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D80" s="8">
         <v>25773967</v>
@@ -12753,7 +12736,7 @@
         <v>28292</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G80" s="7" t="s">
         <v>30</v>
@@ -12768,16 +12751,16 @@
         <v>83</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L80" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="N80" s="7" t="s">
         <v>813</v>
-      </c>
-      <c r="M80" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="N80" s="7" t="s">
-        <v>815</v>
       </c>
       <c r="O80" s="10">
         <v>43800</v>
@@ -12795,7 +12778,7 @@
         <v>42</v>
       </c>
       <c r="T80" s="7" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="U80" s="10">
         <v>29710</v>
@@ -12804,7 +12787,7 @@
         <v>28577899</v>
       </c>
       <c r="W80" s="7" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="X80" s="10">
         <v>38533</v>
@@ -12834,22 +12817,22 @@
       <c r="AM80" s="11"/>
       <c r="AN80" s="11"/>
       <c r="AO80" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AP80" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AQ80" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AR80" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AS80" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AT80" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AU80" s="28">
         <v>468</v>
@@ -12860,10 +12843,10 @@
         <v>46266.894270833334</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D81" s="23">
         <v>34408628</v>
@@ -12872,7 +12855,7 @@
         <v>32954</v>
       </c>
       <c r="F81" s="22" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="G81" s="22" t="s">
         <v>30</v>
@@ -12891,10 +12874,10 @@
         <v>231</v>
       </c>
       <c r="M81" s="22" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="N81" s="22" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="O81" s="25">
         <v>40182</v>
@@ -12912,7 +12895,7 @@
         <v>36</v>
       </c>
       <c r="T81" s="22" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="U81" s="25">
         <v>32954</v>
@@ -12921,7 +12904,7 @@
         <v>344408628</v>
       </c>
       <c r="W81" s="22" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="X81" s="25">
         <v>40149</v>
@@ -12937,7 +12920,7 @@
       </c>
       <c r="AB81" s="26"/>
       <c r="AC81" s="22" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AD81" s="25">
         <v>42385</v>
@@ -12951,7 +12934,7 @@
       <c r="AG81" s="26"/>
       <c r="AH81" s="26"/>
       <c r="AI81" s="22" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AJ81" s="25">
         <v>44985</v>
@@ -12965,19 +12948,19 @@
       <c r="AM81" s="26"/>
       <c r="AN81" s="26"/>
       <c r="AO81" s="22" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="AP81" s="23">
         <v>36174744</v>
       </c>
       <c r="AQ81" s="22" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AR81" s="23">
         <v>34408628</v>
       </c>
       <c r="AS81" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AT81" s="23">
         <v>49817219</v>
@@ -12991,10 +12974,10 @@
         <v>46266.911157407405</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D82" s="8">
         <v>30623004</v>
@@ -13003,7 +12986,7 @@
         <v>30612</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>30</v>
@@ -13019,13 +13002,13 @@
       </c>
       <c r="K82" s="11"/>
       <c r="L82" s="7" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="M82" s="7" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="N82" s="7" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="O82" s="10">
         <v>43800</v>
@@ -13064,10 +13047,10 @@
       <c r="AM82" s="11"/>
       <c r="AN82" s="11"/>
       <c r="AO82" s="7" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AP82" s="8" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="AQ82" s="11"/>
       <c r="AR82" s="11"/>
@@ -13082,19 +13065,19 @@
         <v>46266.911157407405</v>
       </c>
       <c r="B83" s="22" t="s">
+        <v>834</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>835</v>
+      </c>
+      <c r="D83" s="22" t="s">
         <v>836</v>
-      </c>
-      <c r="C83" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="D83" s="22" t="s">
-        <v>838</v>
       </c>
       <c r="E83" s="24">
         <v>32113</v>
       </c>
       <c r="F83" s="22" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G83" s="22" t="s">
         <v>30</v>
@@ -13109,7 +13092,7 @@
         <v>83</v>
       </c>
       <c r="K83" s="22" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L83" s="22" t="s">
         <v>34</v>
@@ -13118,7 +13101,7 @@
         <v>328</v>
       </c>
       <c r="N83" s="22" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="O83" s="25">
         <v>39203</v>
@@ -13157,10 +13140,10 @@
       <c r="AM83" s="26"/>
       <c r="AN83" s="26"/>
       <c r="AO83" s="22" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="AP83" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="AQ83" s="26"/>
       <c r="AR83" s="26"/>
@@ -13175,10 +13158,10 @@
         <v>46266.919317129628</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D84" s="8">
         <v>23255051</v>
@@ -13187,7 +13170,7 @@
         <v>26746</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>30</v>
@@ -13202,16 +13185,16 @@
         <v>32</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="L84" s="7" t="s">
         <v>231</v>
       </c>
       <c r="M84" s="7" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="N84" s="7" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="O84" s="10">
         <v>35644</v>
@@ -13229,7 +13212,7 @@
         <v>40</v>
       </c>
       <c r="T84" s="7" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="U84" s="10">
         <v>26908</v>
@@ -13238,7 +13221,7 @@
         <v>23556106</v>
       </c>
       <c r="W84" s="7" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="X84" s="10">
         <v>37390</v>
@@ -13253,10 +13236,10 @@
         <v>40</v>
       </c>
       <c r="AB84" s="7" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="AC84" s="7" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="AD84" s="10">
         <v>38574</v>
@@ -13278,19 +13261,19 @@
       <c r="AM84" s="11"/>
       <c r="AN84" s="11"/>
       <c r="AO84" s="7" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="AP84" s="8">
         <v>23556106</v>
       </c>
       <c r="AQ84" s="7" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="AR84" s="8">
         <v>43843249</v>
       </c>
       <c r="AS84" s="7" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="AT84" s="8">
         <v>46368000</v>
@@ -13304,19 +13287,19 @@
         <v>46266.930150462962</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D85" s="23">
         <v>27863231</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="F85" s="22" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G85" s="22" t="s">
         <v>30</v>
@@ -13335,10 +13318,10 @@
         <v>293</v>
       </c>
       <c r="M85" s="22" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="N85" s="22" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="O85" s="25">
         <v>37926</v>
@@ -13356,7 +13339,7 @@
         <v>40</v>
       </c>
       <c r="T85" s="22" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="U85" s="25">
         <v>31424</v>
@@ -13365,7 +13348,7 @@
         <v>31970849</v>
       </c>
       <c r="W85" s="22" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="X85" s="25">
         <v>39530</v>
@@ -13383,7 +13366,7 @@
         <v>40</v>
       </c>
       <c r="AC85" s="22" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="AD85" s="25">
         <v>38154</v>
@@ -13407,7 +13390,7 @@
       <c r="AM85" s="26"/>
       <c r="AN85" s="26"/>
       <c r="AO85" s="22" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="AP85" s="23">
         <v>27863231</v>
@@ -13425,10 +13408,10 @@
         <v>46266.940138888887</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D86" s="8">
         <v>24352357</v>
@@ -13437,13 +13420,13 @@
         <v>27565</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>31</v>
@@ -13452,16 +13435,16 @@
         <v>59</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="L86" s="7" t="s">
         <v>34</v>
       </c>
       <c r="M86" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N86" s="7" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="O86" s="10">
         <v>40544</v>
@@ -13479,7 +13462,7 @@
         <v>43</v>
       </c>
       <c r="T86" s="7" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="U86" s="10">
         <v>30449</v>
@@ -13488,7 +13471,7 @@
         <v>29931746</v>
       </c>
       <c r="W86" s="7" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="X86" s="10">
         <v>37504</v>
@@ -13503,10 +13486,10 @@
         <v>40</v>
       </c>
       <c r="AB86" s="7" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="AC86" s="7" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="AD86" s="10">
         <v>38390</v>
@@ -13521,10 +13504,10 @@
         <v>40</v>
       </c>
       <c r="AH86" s="7" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="AI86" s="7" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="AJ86" s="10">
         <v>40458</v>
@@ -13540,7 +13523,7 @@
       </c>
       <c r="AN86" s="11"/>
       <c r="AO86" s="7" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="AP86" s="8">
         <v>24362357</v>
@@ -13558,10 +13541,10 @@
         <v>46266.960023148145</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D87" s="14">
         <v>16879698</v>
@@ -13570,13 +13553,13 @@
         <v>23667</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>30</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>31</v>
@@ -13585,16 +13568,16 @@
         <v>32</v>
       </c>
       <c r="K87" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="L87" s="13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M87" s="13" t="s">
         <v>350</v>
       </c>
       <c r="N87" s="13" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="O87" s="16">
         <v>36528</v>
@@ -13612,7 +13595,7 @@
         <v>43</v>
       </c>
       <c r="T87" s="13" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="U87" s="16">
         <v>23373</v>
@@ -13621,7 +13604,7 @@
         <v>16628010</v>
       </c>
       <c r="W87" s="13" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="X87" s="16">
         <v>45020</v>
@@ -13636,7 +13619,7 @@
         <v>40</v>
       </c>
       <c r="AB87" s="13" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="AC87" s="17"/>
       <c r="AD87" s="17"/>
@@ -13651,7 +13634,7 @@
       <c r="AM87" s="17"/>
       <c r="AN87" s="17"/>
       <c r="AO87" s="13" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="AP87" s="14">
         <v>16628010</v>

--- a/declara.xlsx
+++ b/declara.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="1029">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -2663,6 +2663,444 @@
   </si>
   <si>
     <t>Cabrera Sergio ivan</t>
+  </si>
+  <si>
+    <t>jesicacorrea755@gmail.com</t>
+  </si>
+  <si>
+    <t>Correa jesica</t>
+  </si>
+  <si>
+    <t>Capelli S/n</t>
+  </si>
+  <si>
+    <t>Kl</t>
+  </si>
+  <si>
+    <t>Capo cristobal</t>
+  </si>
+  <si>
+    <t>Capo matias</t>
+  </si>
+  <si>
+    <t>Capo lara</t>
+  </si>
+  <si>
+    <t>Capo brisa</t>
+  </si>
+  <si>
+    <t>valee.1995.vs@gmail.com</t>
+  </si>
+  <si>
+    <t>Salomone Valeria Alejandra</t>
+  </si>
+  <si>
+    <t>Chacabuco 686</t>
+  </si>
+  <si>
+    <t>Inspectora de tránsito</t>
+  </si>
+  <si>
+    <t>Picco Nancy Magdalena</t>
+  </si>
+  <si>
+    <t>Salomone Daniel Fernando</t>
+  </si>
+  <si>
+    <t>alma.octavio.am@gmail.com</t>
+  </si>
+  <si>
+    <t>Miranda Andrea</t>
+  </si>
+  <si>
+    <t>Santa Rosa 25</t>
+  </si>
+  <si>
+    <t>Perito mercantil con especialización contable impositiva</t>
+  </si>
+  <si>
+    <t>Tribunal de faltas</t>
+  </si>
+  <si>
+    <t>S/M</t>
+  </si>
+  <si>
+    <t>36/38</t>
+  </si>
+  <si>
+    <t>Toro Miranda Alma</t>
+  </si>
+  <si>
+    <t>Toro Miranda Octavio</t>
+  </si>
+  <si>
+    <t>Octavio Toro Miranda</t>
+  </si>
+  <si>
+    <t>Alma Toro Miranda</t>
+  </si>
+  <si>
+    <t>gretafischer35@gmail.com</t>
+  </si>
+  <si>
+    <t>Fischer Greta</t>
+  </si>
+  <si>
+    <t>Moreno 1160</t>
+  </si>
+  <si>
+    <t>Diseño de interiores</t>
+  </si>
+  <si>
+    <t>Gerardo Salaberry</t>
+  </si>
+  <si>
+    <t>Salaberry Emma</t>
+  </si>
+  <si>
+    <t>Bassani Juan Francisco</t>
+  </si>
+  <si>
+    <t>Salaberry Valentina Emma</t>
+  </si>
+  <si>
+    <t>digitalizacionper@gmail.com</t>
+  </si>
+  <si>
+    <t>BUSTAMANTE PABLO NELSON</t>
+  </si>
+  <si>
+    <t>30.178.712</t>
+  </si>
+  <si>
+    <t>CHACABUCO 115</t>
+  </si>
+  <si>
+    <t>TITULO SECUNDARIO</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVO OF. DE PERSONAL</t>
+  </si>
+  <si>
+    <t>ARAUJO MERCEDES</t>
+  </si>
+  <si>
+    <t>18.081.796</t>
+  </si>
+  <si>
+    <t>micarochi1103@gmail.com</t>
+  </si>
+  <si>
+    <t>Zalazar Miryam</t>
+  </si>
+  <si>
+    <t>José ingenieros 355</t>
+  </si>
+  <si>
+    <t>Prifesora de Nivel inicial</t>
+  </si>
+  <si>
+    <t>Hogar de Dia</t>
+  </si>
+  <si>
+    <t>Gonzalez Fabricio</t>
+  </si>
+  <si>
+    <t>17/06/0077</t>
+  </si>
+  <si>
+    <t>Gonzalez Micaela</t>
+  </si>
+  <si>
+    <t>Cursando Bioquimica</t>
+  </si>
+  <si>
+    <t>Gonzalez Rocio</t>
+  </si>
+  <si>
+    <t>Medicina</t>
+  </si>
+  <si>
+    <t>Xx</t>
+  </si>
+  <si>
+    <t>1968inesperez@gmail.com</t>
+  </si>
+  <si>
+    <t>PEREZ INES</t>
+  </si>
+  <si>
+    <t>20.129.801</t>
+  </si>
+  <si>
+    <t>América 779</t>
+  </si>
+  <si>
+    <t>3382 571860</t>
+  </si>
+  <si>
+    <t>VAÑOS RAMON ROQUE</t>
+  </si>
+  <si>
+    <t>16.110.656</t>
+  </si>
+  <si>
+    <t>VAÑOS ANGEL CRUZ</t>
+  </si>
+  <si>
+    <t>43.819.797</t>
+  </si>
+  <si>
+    <t>En curso</t>
+  </si>
+  <si>
+    <t>VAÑOS ANGEL JUAN CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ DALMA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>34.591.773</t>
+  </si>
+  <si>
+    <t>moralesaldanaa15@gmail.com</t>
+  </si>
+  <si>
+    <t>Morales Aldana yamila</t>
+  </si>
+  <si>
+    <t>Colón 464</t>
+  </si>
+  <si>
+    <t>Moreno Facundo Ezequiel</t>
+  </si>
+  <si>
+    <t>Moreno Monserrat mia</t>
+  </si>
+  <si>
+    <t>raulimantay@gmail.com</t>
+  </si>
+  <si>
+    <t>Mantay raul</t>
+  </si>
+  <si>
+    <t>Rosabusy 895</t>
+  </si>
+  <si>
+    <t>Diaz mariana</t>
+  </si>
+  <si>
+    <t>Iturria olivia</t>
+  </si>
+  <si>
+    <t>Mariana diaz</t>
+  </si>
+  <si>
+    <t>Olivia iturria</t>
+  </si>
+  <si>
+    <t>mirandandrea972@gmail.com</t>
+  </si>
+  <si>
+    <t>Miranda Andrea Soledad</t>
+  </si>
+  <si>
+    <t>Domingo Ferrari 855</t>
+  </si>
+  <si>
+    <t>Rufino Santa Fe</t>
+  </si>
+  <si>
+    <t>Centro de Acción Faliliar</t>
+  </si>
+  <si>
+    <t>Soltera</t>
+  </si>
+  <si>
+    <t>Benjamin Pérez</t>
+  </si>
+  <si>
+    <t>Margarita Acevedo</t>
+  </si>
+  <si>
+    <t>carrizoolga50@gmail.com</t>
+  </si>
+  <si>
+    <t>Leandro Daniel Ferrari</t>
+  </si>
+  <si>
+    <t>Domingo Ferrari 1085</t>
+  </si>
+  <si>
+    <t>3382_449162</t>
+  </si>
+  <si>
+    <t>Migraña</t>
+  </si>
+  <si>
+    <t>Recolector voluminoso</t>
+  </si>
+  <si>
+    <t>Olga carrizo</t>
+  </si>
+  <si>
+    <t>maximiliano.mp6@gmail.com</t>
+  </si>
+  <si>
+    <t>Chacon maximiliano</t>
+  </si>
+  <si>
+    <t>Catamarca 1330</t>
+  </si>
+  <si>
+    <t>Voluminosos</t>
+  </si>
+  <si>
+    <t>fernandocellario55@gmail.com</t>
+  </si>
+  <si>
+    <t>Cellario fernando</t>
+  </si>
+  <si>
+    <t>Chacabuco 968</t>
+  </si>
+  <si>
+    <t>Rufino santa fe</t>
+  </si>
+  <si>
+    <t>Me faltan materias</t>
+  </si>
+  <si>
+    <t>Agrup. Mantenimiento y producción, operador de equipos pesados</t>
+  </si>
+  <si>
+    <t>Anabel Tali barinaga</t>
+  </si>
+  <si>
+    <t>diegojb265@gmail.com</t>
+  </si>
+  <si>
+    <t>Diego Javier Baretto</t>
+  </si>
+  <si>
+    <t>Ingeniero cutro 265</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Hipertension arterial</t>
+  </si>
+  <si>
+    <t>Jefe de oficina intendencia municipal</t>
+  </si>
+  <si>
+    <t>Marina lujan Sanchez</t>
+  </si>
+  <si>
+    <t>Baretto Luciano Enzo</t>
+  </si>
+  <si>
+    <t>Baretto Giuliano Matias</t>
+  </si>
+  <si>
+    <t>Xxxxx</t>
+  </si>
+  <si>
+    <t>Xxxx</t>
+  </si>
+  <si>
+    <t>Xxx</t>
+  </si>
+  <si>
+    <t>BENITO BIANCO 672</t>
+  </si>
+  <si>
+    <t>Inpeción</t>
+  </si>
+  <si>
+    <t>CONTROL DE SECUESTROS Y ENTREGAS DE MOTOS Y VEHICULOS CONTRO DEPOSITOS .MINI CIUDAD VIAL.CONTROL DE RODADOS DEL INPECTOR , KILOMETROS DE VEHICULOS</t>
+  </si>
+  <si>
+    <t>Perez cecilia Daniela</t>
+  </si>
+  <si>
+    <t>Murua yonatan Ezequiel</t>
+  </si>
+  <si>
+    <t>Daniel Alejandro Perez</t>
+  </si>
+  <si>
+    <t>carlosalcidesvalle@gmail.com</t>
+  </si>
+  <si>
+    <t>Valle Carlos</t>
+  </si>
+  <si>
+    <t>26.870.611</t>
+  </si>
+  <si>
+    <t>Forma 155</t>
+  </si>
+  <si>
+    <t>Trabajo varios</t>
+  </si>
+  <si>
+    <t>43ymedio</t>
+  </si>
+  <si>
+    <t>Carina cernada</t>
+  </si>
+  <si>
+    <t>Valle Agustín</t>
+  </si>
+  <si>
+    <t>Agustín valle</t>
+  </si>
+  <si>
+    <t>Renzo garcia</t>
+  </si>
+  <si>
+    <t>milancr744@gmail.com</t>
+  </si>
+  <si>
+    <t>Giraldez Hernán Maximiliano</t>
+  </si>
+  <si>
+    <t>Mercedes buccio 260</t>
+  </si>
+  <si>
+    <t>Plazas los colibríes</t>
+  </si>
+  <si>
+    <t>Obras Públicas</t>
+  </si>
+  <si>
+    <t>Ortega Eliana Candela</t>
+  </si>
+  <si>
+    <t>Giraldez Martines Thiago</t>
+  </si>
+  <si>
+    <t>Thiago Giraldez Martines</t>
+  </si>
+  <si>
+    <t>bengoleafran5@gmail.com</t>
+  </si>
+  <si>
+    <t>Bengolea Franco Ezequiel</t>
+  </si>
+  <si>
+    <t>Remedios de escalada 265</t>
+  </si>
+  <si>
+    <t>Ghian Franco Bengolea</t>
+  </si>
+  <si>
+    <t>Alessia Yetzali Bengolea</t>
+  </si>
+  <si>
+    <t>Micaela Belen Garcia</t>
   </si>
 </sst>
 </file>
@@ -2720,7 +3158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2968,11 +3406,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3078,6 +3561,30 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3374,7 +3881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AY105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -6728,7 +7235,7 @@
         <v>407</v>
       </c>
       <c r="U29" s="25">
-        <v>16053</v>
+        <v>15688</v>
       </c>
       <c r="V29" s="23">
         <v>6134509</v>
@@ -13647,8 +14154,1980 @@
         <v>170</v>
       </c>
     </row>
+    <row r="88" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A88" s="37">
+        <v>46267.319907407407</v>
+      </c>
+      <c r="B88" s="38" t="s">
+        <v>883</v>
+      </c>
+      <c r="C88" s="38" t="s">
+        <v>884</v>
+      </c>
+      <c r="D88" s="39">
+        <v>31905593</v>
+      </c>
+      <c r="E88" s="40">
+        <v>31402</v>
+      </c>
+      <c r="F88" s="38" t="s">
+        <v>885</v>
+      </c>
+      <c r="G88" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H88" s="39">
+        <v>3382508883</v>
+      </c>
+      <c r="I88" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="J88" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="K88" s="41"/>
+      <c r="L88" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="M88" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="N88" s="38" t="s">
+        <v>434</v>
+      </c>
+      <c r="O88" s="42">
+        <v>43800</v>
+      </c>
+      <c r="P88" s="38" t="s">
+        <v>886</v>
+      </c>
+      <c r="Q88" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="R88" s="39">
+        <v>48</v>
+      </c>
+      <c r="S88" s="39">
+        <v>39</v>
+      </c>
+      <c r="T88" s="38" t="s">
+        <v>887</v>
+      </c>
+      <c r="U88" s="42">
+        <v>30952</v>
+      </c>
+      <c r="V88" s="39">
+        <v>31035889</v>
+      </c>
+      <c r="W88" s="38" t="s">
+        <v>888</v>
+      </c>
+      <c r="X88" s="42">
+        <v>36990</v>
+      </c>
+      <c r="Y88" s="39">
+        <v>43284819</v>
+      </c>
+      <c r="Z88" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA88" s="41"/>
+      <c r="AB88" s="41"/>
+      <c r="AC88" s="38" t="s">
+        <v>889</v>
+      </c>
+      <c r="AD88" s="42">
+        <v>38036</v>
+      </c>
+      <c r="AE88" s="39">
+        <v>45493137</v>
+      </c>
+      <c r="AF88" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG88" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH88" s="38" t="s">
+        <v>500</v>
+      </c>
+      <c r="AI88" s="38" t="s">
+        <v>890</v>
+      </c>
+      <c r="AJ88" s="42">
+        <v>38762</v>
+      </c>
+      <c r="AK88" s="39">
+        <v>46998246</v>
+      </c>
+      <c r="AL88" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM88" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN88" s="38" t="s">
+        <v>500</v>
+      </c>
+      <c r="AO88" s="38" t="s">
+        <v>888</v>
+      </c>
+      <c r="AP88" s="39">
+        <v>43284819</v>
+      </c>
+      <c r="AQ88" s="38" t="s">
+        <v>890</v>
+      </c>
+      <c r="AR88" s="39">
+        <v>46998246</v>
+      </c>
+      <c r="AS88" s="38" t="s">
+        <v>889</v>
+      </c>
+      <c r="AT88" s="39">
+        <v>45493137</v>
+      </c>
+      <c r="AU88" s="43">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="89" spans="1:47" ht="39" thickBot="1">
+      <c r="A89" s="21">
+        <v>46267.322500000002</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>891</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="D89" s="23">
+        <v>37902957</v>
+      </c>
+      <c r="E89" s="24">
+        <v>34750</v>
+      </c>
+      <c r="F89" s="22" t="s">
+        <v>893</v>
+      </c>
+      <c r="G89" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H89" s="23">
+        <v>3382447170</v>
+      </c>
+      <c r="I89" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J89" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K89" s="26"/>
+      <c r="L89" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M89" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="N89" s="22" t="s">
+        <v>894</v>
+      </c>
+      <c r="O89" s="25">
+        <v>44531</v>
+      </c>
+      <c r="P89" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q89" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R89" s="23">
+        <v>50</v>
+      </c>
+      <c r="S89" s="23">
+        <v>37</v>
+      </c>
+      <c r="T89" s="26"/>
+      <c r="U89" s="26"/>
+      <c r="V89" s="26"/>
+      <c r="W89" s="26"/>
+      <c r="X89" s="26"/>
+      <c r="Y89" s="26"/>
+      <c r="Z89" s="26"/>
+      <c r="AA89" s="26"/>
+      <c r="AB89" s="26"/>
+      <c r="AC89" s="26"/>
+      <c r="AD89" s="26"/>
+      <c r="AE89" s="26"/>
+      <c r="AF89" s="26"/>
+      <c r="AG89" s="26"/>
+      <c r="AH89" s="26"/>
+      <c r="AI89" s="26"/>
+      <c r="AJ89" s="26"/>
+      <c r="AK89" s="26"/>
+      <c r="AL89" s="26"/>
+      <c r="AM89" s="26"/>
+      <c r="AN89" s="26"/>
+      <c r="AO89" s="22" t="s">
+        <v>895</v>
+      </c>
+      <c r="AP89" s="23">
+        <v>14934566</v>
+      </c>
+      <c r="AQ89" s="22" t="s">
+        <v>896</v>
+      </c>
+      <c r="AR89" s="23">
+        <v>16879655</v>
+      </c>
+      <c r="AS89" s="26"/>
+      <c r="AT89" s="26"/>
+      <c r="AU89" s="27">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="90" spans="1:47" ht="77.25" thickBot="1">
+      <c r="A90" s="6">
+        <v>46267.328703703701</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="D90" s="8">
+        <v>26318862</v>
+      </c>
+      <c r="E90" s="9">
+        <v>28492</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H90" s="8">
+        <v>3382576242</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="L90" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="M90" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="N90" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="O90" s="10">
+        <v>36101</v>
+      </c>
+      <c r="P90" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="Q90" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="R90" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="S90" s="8">
+        <v>39</v>
+      </c>
+      <c r="T90" s="11"/>
+      <c r="U90" s="11"/>
+      <c r="V90" s="11"/>
+      <c r="W90" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="X90" s="10">
+        <v>37692</v>
+      </c>
+      <c r="Y90" s="8">
+        <v>44773350</v>
+      </c>
+      <c r="Z90" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA90" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB90" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC90" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="AD90" s="10">
+        <v>39397</v>
+      </c>
+      <c r="AE90" s="8">
+        <v>47779544</v>
+      </c>
+      <c r="AF90" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG90" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH90" s="11"/>
+      <c r="AI90" s="11"/>
+      <c r="AJ90" s="11"/>
+      <c r="AK90" s="11"/>
+      <c r="AL90" s="11"/>
+      <c r="AM90" s="11"/>
+      <c r="AN90" s="11"/>
+      <c r="AO90" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="AP90" s="8">
+        <v>47779544</v>
+      </c>
+      <c r="AQ90" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="AR90" s="8">
+        <v>44773350</v>
+      </c>
+      <c r="AS90" s="11"/>
+      <c r="AT90" s="11"/>
+      <c r="AU90" s="29">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="1:47" ht="39" thickBot="1">
+      <c r="A91" s="21">
+        <v>46267.331782407404</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>908</v>
+      </c>
+      <c r="C91" s="22" t="s">
+        <v>909</v>
+      </c>
+      <c r="D91" s="23">
+        <v>26870693</v>
+      </c>
+      <c r="E91" s="24">
+        <v>28809</v>
+      </c>
+      <c r="F91" s="22" t="s">
+        <v>910</v>
+      </c>
+      <c r="G91" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H91" s="23">
+        <v>3382676481</v>
+      </c>
+      <c r="I91" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J91" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K91" s="22" t="s">
+        <v>911</v>
+      </c>
+      <c r="L91" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="M91" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="N91" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="O91" s="25">
+        <v>38477</v>
+      </c>
+      <c r="P91" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q91" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="R91" s="23">
+        <v>36</v>
+      </c>
+      <c r="S91" s="23">
+        <v>37</v>
+      </c>
+      <c r="T91" s="22" t="s">
+        <v>912</v>
+      </c>
+      <c r="U91" s="25">
+        <v>24667</v>
+      </c>
+      <c r="V91" s="23">
+        <v>17881776</v>
+      </c>
+      <c r="W91" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="X91" s="25">
+        <v>28809</v>
+      </c>
+      <c r="Y91" s="23">
+        <v>26870693</v>
+      </c>
+      <c r="Z91" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA91" s="26"/>
+      <c r="AB91" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC91" s="22" t="s">
+        <v>914</v>
+      </c>
+      <c r="AD91" s="25">
+        <v>37357</v>
+      </c>
+      <c r="AE91" s="23">
+        <v>43843231</v>
+      </c>
+      <c r="AF91" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG91" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH91" s="26"/>
+      <c r="AI91" s="26"/>
+      <c r="AJ91" s="26"/>
+      <c r="AK91" s="26"/>
+      <c r="AL91" s="26"/>
+      <c r="AM91" s="26"/>
+      <c r="AN91" s="26"/>
+      <c r="AO91" s="22" t="s">
+        <v>914</v>
+      </c>
+      <c r="AP91" s="23">
+        <v>43843231</v>
+      </c>
+      <c r="AQ91" s="22" t="s">
+        <v>915</v>
+      </c>
+      <c r="AR91" s="23">
+        <v>53777121</v>
+      </c>
+      <c r="AS91" s="26"/>
+      <c r="AT91" s="26"/>
+      <c r="AU91" s="27">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="92" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A92" s="6">
+        <v>46267.333715277775</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="E92" s="9">
+        <v>30455</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H92" s="8">
+        <v>3382677500</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K92" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="L92" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="M92" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="N92" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="O92" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P92" s="8">
+        <v>40</v>
+      </c>
+      <c r="Q92" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="R92" s="8">
+        <v>42</v>
+      </c>
+      <c r="S92" s="8">
+        <v>41</v>
+      </c>
+      <c r="T92" s="11"/>
+      <c r="U92" s="11"/>
+      <c r="V92" s="11"/>
+      <c r="W92" s="11"/>
+      <c r="X92" s="11"/>
+      <c r="Y92" s="11"/>
+      <c r="Z92" s="11"/>
+      <c r="AA92" s="11"/>
+      <c r="AB92" s="11"/>
+      <c r="AC92" s="11"/>
+      <c r="AD92" s="11"/>
+      <c r="AE92" s="11"/>
+      <c r="AF92" s="11"/>
+      <c r="AG92" s="11"/>
+      <c r="AH92" s="11"/>
+      <c r="AI92" s="11"/>
+      <c r="AJ92" s="11"/>
+      <c r="AK92" s="11"/>
+      <c r="AL92" s="11"/>
+      <c r="AM92" s="11"/>
+      <c r="AN92" s="11"/>
+      <c r="AO92" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="AP92" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="AQ92" s="11"/>
+      <c r="AR92" s="11"/>
+      <c r="AS92" s="11"/>
+      <c r="AT92" s="11"/>
+      <c r="AU92" s="28">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="93" spans="1:47" ht="39" thickBot="1">
+      <c r="A93" s="21">
+        <v>46267.345034722224</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>924</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>925</v>
+      </c>
+      <c r="D93" s="23">
+        <v>26207742</v>
+      </c>
+      <c r="E93" s="24">
+        <v>28551</v>
+      </c>
+      <c r="F93" s="22" t="s">
+        <v>926</v>
+      </c>
+      <c r="G93" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H93" s="23">
+        <v>3382677239</v>
+      </c>
+      <c r="I93" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J93" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K93" s="22" t="s">
+        <v>927</v>
+      </c>
+      <c r="L93" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M93" s="22" t="s">
+        <v>928</v>
+      </c>
+      <c r="N93" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="O93" s="25">
+        <v>37377</v>
+      </c>
+      <c r="P93" s="23">
+        <v>36</v>
+      </c>
+      <c r="Q93" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R93" s="23">
+        <v>42</v>
+      </c>
+      <c r="S93" s="23">
+        <v>36</v>
+      </c>
+      <c r="T93" s="22" t="s">
+        <v>929</v>
+      </c>
+      <c r="U93" s="23" t="s">
+        <v>930</v>
+      </c>
+      <c r="V93" s="23">
+        <v>25773990</v>
+      </c>
+      <c r="W93" s="22" t="s">
+        <v>931</v>
+      </c>
+      <c r="X93" s="25">
+        <v>38057</v>
+      </c>
+      <c r="Y93" s="23">
+        <v>45508086</v>
+      </c>
+      <c r="Z93" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA93" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB93" s="22" t="s">
+        <v>932</v>
+      </c>
+      <c r="AC93" s="22" t="s">
+        <v>933</v>
+      </c>
+      <c r="AD93" s="25">
+        <v>39365</v>
+      </c>
+      <c r="AE93" s="23">
+        <v>47779509</v>
+      </c>
+      <c r="AF93" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG93" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH93" s="22" t="s">
+        <v>934</v>
+      </c>
+      <c r="AI93" s="26"/>
+      <c r="AJ93" s="26"/>
+      <c r="AK93" s="26"/>
+      <c r="AL93" s="26"/>
+      <c r="AM93" s="26"/>
+      <c r="AN93" s="26"/>
+      <c r="AO93" s="22" t="s">
+        <v>935</v>
+      </c>
+      <c r="AP93" s="22" t="s">
+        <v>935</v>
+      </c>
+      <c r="AQ93" s="26"/>
+      <c r="AR93" s="26"/>
+      <c r="AS93" s="26"/>
+      <c r="AT93" s="26"/>
+      <c r="AU93" s="27">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="94" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A94" s="6">
+        <v>46267.351435185185</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>936</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>937</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="E94" s="9">
+        <v>24855</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>940</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="L94" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="M94" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="N94" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="O94" s="10">
+        <v>41804</v>
+      </c>
+      <c r="P94" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q94" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="R94" s="8">
+        <v>42</v>
+      </c>
+      <c r="S94" s="8">
+        <v>38</v>
+      </c>
+      <c r="T94" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="U94" s="10">
+        <v>22948</v>
+      </c>
+      <c r="V94" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="W94" s="7" t="s">
+        <v>943</v>
+      </c>
+      <c r="X94" s="10">
+        <v>37325</v>
+      </c>
+      <c r="Y94" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="Z94" s="11"/>
+      <c r="AA94" s="11"/>
+      <c r="AB94" s="7" t="s">
+        <v>945</v>
+      </c>
+      <c r="AC94" s="11"/>
+      <c r="AD94" s="11"/>
+      <c r="AE94" s="11"/>
+      <c r="AF94" s="11"/>
+      <c r="AG94" s="11"/>
+      <c r="AH94" s="11"/>
+      <c r="AI94" s="11"/>
+      <c r="AJ94" s="11"/>
+      <c r="AK94" s="11"/>
+      <c r="AL94" s="11"/>
+      <c r="AM94" s="11"/>
+      <c r="AN94" s="11"/>
+      <c r="AO94" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="AP94" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="AQ94" s="7" t="s">
+        <v>947</v>
+      </c>
+      <c r="AR94" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="AS94" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="AT94" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="AU94" s="28">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="95" spans="1:47" ht="39" thickBot="1">
+      <c r="A95" s="21">
+        <v>46267.368414351855</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>949</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>950</v>
+      </c>
+      <c r="D95" s="23">
+        <v>37902945</v>
+      </c>
+      <c r="E95" s="24">
+        <v>34745</v>
+      </c>
+      <c r="F95" s="22" t="s">
+        <v>951</v>
+      </c>
+      <c r="G95" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H95" s="23">
+        <v>3382480954</v>
+      </c>
+      <c r="I95" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J95" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K95" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="L95" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="M95" s="22" t="s">
+        <v>901</v>
+      </c>
+      <c r="N95" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="O95" s="25">
+        <v>44531</v>
+      </c>
+      <c r="P95" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q95" s="23">
+        <v>2</v>
+      </c>
+      <c r="R95" s="23">
+        <v>38</v>
+      </c>
+      <c r="S95" s="23">
+        <v>36</v>
+      </c>
+      <c r="T95" s="22" t="s">
+        <v>952</v>
+      </c>
+      <c r="U95" s="25">
+        <v>36519</v>
+      </c>
+      <c r="V95" s="23">
+        <v>41654843</v>
+      </c>
+      <c r="W95" s="22" t="s">
+        <v>953</v>
+      </c>
+      <c r="X95" s="25">
+        <v>43836</v>
+      </c>
+      <c r="Y95" s="23">
+        <v>57460994</v>
+      </c>
+      <c r="Z95" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA95" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB95" s="26"/>
+      <c r="AC95" s="26"/>
+      <c r="AD95" s="26"/>
+      <c r="AE95" s="26"/>
+      <c r="AF95" s="26"/>
+      <c r="AG95" s="26"/>
+      <c r="AH95" s="26"/>
+      <c r="AI95" s="26"/>
+      <c r="AJ95" s="26"/>
+      <c r="AK95" s="26"/>
+      <c r="AL95" s="26"/>
+      <c r="AM95" s="26"/>
+      <c r="AN95" s="26"/>
+      <c r="AO95" s="22" t="s">
+        <v>953</v>
+      </c>
+      <c r="AP95" s="23">
+        <v>57460994</v>
+      </c>
+      <c r="AQ95" s="26"/>
+      <c r="AR95" s="26"/>
+      <c r="AS95" s="26"/>
+      <c r="AT95" s="26"/>
+      <c r="AU95" s="27">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="96" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A96" s="6">
+        <v>46267.401921296296</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>955</v>
+      </c>
+      <c r="D96" s="8">
+        <v>30623205</v>
+      </c>
+      <c r="E96" s="9">
+        <v>30838</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H96" s="8">
+        <v>3382449200</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K96" s="11"/>
+      <c r="L96" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M96" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="N96" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="O96" s="10">
+        <v>38844</v>
+      </c>
+      <c r="P96" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q96" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="R96" s="8">
+        <v>42</v>
+      </c>
+      <c r="S96" s="8">
+        <v>41</v>
+      </c>
+      <c r="T96" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="U96" s="10">
+        <v>31450</v>
+      </c>
+      <c r="V96" s="8">
+        <v>32171175</v>
+      </c>
+      <c r="W96" s="7" t="s">
+        <v>958</v>
+      </c>
+      <c r="X96" s="10">
+        <v>42450</v>
+      </c>
+      <c r="Y96" s="8">
+        <v>55403727</v>
+      </c>
+      <c r="Z96" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA96" s="11"/>
+      <c r="AB96" s="11"/>
+      <c r="AC96" s="11"/>
+      <c r="AD96" s="11"/>
+      <c r="AE96" s="11"/>
+      <c r="AF96" s="11"/>
+      <c r="AG96" s="11"/>
+      <c r="AH96" s="11"/>
+      <c r="AI96" s="11"/>
+      <c r="AJ96" s="11"/>
+      <c r="AK96" s="11"/>
+      <c r="AL96" s="11"/>
+      <c r="AM96" s="11"/>
+      <c r="AN96" s="11"/>
+      <c r="AO96" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="AP96" s="8">
+        <v>32171135</v>
+      </c>
+      <c r="AQ96" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="AR96" s="8">
+        <v>55403727</v>
+      </c>
+      <c r="AS96" s="11"/>
+      <c r="AT96" s="11"/>
+      <c r="AU96" s="28">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="97" spans="1:47" ht="39" thickBot="1">
+      <c r="A97" s="21">
+        <v>46267.445509259262</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>961</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>962</v>
+      </c>
+      <c r="D97" s="23">
+        <v>37902967</v>
+      </c>
+      <c r="E97" s="24">
+        <v>34782</v>
+      </c>
+      <c r="F97" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="G97" s="22" t="s">
+        <v>964</v>
+      </c>
+      <c r="H97" s="23">
+        <v>3382505842</v>
+      </c>
+      <c r="I97" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J97" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K97" s="26"/>
+      <c r="L97" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="M97" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="N97" s="22" t="s">
+        <v>588</v>
+      </c>
+      <c r="O97" s="25">
+        <v>44896</v>
+      </c>
+      <c r="P97" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q97" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="R97" s="23">
+        <v>38</v>
+      </c>
+      <c r="S97" s="23">
+        <v>36</v>
+      </c>
+      <c r="T97" s="22" t="s">
+        <v>966</v>
+      </c>
+      <c r="U97" s="26"/>
+      <c r="V97" s="26"/>
+      <c r="W97" s="22" t="s">
+        <v>967</v>
+      </c>
+      <c r="X97" s="25">
+        <v>41433</v>
+      </c>
+      <c r="Y97" s="23">
+        <v>53269509</v>
+      </c>
+      <c r="Z97" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA97" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB97" s="26"/>
+      <c r="AC97" s="26"/>
+      <c r="AD97" s="26"/>
+      <c r="AE97" s="26"/>
+      <c r="AF97" s="26"/>
+      <c r="AG97" s="26"/>
+      <c r="AH97" s="26"/>
+      <c r="AI97" s="26"/>
+      <c r="AJ97" s="26"/>
+      <c r="AK97" s="26"/>
+      <c r="AL97" s="26"/>
+      <c r="AM97" s="26"/>
+      <c r="AN97" s="26"/>
+      <c r="AO97" s="22" t="s">
+        <v>968</v>
+      </c>
+      <c r="AP97" s="23">
+        <v>16615259</v>
+      </c>
+      <c r="AQ97" s="26"/>
+      <c r="AR97" s="26"/>
+      <c r="AS97" s="26"/>
+      <c r="AT97" s="26"/>
+      <c r="AU97" s="27">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="98" spans="1:47" ht="39" thickBot="1">
+      <c r="A98" s="6">
+        <v>46267.544548611113</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>969</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="D98" s="8">
+        <v>35250245</v>
+      </c>
+      <c r="E98" s="9">
+        <v>33154</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>972</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="M98" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="N98" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="O98" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P98" s="8">
+        <v>42</v>
+      </c>
+      <c r="Q98" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="R98" s="8">
+        <v>44</v>
+      </c>
+      <c r="S98" s="8">
+        <v>42</v>
+      </c>
+      <c r="T98" s="11"/>
+      <c r="U98" s="11"/>
+      <c r="V98" s="11"/>
+      <c r="W98" s="11"/>
+      <c r="X98" s="11"/>
+      <c r="Y98" s="11"/>
+      <c r="Z98" s="11"/>
+      <c r="AA98" s="11"/>
+      <c r="AB98" s="11"/>
+      <c r="AC98" s="11"/>
+      <c r="AD98" s="11"/>
+      <c r="AE98" s="11"/>
+      <c r="AF98" s="11"/>
+      <c r="AG98" s="11"/>
+      <c r="AH98" s="11"/>
+      <c r="AI98" s="11"/>
+      <c r="AJ98" s="11"/>
+      <c r="AK98" s="11"/>
+      <c r="AL98" s="11"/>
+      <c r="AM98" s="11"/>
+      <c r="AN98" s="11"/>
+      <c r="AO98" s="7" t="s">
+        <v>975</v>
+      </c>
+      <c r="AP98" s="8">
+        <v>20233218</v>
+      </c>
+      <c r="AQ98" s="11"/>
+      <c r="AR98" s="11"/>
+      <c r="AS98" s="11"/>
+      <c r="AT98" s="11"/>
+      <c r="AU98" s="28">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="99" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A99" s="21">
+        <v>46267.600081018521</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>976</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>977</v>
+      </c>
+      <c r="D99" s="23">
+        <v>40277764</v>
+      </c>
+      <c r="E99" s="24">
+        <v>35823</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>978</v>
+      </c>
+      <c r="G99" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="23">
+        <v>3382462643</v>
+      </c>
+      <c r="I99" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J99" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="L99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="M99" s="22" t="s">
+        <v>856</v>
+      </c>
+      <c r="N99" s="22" t="s">
+        <v>979</v>
+      </c>
+      <c r="O99" s="25">
+        <v>46267</v>
+      </c>
+      <c r="P99" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q99" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R99" s="23">
+        <v>40</v>
+      </c>
+      <c r="S99" s="23">
+        <v>41</v>
+      </c>
+      <c r="T99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="U99" s="26"/>
+      <c r="V99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="W99" s="26"/>
+      <c r="X99" s="26"/>
+      <c r="Y99" s="26"/>
+      <c r="Z99" s="26"/>
+      <c r="AA99" s="26"/>
+      <c r="AB99" s="26"/>
+      <c r="AC99" s="26"/>
+      <c r="AD99" s="26"/>
+      <c r="AE99" s="26"/>
+      <c r="AF99" s="26"/>
+      <c r="AG99" s="26"/>
+      <c r="AH99" s="26"/>
+      <c r="AI99" s="26"/>
+      <c r="AJ99" s="26"/>
+      <c r="AK99" s="26"/>
+      <c r="AL99" s="26"/>
+      <c r="AM99" s="26"/>
+      <c r="AN99" s="26"/>
+      <c r="AO99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="AP99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="AQ99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="AR99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="AS99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="AT99" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="AU99" s="27">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="100" spans="1:47" ht="90" thickBot="1">
+      <c r="A100" s="6">
+        <v>46267.633715277778</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>980</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>981</v>
+      </c>
+      <c r="D100" s="8">
+        <v>32195807</v>
+      </c>
+      <c r="E100" s="9">
+        <v>31552</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>983</v>
+      </c>
+      <c r="H100" s="8">
+        <v>3382579046</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K100" s="11"/>
+      <c r="L100" s="7" t="s">
+        <v>984</v>
+      </c>
+      <c r="M100" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="N100" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="O100" s="10">
+        <v>40575</v>
+      </c>
+      <c r="P100" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q100" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R100" s="8">
+        <v>42</v>
+      </c>
+      <c r="S100" s="8">
+        <v>39</v>
+      </c>
+      <c r="T100" s="11"/>
+      <c r="U100" s="11"/>
+      <c r="V100" s="11"/>
+      <c r="W100" s="11"/>
+      <c r="X100" s="11"/>
+      <c r="Y100" s="11"/>
+      <c r="Z100" s="11"/>
+      <c r="AA100" s="11"/>
+      <c r="AB100" s="11"/>
+      <c r="AC100" s="11"/>
+      <c r="AD100" s="11"/>
+      <c r="AE100" s="11"/>
+      <c r="AF100" s="11"/>
+      <c r="AG100" s="11"/>
+      <c r="AH100" s="11"/>
+      <c r="AI100" s="11"/>
+      <c r="AJ100" s="11"/>
+      <c r="AK100" s="11"/>
+      <c r="AL100" s="11"/>
+      <c r="AM100" s="11"/>
+      <c r="AN100" s="11"/>
+      <c r="AO100" s="7" t="s">
+        <v>986</v>
+      </c>
+      <c r="AP100" s="8">
+        <v>36997389</v>
+      </c>
+      <c r="AQ100" s="11"/>
+      <c r="AR100" s="11"/>
+      <c r="AS100" s="11"/>
+      <c r="AT100" s="11"/>
+      <c r="AU100" s="28">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="101" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A101" s="21">
+        <v>46267.693356481483</v>
+      </c>
+      <c r="B101" s="22" t="s">
+        <v>987</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>988</v>
+      </c>
+      <c r="D101" s="23">
+        <v>24918176</v>
+      </c>
+      <c r="E101" s="25">
+        <v>27848</v>
+      </c>
+      <c r="F101" s="22" t="s">
+        <v>989</v>
+      </c>
+      <c r="G101" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H101" s="23">
+        <v>406517</v>
+      </c>
+      <c r="I101" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J101" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K101" s="22" t="s">
+        <v>990</v>
+      </c>
+      <c r="L101" s="22" t="s">
+        <v>991</v>
+      </c>
+      <c r="M101" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="N101" s="22" t="s">
+        <v>992</v>
+      </c>
+      <c r="O101" s="25">
+        <v>36395</v>
+      </c>
+      <c r="P101" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q101" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="R101" s="23">
+        <v>48</v>
+      </c>
+      <c r="S101" s="23">
+        <v>43</v>
+      </c>
+      <c r="T101" s="22" t="s">
+        <v>993</v>
+      </c>
+      <c r="U101" s="25">
+        <v>28571</v>
+      </c>
+      <c r="V101" s="23">
+        <v>26318956</v>
+      </c>
+      <c r="W101" s="22" t="s">
+        <v>994</v>
+      </c>
+      <c r="X101" s="25">
+        <v>40819</v>
+      </c>
+      <c r="Y101" s="23">
+        <v>51356911</v>
+      </c>
+      <c r="Z101" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA101" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB101" s="26"/>
+      <c r="AC101" s="22" t="s">
+        <v>995</v>
+      </c>
+      <c r="AD101" s="25">
+        <v>43335</v>
+      </c>
+      <c r="AE101" s="23">
+        <v>56965095</v>
+      </c>
+      <c r="AF101" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG101" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="AH101" s="26"/>
+      <c r="AI101" s="26"/>
+      <c r="AJ101" s="26"/>
+      <c r="AK101" s="26"/>
+      <c r="AL101" s="26"/>
+      <c r="AM101" s="26"/>
+      <c r="AN101" s="26"/>
+      <c r="AO101" s="22" t="s">
+        <v>996</v>
+      </c>
+      <c r="AP101" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="AQ101" s="22" t="s">
+        <v>997</v>
+      </c>
+      <c r="AR101" s="22" t="s">
+        <v>998</v>
+      </c>
+      <c r="AS101" s="26"/>
+      <c r="AT101" s="26"/>
+      <c r="AU101" s="27">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="102" spans="1:47" ht="268.5" thickBot="1">
+      <c r="A102" s="6">
+        <v>46267.85565972222</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>795</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="D102" s="8">
+        <v>21767045</v>
+      </c>
+      <c r="E102" s="9">
+        <v>25967</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>999</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H102" s="8">
+        <v>3382412350</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K102" s="11"/>
+      <c r="L102" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="M102" s="7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N102" s="7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="O102" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P102" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>10</v>
+      </c>
+      <c r="R102" s="8">
+        <v>60</v>
+      </c>
+      <c r="S102" s="8">
+        <v>41</v>
+      </c>
+      <c r="T102" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="U102" s="10">
+        <v>25856</v>
+      </c>
+      <c r="V102" s="8">
+        <v>21534233</v>
+      </c>
+      <c r="W102" s="11"/>
+      <c r="X102" s="11"/>
+      <c r="Y102" s="11"/>
+      <c r="Z102" s="11"/>
+      <c r="AA102" s="11"/>
+      <c r="AB102" s="11"/>
+      <c r="AC102" s="11"/>
+      <c r="AD102" s="11"/>
+      <c r="AE102" s="11"/>
+      <c r="AF102" s="11"/>
+      <c r="AG102" s="11"/>
+      <c r="AH102" s="11"/>
+      <c r="AI102" s="11"/>
+      <c r="AJ102" s="11"/>
+      <c r="AK102" s="11"/>
+      <c r="AL102" s="11"/>
+      <c r="AM102" s="11"/>
+      <c r="AN102" s="11"/>
+      <c r="AO102" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AP102" s="8">
+        <v>43843221</v>
+      </c>
+      <c r="AQ102" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="AR102" s="8">
+        <v>37902726</v>
+      </c>
+      <c r="AS102" s="7" t="s">
+        <v>1004</v>
+      </c>
+      <c r="AT102" s="8">
+        <v>42127983</v>
+      </c>
+      <c r="AU102" s="28">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="103" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A103" s="21">
+        <v>46267.866631944446</v>
+      </c>
+      <c r="B103" s="22" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C103" s="22" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D103" s="23" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E103" s="24">
+        <v>28718</v>
+      </c>
+      <c r="F103" s="22" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G103" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H103" s="23">
+        <v>3382670588</v>
+      </c>
+      <c r="I103" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J103" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K103" s="26"/>
+      <c r="L103" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="M103" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="N103" s="22" t="s">
+        <v>1009</v>
+      </c>
+      <c r="O103" s="25">
+        <v>36535</v>
+      </c>
+      <c r="P103" s="23">
+        <v>60</v>
+      </c>
+      <c r="Q103" s="44">
+        <v>46304</v>
+      </c>
+      <c r="R103" s="23">
+        <v>58</v>
+      </c>
+      <c r="S103" s="22" t="s">
+        <v>1010</v>
+      </c>
+      <c r="T103" s="22" t="s">
+        <v>1011</v>
+      </c>
+      <c r="U103" s="25">
+        <v>27155</v>
+      </c>
+      <c r="V103" s="23">
+        <v>23667798</v>
+      </c>
+      <c r="W103" s="22" t="s">
+        <v>1012</v>
+      </c>
+      <c r="X103" s="25">
+        <v>36347</v>
+      </c>
+      <c r="Y103" s="23">
+        <v>41654681</v>
+      </c>
+      <c r="Z103" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA103" s="26"/>
+      <c r="AB103" s="26"/>
+      <c r="AC103" s="26"/>
+      <c r="AD103" s="26"/>
+      <c r="AE103" s="26"/>
+      <c r="AF103" s="26"/>
+      <c r="AG103" s="26"/>
+      <c r="AH103" s="26"/>
+      <c r="AI103" s="26"/>
+      <c r="AJ103" s="26"/>
+      <c r="AK103" s="26"/>
+      <c r="AL103" s="26"/>
+      <c r="AM103" s="26"/>
+      <c r="AN103" s="26"/>
+      <c r="AO103" s="22" t="s">
+        <v>1011</v>
+      </c>
+      <c r="AP103" s="23">
+        <v>23667798</v>
+      </c>
+      <c r="AQ103" s="22" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AR103" s="23">
+        <v>41654681</v>
+      </c>
+      <c r="AS103" s="22" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AT103" s="23">
+        <v>37902946</v>
+      </c>
+      <c r="AU103" s="27">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="104" spans="1:47" ht="39" thickBot="1">
+      <c r="A104" s="6">
+        <v>46267.902268518519</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D104" s="8">
+        <v>37295744</v>
+      </c>
+      <c r="E104" s="9">
+        <v>34379</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H104" s="8">
+        <v>3382506150</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K104" s="11"/>
+      <c r="L104" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M104" s="7" t="s">
+        <v>1018</v>
+      </c>
+      <c r="N104" s="7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="O104" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P104" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q104" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="R104" s="8">
+        <v>40</v>
+      </c>
+      <c r="S104" s="8">
+        <v>40</v>
+      </c>
+      <c r="T104" s="7" t="s">
+        <v>1020</v>
+      </c>
+      <c r="U104" s="10">
+        <v>36667</v>
+      </c>
+      <c r="V104" s="8">
+        <v>42127944</v>
+      </c>
+      <c r="W104" s="7" t="s">
+        <v>1021</v>
+      </c>
+      <c r="X104" s="10">
+        <v>41396</v>
+      </c>
+      <c r="Y104" s="8">
+        <v>53180910</v>
+      </c>
+      <c r="Z104" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA104" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB104" s="11"/>
+      <c r="AC104" s="11"/>
+      <c r="AD104" s="11"/>
+      <c r="AE104" s="11"/>
+      <c r="AF104" s="11"/>
+      <c r="AG104" s="11"/>
+      <c r="AH104" s="11"/>
+      <c r="AI104" s="11"/>
+      <c r="AJ104" s="11"/>
+      <c r="AK104" s="11"/>
+      <c r="AL104" s="11"/>
+      <c r="AM104" s="11"/>
+      <c r="AN104" s="11"/>
+      <c r="AO104" s="7" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AP104" s="8">
+        <v>53180910</v>
+      </c>
+      <c r="AQ104" s="11"/>
+      <c r="AR104" s="11"/>
+      <c r="AS104" s="11"/>
+      <c r="AT104" s="11"/>
+      <c r="AU104" s="28">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="105" spans="1:47" ht="39" thickBot="1">
+      <c r="A105" s="12">
+        <v>46268.024733796294</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D105" s="14">
+        <v>34175564</v>
+      </c>
+      <c r="E105" s="15">
+        <v>32752</v>
+      </c>
+      <c r="F105" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G105" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H105" s="14">
+        <v>3382406506</v>
+      </c>
+      <c r="I105" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J105" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="K105" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="L105" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="M105" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="N105" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="O105" s="16">
+        <v>44531</v>
+      </c>
+      <c r="P105" s="14">
+        <v>44</v>
+      </c>
+      <c r="Q105" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="R105" s="14">
+        <v>50</v>
+      </c>
+      <c r="S105" s="14">
+        <v>45</v>
+      </c>
+      <c r="T105" s="17"/>
+      <c r="U105" s="17"/>
+      <c r="V105" s="17"/>
+      <c r="W105" s="13" t="s">
+        <v>1026</v>
+      </c>
+      <c r="X105" s="16">
+        <v>42619</v>
+      </c>
+      <c r="Y105" s="14">
+        <v>55798119</v>
+      </c>
+      <c r="Z105" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA105" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB105" s="17"/>
+      <c r="AC105" s="13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AD105" s="16">
+        <v>44590</v>
+      </c>
+      <c r="AE105" s="14">
+        <v>59103651</v>
+      </c>
+      <c r="AF105" s="17"/>
+      <c r="AG105" s="17"/>
+      <c r="AH105" s="17"/>
+      <c r="AI105" s="17"/>
+      <c r="AJ105" s="17"/>
+      <c r="AK105" s="17"/>
+      <c r="AL105" s="17"/>
+      <c r="AM105" s="17"/>
+      <c r="AN105" s="17"/>
+      <c r="AO105" s="13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AP105" s="14">
+        <v>39049433</v>
+      </c>
+      <c r="AQ105" s="17"/>
+      <c r="AR105" s="17"/>
+      <c r="AS105" s="17"/>
+      <c r="AT105" s="17"/>
+      <c r="AU105" s="18">
+        <v>512</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/declara.xlsx
+++ b/declara.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="1147">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -3212,6 +3212,249 @@
   </si>
   <si>
     <t>Marcelo Quiñones</t>
+  </si>
+  <si>
+    <t>danielamoya007@gmail.com</t>
+  </si>
+  <si>
+    <t>Moya Daniela Marina</t>
+  </si>
+  <si>
+    <t>1° de mayo 140</t>
+  </si>
+  <si>
+    <t>3382-671327</t>
+  </si>
+  <si>
+    <t>Asma, Hipotiroidismo, Obesidad morbida</t>
+  </si>
+  <si>
+    <t>Administrativa y secretaria de la Junta Evaluadora de Discapacidad</t>
+  </si>
+  <si>
+    <t>Moya Agüero Priscila Luna</t>
+  </si>
+  <si>
+    <t>Abogada</t>
+  </si>
+  <si>
+    <t>Agüero Moya Didier Andres</t>
+  </si>
+  <si>
+    <t>Secundaria de formación técnica</t>
+  </si>
+  <si>
+    <t>Moya Agüero Alma Daphne (nieta)</t>
+  </si>
+  <si>
+    <t>zolezzipablo@gmail.com</t>
+  </si>
+  <si>
+    <t>Perez valeria</t>
+  </si>
+  <si>
+    <t>F. Garin 645</t>
+  </si>
+  <si>
+    <t>3382-572380</t>
+  </si>
+  <si>
+    <t>Perito mercantil</t>
+  </si>
+  <si>
+    <t>Inspección general</t>
+  </si>
+  <si>
+    <t>Pablo Martin Zolezzi</t>
+  </si>
+  <si>
+    <t>Zolezzi Perez Alina</t>
+  </si>
+  <si>
+    <t>Alejo Zolezzi Perez</t>
+  </si>
+  <si>
+    <t>rosana.marina81@gmail.com</t>
+  </si>
+  <si>
+    <t>Robledo Rosana Marina</t>
+  </si>
+  <si>
+    <t>F.N. Laprida 830</t>
+  </si>
+  <si>
+    <t>Terminal- Punto Digital</t>
+  </si>
+  <si>
+    <t>Maestranza - Atención al público</t>
+  </si>
+  <si>
+    <t>Jorge Sosa</t>
+  </si>
+  <si>
+    <t>Sosa Ignacio - Lina Sosa ( hija)</t>
+  </si>
+  <si>
+    <t>Sosa Guadalupe</t>
+  </si>
+  <si>
+    <t>Enfermería</t>
+  </si>
+  <si>
+    <t>Sosa Luciano</t>
+  </si>
+  <si>
+    <t>Ignacio Sosa - Lina Sosa (hija)</t>
+  </si>
+  <si>
+    <t>rosaby80@gmail.com</t>
+  </si>
+  <si>
+    <t>Ojeda Rosana</t>
+  </si>
+  <si>
+    <t>Remedios de Escalada 620</t>
+  </si>
+  <si>
+    <t>Titulo nivel medio 5to año</t>
+  </si>
+  <si>
+    <t>Mesa de Entradas</t>
+  </si>
+  <si>
+    <t>Jefe de Mesa de Entradas</t>
+  </si>
+  <si>
+    <t>Chaves Rocio lumila</t>
+  </si>
+  <si>
+    <t>Terminando carrera de contador</t>
+  </si>
+  <si>
+    <t>Chaves Abby Yazmin</t>
+  </si>
+  <si>
+    <t>Bernabé Ferreyra 1105</t>
+  </si>
+  <si>
+    <t>Manstranza</t>
+  </si>
+  <si>
+    <t>Brenda gimena lietzmann</t>
+  </si>
+  <si>
+    <t>ferreyramicaela648@gmail.com</t>
+  </si>
+  <si>
+    <t>Valdez mabel</t>
+  </si>
+  <si>
+    <t>Victorero 971</t>
+  </si>
+  <si>
+    <t>3382 460533</t>
+  </si>
+  <si>
+    <t>Mantenimiento de espacios verde</t>
+  </si>
+  <si>
+    <t>Hector ferreyra</t>
+  </si>
+  <si>
+    <t>Micaela yolanda ferreyra</t>
+  </si>
+  <si>
+    <t>Nicolas alberto ferreyra</t>
+  </si>
+  <si>
+    <t>Ramiro nahuel ferreyra</t>
+  </si>
+  <si>
+    <t>molinasergiodaniel44@gmail.com</t>
+  </si>
+  <si>
+    <t>Molina, Sergio Daniel</t>
+  </si>
+  <si>
+    <t>Santa Rosa 341</t>
+  </si>
+  <si>
+    <t>Predio Ferrocarril</t>
+  </si>
+  <si>
+    <t>Patricia Beatriz Viglianco</t>
+  </si>
+  <si>
+    <t>Lázaro Sergio Paul Molina</t>
+  </si>
+  <si>
+    <t>Patricia Viglianco</t>
+  </si>
+  <si>
+    <t>vivibarraza123@gmail.com</t>
+  </si>
+  <si>
+    <t>Barraza Viviana</t>
+  </si>
+  <si>
+    <t>Pte Peron 719</t>
+  </si>
+  <si>
+    <t>3382 410799</t>
+  </si>
+  <si>
+    <t>Asistente Social</t>
+  </si>
+  <si>
+    <t>Desarrollo Social</t>
+  </si>
+  <si>
+    <t>Mauricio Carroll</t>
+  </si>
+  <si>
+    <t>Carroll Brenda</t>
+  </si>
+  <si>
+    <t>Estudiante</t>
+  </si>
+  <si>
+    <t>Erika Carroll</t>
+  </si>
+  <si>
+    <t>Oscar Barraza</t>
+  </si>
+  <si>
+    <t>6.140.116</t>
+  </si>
+  <si>
+    <t>Brenda Carroll</t>
+  </si>
+  <si>
+    <t>gianoliosilviocarlos@gmail.com</t>
+  </si>
+  <si>
+    <t>Gianolio Silvio Carlos</t>
+  </si>
+  <si>
+    <t>General Paz 70</t>
+  </si>
+  <si>
+    <t>Auxiliar tecnico administracion empresas</t>
+  </si>
+  <si>
+    <t>Oficina catastro</t>
+  </si>
+  <si>
+    <t>Valeria Jaquelina Rosano</t>
+  </si>
+  <si>
+    <t>Gianolio Facundo Carlos</t>
+  </si>
+  <si>
+    <t>Catalina Gianolio</t>
+  </si>
+  <si>
+    <t>Facundo Carlos Gianolio</t>
   </si>
 </sst>
 </file>
@@ -4043,7 +4286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -16754,6 +16997,1286 @@
         <v>267</v>
       </c>
     </row>
+    <row r="110" spans="1:47" ht="102.75" thickBot="1">
+      <c r="A110" s="37">
+        <v>46269.356238425928</v>
+      </c>
+      <c r="B110" s="38" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C110" s="38" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D110" s="39">
+        <v>22797159</v>
+      </c>
+      <c r="E110" s="40">
+        <v>26618</v>
+      </c>
+      <c r="F110" s="38" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G110" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H110" s="38" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I110" s="38" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J110" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="K110" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="L110" s="38" t="s">
+        <v>1070</v>
+      </c>
+      <c r="M110" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="N110" s="38" t="s">
+        <v>1071</v>
+      </c>
+      <c r="O110" s="42">
+        <v>38450</v>
+      </c>
+      <c r="P110" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q110" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="R110" s="39">
+        <v>50</v>
+      </c>
+      <c r="S110" s="39">
+        <v>40</v>
+      </c>
+      <c r="T110" s="41"/>
+      <c r="U110" s="41"/>
+      <c r="V110" s="41"/>
+      <c r="W110" s="38" t="s">
+        <v>1072</v>
+      </c>
+      <c r="X110" s="42">
+        <v>35662</v>
+      </c>
+      <c r="Y110" s="39">
+        <v>40277591</v>
+      </c>
+      <c r="Z110" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA110" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB110" s="38" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AC110" s="38" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AD110" s="42">
+        <v>38995</v>
+      </c>
+      <c r="AE110" s="39">
+        <v>47329419</v>
+      </c>
+      <c r="AF110" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG110" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH110" s="38" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AI110" s="38" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AJ110" s="42">
+        <v>44952</v>
+      </c>
+      <c r="AK110" s="39">
+        <v>59654163</v>
+      </c>
+      <c r="AL110" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="AM110" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN110" s="41"/>
+      <c r="AO110" s="38" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AP110" s="39">
+        <v>40277591</v>
+      </c>
+      <c r="AQ110" s="38" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AR110" s="39">
+        <v>47329419</v>
+      </c>
+      <c r="AS110" s="41"/>
+      <c r="AT110" s="41"/>
+      <c r="AU110" s="43">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="111" spans="1:47" ht="39" thickBot="1">
+      <c r="A111" s="21">
+        <v>46269.427708333336</v>
+      </c>
+      <c r="B111" s="22" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C111" s="22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D111" s="23">
+        <v>31116949</v>
+      </c>
+      <c r="E111" s="24">
+        <v>31085</v>
+      </c>
+      <c r="F111" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G111" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H111" s="22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I111" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J111" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K111" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M111" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N111" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="O111" s="25">
+        <v>38412</v>
+      </c>
+      <c r="P111" s="23">
+        <v>48</v>
+      </c>
+      <c r="Q111" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R111" s="23">
+        <v>50</v>
+      </c>
+      <c r="S111" s="23">
+        <v>40</v>
+      </c>
+      <c r="T111" s="22" t="s">
+        <v>1083</v>
+      </c>
+      <c r="U111" s="25">
+        <v>29776</v>
+      </c>
+      <c r="V111" s="23">
+        <v>28572997</v>
+      </c>
+      <c r="W111" s="22" t="s">
+        <v>1084</v>
+      </c>
+      <c r="X111" s="25">
+        <v>40646</v>
+      </c>
+      <c r="Y111" s="23">
+        <v>50923407</v>
+      </c>
+      <c r="Z111" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA111" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC111" s="22" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AD111" s="25">
+        <v>41926</v>
+      </c>
+      <c r="AE111" s="23">
+        <v>54202483</v>
+      </c>
+      <c r="AF111" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI111" s="26"/>
+      <c r="AJ111" s="26"/>
+      <c r="AK111" s="26"/>
+      <c r="AL111" s="26"/>
+      <c r="AM111" s="26"/>
+      <c r="AN111" s="26"/>
+      <c r="AO111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AQ111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AR111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AS111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AT111" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AU111" s="27">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="112" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A112" s="6">
+        <v>46269.740752314814</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D112" s="8">
+        <v>27865190</v>
+      </c>
+      <c r="E112" s="9">
+        <v>29722</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H112" s="8">
+        <v>3382676882</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K112" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="L112" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M112" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="N112" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="O112" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P112" s="8">
+        <v>40</v>
+      </c>
+      <c r="Q112" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R112" s="8">
+        <v>44</v>
+      </c>
+      <c r="S112" s="8">
+        <v>38</v>
+      </c>
+      <c r="T112" s="7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="U112" s="10">
+        <v>29720</v>
+      </c>
+      <c r="V112" s="8">
+        <v>28301047</v>
+      </c>
+      <c r="W112" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="X112" s="10">
+        <v>36349</v>
+      </c>
+      <c r="Y112" s="8">
+        <v>41654702</v>
+      </c>
+      <c r="Z112" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA112" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB112" s="11"/>
+      <c r="AC112" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AD112" s="10">
+        <v>36732</v>
+      </c>
+      <c r="AE112" s="8">
+        <v>42127997</v>
+      </c>
+      <c r="AF112" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG112" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH112" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AI112" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AJ112" s="10">
+        <v>38056</v>
+      </c>
+      <c r="AK112" s="8">
+        <v>45508102</v>
+      </c>
+      <c r="AL112" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM112" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN112" s="11"/>
+      <c r="AO112" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AP112" s="8">
+        <v>41654702</v>
+      </c>
+      <c r="AQ112" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AR112" s="8">
+        <v>42127997</v>
+      </c>
+      <c r="AS112" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AT112" s="8">
+        <v>45508102</v>
+      </c>
+      <c r="AU112" s="28">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="113" spans="1:47" ht="39" thickBot="1">
+      <c r="A113" s="21">
+        <v>46271.867939814816</v>
+      </c>
+      <c r="B113" s="22" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D113" s="23">
+        <v>21416800</v>
+      </c>
+      <c r="E113" s="24">
+        <v>25619</v>
+      </c>
+      <c r="F113" s="22" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G113" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H113" s="23">
+        <v>3382458324</v>
+      </c>
+      <c r="I113" s="22" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J113" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K113" s="22" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L113" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M113" s="22" t="s">
+        <v>1101</v>
+      </c>
+      <c r="N113" s="22" t="s">
+        <v>1102</v>
+      </c>
+      <c r="O113" s="25">
+        <v>34578</v>
+      </c>
+      <c r="P113" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q113" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R113" s="23">
+        <v>40</v>
+      </c>
+      <c r="S113" s="23">
+        <v>38</v>
+      </c>
+      <c r="T113" s="26"/>
+      <c r="U113" s="26"/>
+      <c r="V113" s="26"/>
+      <c r="W113" s="22" t="s">
+        <v>1103</v>
+      </c>
+      <c r="X113" s="25">
+        <v>36453</v>
+      </c>
+      <c r="Y113" s="23">
+        <v>41654791</v>
+      </c>
+      <c r="Z113" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA113" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB113" s="22" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AC113" s="22" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AD113" s="25">
+        <v>41191</v>
+      </c>
+      <c r="AE113" s="23">
+        <v>52633659</v>
+      </c>
+      <c r="AF113" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG113" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH113" s="26"/>
+      <c r="AI113" s="26"/>
+      <c r="AJ113" s="26"/>
+      <c r="AK113" s="26"/>
+      <c r="AL113" s="26"/>
+      <c r="AM113" s="26"/>
+      <c r="AN113" s="26"/>
+      <c r="AO113" s="22" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AP113" s="23">
+        <v>41654791</v>
+      </c>
+      <c r="AQ113" s="22" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AR113" s="23">
+        <v>52633659</v>
+      </c>
+      <c r="AS113" s="26"/>
+      <c r="AT113" s="26"/>
+      <c r="AU113" s="27">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:47" ht="39" thickBot="1">
+      <c r="A114" s="6">
+        <v>46272.572465277779</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D114" s="8">
+        <v>27060256</v>
+      </c>
+      <c r="E114" s="9">
+        <v>28858</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H114" s="8">
+        <v>3382460661</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M114" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="N114" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="O114" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P114" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q114" s="8">
+        <v>3</v>
+      </c>
+      <c r="R114" s="8">
+        <v>42</v>
+      </c>
+      <c r="S114" s="8">
+        <v>38</v>
+      </c>
+      <c r="T114" s="11"/>
+      <c r="U114" s="11"/>
+      <c r="V114" s="11"/>
+      <c r="W114" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X114" s="10">
+        <v>35543</v>
+      </c>
+      <c r="Y114" s="8">
+        <v>40277508</v>
+      </c>
+      <c r="Z114" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA114" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB114" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC114" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AD114" s="10">
+        <v>37775</v>
+      </c>
+      <c r="AE114" s="8">
+        <v>44810215</v>
+      </c>
+      <c r="AF114" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG114" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH114" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI114" s="11"/>
+      <c r="AJ114" s="11"/>
+      <c r="AK114" s="11"/>
+      <c r="AL114" s="11"/>
+      <c r="AM114" s="11"/>
+      <c r="AN114" s="11"/>
+      <c r="AO114" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AP114" s="8">
+        <v>40277508</v>
+      </c>
+      <c r="AQ114" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AR114" s="8">
+        <v>44810216</v>
+      </c>
+      <c r="AS114" s="11"/>
+      <c r="AT114" s="11"/>
+      <c r="AU114" s="28">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="115" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A115" s="21">
+        <v>46273.383287037039</v>
+      </c>
+      <c r="B115" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C115" s="22" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D115" s="23">
+        <v>30399457</v>
+      </c>
+      <c r="E115" s="24">
+        <v>29996</v>
+      </c>
+      <c r="F115" s="22" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G115" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H115" s="22" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I115" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J115" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K115" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="L115" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M115" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="N115" s="22" t="s">
+        <v>1113</v>
+      </c>
+      <c r="O115" s="25">
+        <v>44896</v>
+      </c>
+      <c r="P115" s="23">
+        <v>44</v>
+      </c>
+      <c r="Q115" s="23">
+        <v>5</v>
+      </c>
+      <c r="R115" s="23">
+        <v>44</v>
+      </c>
+      <c r="S115" s="23">
+        <v>38</v>
+      </c>
+      <c r="T115" s="22" t="s">
+        <v>1114</v>
+      </c>
+      <c r="U115" s="25">
+        <v>25850</v>
+      </c>
+      <c r="V115" s="23">
+        <v>21555550</v>
+      </c>
+      <c r="W115" s="22" t="s">
+        <v>1115</v>
+      </c>
+      <c r="X115" s="25">
+        <v>37432</v>
+      </c>
+      <c r="Y115" s="23">
+        <v>43843291</v>
+      </c>
+      <c r="Z115" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA115" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB115" s="26"/>
+      <c r="AC115" s="22" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AD115" s="25">
+        <v>38062</v>
+      </c>
+      <c r="AE115" s="23">
+        <v>45508098</v>
+      </c>
+      <c r="AF115" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG115" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH115" s="26"/>
+      <c r="AI115" s="22" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AJ115" s="25">
+        <v>38853</v>
+      </c>
+      <c r="AK115" s="23">
+        <v>47107320</v>
+      </c>
+      <c r="AL115" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM115" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN115" s="26"/>
+      <c r="AO115" s="22" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AP115" s="23">
+        <v>43843291</v>
+      </c>
+      <c r="AQ115" s="22" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AR115" s="23">
+        <v>47107320</v>
+      </c>
+      <c r="AS115" s="22" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AT115" s="23">
+        <v>45508098</v>
+      </c>
+      <c r="AU115" s="27">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="116" spans="1:47" ht="39" thickBot="1">
+      <c r="A116" s="6">
+        <v>46273.391805555555</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D116" s="8">
+        <v>18001714</v>
+      </c>
+      <c r="E116" s="8">
+        <v>19021967</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H116" s="8">
+        <v>3382409515</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K116" s="11"/>
+      <c r="L116" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M116" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="N116" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="O116" s="10">
+        <v>37075</v>
+      </c>
+      <c r="P116" s="8">
+        <v>52</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>52</v>
+      </c>
+      <c r="R116" s="8">
+        <v>52</v>
+      </c>
+      <c r="S116" s="8">
+        <v>45</v>
+      </c>
+      <c r="T116" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="U116" s="10">
+        <v>26860</v>
+      </c>
+      <c r="V116" s="8">
+        <v>23255156</v>
+      </c>
+      <c r="W116" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="X116" s="10">
+        <v>35901</v>
+      </c>
+      <c r="Y116" s="8">
+        <v>40959346</v>
+      </c>
+      <c r="Z116" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA116" s="11"/>
+      <c r="AB116" s="11"/>
+      <c r="AC116" s="11"/>
+      <c r="AD116" s="11"/>
+      <c r="AE116" s="11"/>
+      <c r="AF116" s="11"/>
+      <c r="AG116" s="11"/>
+      <c r="AH116" s="11"/>
+      <c r="AI116" s="11"/>
+      <c r="AJ116" s="11"/>
+      <c r="AK116" s="11"/>
+      <c r="AL116" s="11"/>
+      <c r="AM116" s="11"/>
+      <c r="AN116" s="11"/>
+      <c r="AO116" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AP116" s="8">
+        <v>23255156</v>
+      </c>
+      <c r="AQ116" s="11"/>
+      <c r="AR116" s="11"/>
+      <c r="AS116" s="11"/>
+      <c r="AT116" s="11"/>
+      <c r="AU116" s="28">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="117" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A117" s="21">
+        <v>46273.624247685184</v>
+      </c>
+      <c r="B117" s="22" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C117" s="22" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D117" s="23">
+        <v>21767041</v>
+      </c>
+      <c r="E117" s="24">
+        <v>25976</v>
+      </c>
+      <c r="F117" s="22" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G117" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H117" s="22" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I117" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J117" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K117" s="22" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L117" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M117" s="22" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N117" s="22" t="s">
+        <v>1129</v>
+      </c>
+      <c r="O117" s="25">
+        <v>39449</v>
+      </c>
+      <c r="P117" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q117" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R117" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="S117" s="23">
+        <v>36</v>
+      </c>
+      <c r="T117" s="22" t="s">
+        <v>1131</v>
+      </c>
+      <c r="U117" s="25">
+        <v>25490</v>
+      </c>
+      <c r="V117" s="23">
+        <v>20703838</v>
+      </c>
+      <c r="W117" s="22" t="s">
+        <v>1132</v>
+      </c>
+      <c r="X117" s="25">
+        <v>35028</v>
+      </c>
+      <c r="Y117" s="23">
+        <v>39049283</v>
+      </c>
+      <c r="Z117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB117" s="22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AC117" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AD117" s="25">
+        <v>36770</v>
+      </c>
+      <c r="AE117" s="23">
+        <v>42532435</v>
+      </c>
+      <c r="AF117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH117" s="22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AI117" s="22" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AJ117" s="25">
+        <v>16681</v>
+      </c>
+      <c r="AK117" s="23" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AL117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM117" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN117" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AO117" s="22" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AP117" s="23">
+        <v>20703838</v>
+      </c>
+      <c r="AQ117" s="22" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AR117" s="23">
+        <v>39049283</v>
+      </c>
+      <c r="AS117" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AT117" s="23">
+        <v>42532435</v>
+      </c>
+      <c r="AU117" s="27">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="118" spans="1:47" ht="64.5" thickBot="1">
+      <c r="A118" s="6">
+        <v>46273.680868055555</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D118" s="8">
+        <v>21767233</v>
+      </c>
+      <c r="E118" s="9">
+        <v>26231</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H118" s="8">
+        <v>3382446330</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L118" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M118" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="N118" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="O118" s="10">
+        <v>33574</v>
+      </c>
+      <c r="P118" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q118" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="R118" s="8">
+        <v>48</v>
+      </c>
+      <c r="S118" s="8">
+        <v>41</v>
+      </c>
+      <c r="T118" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="U118" s="10">
+        <v>29009</v>
+      </c>
+      <c r="V118" s="8">
+        <v>27419861</v>
+      </c>
+      <c r="W118" s="7" t="s">
+        <v>1144</v>
+      </c>
+      <c r="X118" s="10">
+        <v>39071</v>
+      </c>
+      <c r="Y118" s="8">
+        <v>47508181</v>
+      </c>
+      <c r="Z118" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA118" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB118" s="11"/>
+      <c r="AC118" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AD118" s="10">
+        <v>40188</v>
+      </c>
+      <c r="AE118" s="8">
+        <v>49817254</v>
+      </c>
+      <c r="AF118" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG118" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH118" s="11"/>
+      <c r="AI118" s="11"/>
+      <c r="AJ118" s="11"/>
+      <c r="AK118" s="11"/>
+      <c r="AL118" s="11"/>
+      <c r="AM118" s="11"/>
+      <c r="AN118" s="11"/>
+      <c r="AO118" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AP118" s="8">
+        <v>27419861</v>
+      </c>
+      <c r="AQ118" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AR118" s="8">
+        <v>47508181</v>
+      </c>
+      <c r="AS118" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AT118" s="8">
+        <v>49817254</v>
+      </c>
+      <c r="AU118" s="28">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="119" spans="1:47" ht="64.5" thickBot="1">
+      <c r="A119" s="12">
+        <v>46273.692303240743</v>
+      </c>
+      <c r="B119" s="13" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D119" s="14">
+        <v>21767233</v>
+      </c>
+      <c r="E119" s="15">
+        <v>26231</v>
+      </c>
+      <c r="F119" s="13" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G119" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H119" s="14">
+        <v>3382446330</v>
+      </c>
+      <c r="I119" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J119" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K119" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="L119" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="M119" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="N119" s="13" t="s">
+        <v>1142</v>
+      </c>
+      <c r="O119" s="16">
+        <v>33574</v>
+      </c>
+      <c r="P119" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q119" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="R119" s="14">
+        <v>48</v>
+      </c>
+      <c r="S119" s="14">
+        <v>41</v>
+      </c>
+      <c r="T119" s="13" t="s">
+        <v>1143</v>
+      </c>
+      <c r="U119" s="16">
+        <v>29009</v>
+      </c>
+      <c r="V119" s="14">
+        <v>27419861</v>
+      </c>
+      <c r="W119" s="13" t="s">
+        <v>1144</v>
+      </c>
+      <c r="X119" s="16">
+        <v>39071</v>
+      </c>
+      <c r="Y119" s="14">
+        <v>47508181</v>
+      </c>
+      <c r="Z119" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA119" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB119" s="17"/>
+      <c r="AC119" s="13" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AD119" s="16">
+        <v>40189</v>
+      </c>
+      <c r="AE119" s="14">
+        <v>49817254</v>
+      </c>
+      <c r="AF119" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG119" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH119" s="17"/>
+      <c r="AI119" s="17"/>
+      <c r="AJ119" s="17"/>
+      <c r="AK119" s="17"/>
+      <c r="AL119" s="17"/>
+      <c r="AM119" s="17"/>
+      <c r="AN119" s="17"/>
+      <c r="AO119" s="13" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AP119" s="14">
+        <v>27419861</v>
+      </c>
+      <c r="AQ119" s="13" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AR119" s="14">
+        <v>47508181</v>
+      </c>
+      <c r="AS119" s="13" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AT119" s="14">
+        <v>49817254</v>
+      </c>
+      <c r="AU119" s="18">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/declara.xlsx
+++ b/declara.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="1123">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -2272,30 +2272,6 @@
     <t>Giorgi valentino</t>
   </si>
   <si>
-    <t>facunuez893@gmail.com</t>
-  </si>
-  <si>
-    <t>Nuez facundo Matías</t>
-  </si>
-  <si>
-    <t>Falucho 525</t>
-  </si>
-  <si>
-    <t>Keila rueda</t>
-  </si>
-  <si>
-    <t>Lionel Nicolás nuez</t>
-  </si>
-  <si>
-    <t>Bruno elias nuez</t>
-  </si>
-  <si>
-    <t>Facundo Matías nuez</t>
-  </si>
-  <si>
-    <t>Keila Ayelen rueda</t>
-  </si>
-  <si>
     <t>juancarlosviglianco44@gmail.com</t>
   </si>
   <si>
@@ -2392,39 +2368,12 @@
     <t>Astudiano Zulma Noemi</t>
   </si>
   <si>
-    <t>Benito Bianco 672</t>
-  </si>
-  <si>
     <t>Asma</t>
   </si>
   <si>
-    <t>INPECIÓN</t>
-  </si>
-  <si>
-    <t>CONTROL EN ENTREGAS Y SECUESTROS DE MOTOS Y VEHICULOS , Control en depositos de Mini ciudad vial, control de CONOS , VALLAS Y DEMAS</t>
-  </si>
-  <si>
-    <t>XXL.54</t>
-  </si>
-  <si>
     <t>PEREZ DANTE DANIEL</t>
   </si>
   <si>
-    <t>PEREZ CECILIA DANIELA</t>
-  </si>
-  <si>
-    <t>BACHILLER EN ECONOMIA Y ADMINISTRACIÓN</t>
-  </si>
-  <si>
-    <t>Zulma Noemi Astudiano</t>
-  </si>
-  <si>
-    <t>Perez Dante Dsniel</t>
-  </si>
-  <si>
-    <t>Perez Cecilia Daniela</t>
-  </si>
-  <si>
     <t>ivanblanco230@gmail.com</t>
   </si>
   <si>
@@ -2929,18 +2878,6 @@
     <t>Olga carrizo</t>
   </si>
   <si>
-    <t>maximiliano.mp6@gmail.com</t>
-  </si>
-  <si>
-    <t>Chacon maximiliano</t>
-  </si>
-  <si>
-    <t>Catamarca 1330</t>
-  </si>
-  <si>
-    <t>Voluminosos</t>
-  </si>
-  <si>
     <t>fernandocellario55@gmail.com</t>
   </si>
   <si>
@@ -3137,15 +3074,6 @@
   </si>
   <si>
     <t>Wilson María de los angeles</t>
-  </si>
-  <si>
-    <t>Bernabé Ferreyra</t>
-  </si>
-  <si>
-    <t>Mastranza</t>
-  </si>
-  <si>
-    <t>Lietzmann Brenda gimena</t>
   </si>
   <si>
     <t>Selena Fernanda wilson</t>
@@ -4286,7 +4214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -12667,7 +12595,7 @@
         <v>740</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>877</v>
+        <v>860</v>
       </c>
       <c r="D72" s="23">
         <v>27180064</v>
@@ -12897,448 +12825,450 @@
         <v>532</v>
       </c>
     </row>
-    <row r="74" spans="1:47" ht="39" thickBot="1">
-      <c r="A74" s="21">
-        <v>46266.804722222223</v>
-      </c>
-      <c r="B74" s="22" t="s">
+    <row r="74" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A74" s="6">
+        <v>46266.811111111114</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>752</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="D74" s="23">
-        <v>41654641</v>
-      </c>
-      <c r="E74" s="24">
-        <v>36270</v>
-      </c>
-      <c r="F74" s="22" t="s">
+      <c r="D74" s="8">
+        <v>23255185</v>
+      </c>
+      <c r="E74" s="7" t="s">
         <v>754</v>
       </c>
-      <c r="G74" s="22" t="s">
+      <c r="F74" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="G74" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H74" s="23">
-        <v>3382447125</v>
-      </c>
-      <c r="I74" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J74" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="K74" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="L74" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M74" s="22" t="s">
-        <v>508</v>
-      </c>
-      <c r="N74" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="O74" s="25">
-        <v>44551</v>
-      </c>
-      <c r="P74" s="23">
-        <v>44</v>
-      </c>
-      <c r="Q74" s="23">
-        <v>44</v>
-      </c>
-      <c r="R74" s="23">
-        <v>44</v>
-      </c>
-      <c r="S74" s="23">
-        <v>44</v>
-      </c>
-      <c r="T74" s="22" t="s">
-        <v>755</v>
-      </c>
-      <c r="U74" s="25">
-        <v>38043</v>
-      </c>
-      <c r="V74" s="23">
-        <v>45508101</v>
-      </c>
-      <c r="W74" s="22" t="s">
+      <c r="H74" s="8">
+        <v>3382408376</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K74" s="11"/>
+      <c r="L74" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M74" s="7" t="s">
         <v>756</v>
       </c>
-      <c r="X74" s="25">
-        <v>44210</v>
-      </c>
-      <c r="Y74" s="23">
-        <v>58328389</v>
-      </c>
-      <c r="Z74" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA74" s="26"/>
-      <c r="AB74" s="26"/>
-      <c r="AC74" s="22" t="s">
+      <c r="N74" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="AD74" s="25">
-        <v>46189</v>
-      </c>
-      <c r="AE74" s="23">
-        <v>71146228</v>
-      </c>
-      <c r="AF74" s="26"/>
-      <c r="AG74" s="26"/>
-      <c r="AH74" s="26"/>
-      <c r="AI74" s="26"/>
-      <c r="AJ74" s="26"/>
-      <c r="AK74" s="26"/>
-      <c r="AL74" s="26"/>
-      <c r="AM74" s="26"/>
-      <c r="AN74" s="26"/>
-      <c r="AO74" s="22" t="s">
+      <c r="O74" s="10">
+        <v>37960</v>
+      </c>
+      <c r="P74" s="8">
+        <v>46</v>
+      </c>
+      <c r="Q74" s="8">
+        <v>46</v>
+      </c>
+      <c r="R74" s="8">
+        <v>46</v>
+      </c>
+      <c r="S74" s="8">
+        <v>41</v>
+      </c>
+      <c r="T74" s="7" t="s">
         <v>758</v>
       </c>
-      <c r="AP74" s="23">
-        <v>41654641</v>
-      </c>
-      <c r="AQ74" s="22" t="s">
+      <c r="U74" s="10">
+        <v>28626</v>
+      </c>
+      <c r="V74" s="8">
+        <v>26590227</v>
+      </c>
+      <c r="W74" s="7" t="s">
         <v>759</v>
       </c>
-      <c r="AR74" s="23">
-        <v>45508101</v>
-      </c>
-      <c r="AS74" s="22" t="s">
-        <v>756</v>
-      </c>
-      <c r="AT74" s="23">
-        <v>58328389</v>
-      </c>
-      <c r="AU74" s="27">
-        <v>524</v>
+      <c r="X74" s="10">
+        <v>36711</v>
+      </c>
+      <c r="Y74" s="8">
+        <v>42127989</v>
+      </c>
+      <c r="Z74" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA74" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB74" s="11"/>
+      <c r="AC74" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="AD74" s="10">
+        <v>37545</v>
+      </c>
+      <c r="AE74" s="8">
+        <v>44067886</v>
+      </c>
+      <c r="AF74" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG74" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH74" s="11"/>
+      <c r="AI74" s="11"/>
+      <c r="AJ74" s="11"/>
+      <c r="AK74" s="11"/>
+      <c r="AL74" s="11"/>
+      <c r="AM74" s="11"/>
+      <c r="AN74" s="11"/>
+      <c r="AO74" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="AP74" s="8">
+        <v>23255185</v>
+      </c>
+      <c r="AQ74" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="AR74" s="8">
+        <v>26590227</v>
+      </c>
+      <c r="AS74" s="11"/>
+      <c r="AT74" s="11"/>
+      <c r="AU74" s="28">
+        <v>365</v>
       </c>
     </row>
     <row r="75" spans="1:47" ht="51.75" thickBot="1">
-      <c r="A75" s="6">
-        <v>46266.811111111114</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="C75" s="7" t="s">
+      <c r="A75" s="21">
+        <v>46266.812395833331</v>
+      </c>
+      <c r="B75" s="22" t="s">
         <v>761</v>
       </c>
-      <c r="D75" s="8">
-        <v>23255185</v>
-      </c>
-      <c r="E75" s="7" t="s">
+      <c r="C75" s="22" t="s">
         <v>762</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="D75" s="23">
+        <v>27419925</v>
+      </c>
+      <c r="E75" s="24">
+        <v>29076</v>
+      </c>
+      <c r="F75" s="22" t="s">
         <v>763</v>
       </c>
-      <c r="G75" s="7" t="s">
+      <c r="G75" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="H75" s="8">
-        <v>3382408376</v>
-      </c>
-      <c r="I75" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="7" t="s">
+      <c r="H75" s="22" t="s">
+        <v>764</v>
+      </c>
+      <c r="I75" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J75" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K75" s="22" t="s">
+        <v>765</v>
+      </c>
+      <c r="L75" s="22" t="s">
+        <v>766</v>
+      </c>
+      <c r="M75" s="22" t="s">
+        <v>767</v>
+      </c>
+      <c r="N75" s="22" t="s">
+        <v>768</v>
+      </c>
+      <c r="O75" s="25">
+        <v>36101</v>
+      </c>
+      <c r="P75" s="23">
+        <v>50</v>
+      </c>
+      <c r="Q75" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="R75" s="23">
+        <v>50</v>
+      </c>
+      <c r="S75" s="23">
+        <v>44</v>
+      </c>
+      <c r="T75" s="22" t="s">
+        <v>769</v>
+      </c>
+      <c r="U75" s="25">
+        <v>31613</v>
+      </c>
+      <c r="V75" s="23">
+        <v>32348195</v>
+      </c>
+      <c r="W75" s="22" t="s">
+        <v>770</v>
+      </c>
+      <c r="X75" s="25">
+        <v>42087</v>
+      </c>
+      <c r="Y75" s="23">
+        <v>54615931</v>
+      </c>
+      <c r="Z75" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA75" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="M75" s="7" t="s">
-        <v>764</v>
-      </c>
-      <c r="N75" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="O75" s="10">
-        <v>37960</v>
-      </c>
-      <c r="P75" s="8">
-        <v>46</v>
-      </c>
-      <c r="Q75" s="8">
-        <v>46</v>
-      </c>
-      <c r="R75" s="8">
-        <v>46</v>
-      </c>
-      <c r="S75" s="8">
-        <v>41</v>
-      </c>
-      <c r="T75" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="U75" s="10">
-        <v>28626</v>
-      </c>
-      <c r="V75" s="8">
-        <v>26590227</v>
-      </c>
-      <c r="W75" s="7" t="s">
-        <v>767</v>
-      </c>
-      <c r="X75" s="10">
-        <v>36711</v>
-      </c>
-      <c r="Y75" s="8">
-        <v>42127989</v>
-      </c>
-      <c r="Z75" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA75" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB75" s="11"/>
-      <c r="AC75" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="AD75" s="10">
-        <v>37545</v>
-      </c>
-      <c r="AE75" s="8">
-        <v>44067886</v>
-      </c>
-      <c r="AF75" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG75" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH75" s="11"/>
-      <c r="AI75" s="11"/>
-      <c r="AJ75" s="11"/>
-      <c r="AK75" s="11"/>
-      <c r="AL75" s="11"/>
-      <c r="AM75" s="11"/>
-      <c r="AN75" s="11"/>
-      <c r="AO75" s="7" t="s">
-        <v>761</v>
-      </c>
-      <c r="AP75" s="8">
-        <v>23255185</v>
-      </c>
-      <c r="AQ75" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="AR75" s="8">
-        <v>26590227</v>
-      </c>
-      <c r="AS75" s="11"/>
-      <c r="AT75" s="11"/>
-      <c r="AU75" s="28">
-        <v>365</v>
+      <c r="AB75" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC75" s="22" t="s">
+        <v>771</v>
+      </c>
+      <c r="AD75" s="25">
+        <v>44973</v>
+      </c>
+      <c r="AE75" s="23">
+        <v>59654188</v>
+      </c>
+      <c r="AF75" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG75" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH75" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI75" s="26"/>
+      <c r="AJ75" s="26"/>
+      <c r="AK75" s="26"/>
+      <c r="AL75" s="26"/>
+      <c r="AM75" s="26"/>
+      <c r="AN75" s="26"/>
+      <c r="AO75" s="22" t="s">
+        <v>772</v>
+      </c>
+      <c r="AP75" s="23">
+        <v>32348195</v>
+      </c>
+      <c r="AQ75" s="22" t="s">
+        <v>770</v>
+      </c>
+      <c r="AR75" s="23">
+        <v>54615931</v>
+      </c>
+      <c r="AS75" s="22" t="s">
+        <v>771</v>
+      </c>
+      <c r="AT75" s="23">
+        <v>59654188</v>
+      </c>
+      <c r="AU75" s="27">
+        <v>128</v>
       </c>
     </row>
-    <row r="76" spans="1:47" ht="51.75" thickBot="1">
-      <c r="A76" s="21">
-        <v>46266.812395833331</v>
-      </c>
-      <c r="B76" s="22" t="s">
-        <v>769</v>
-      </c>
-      <c r="C76" s="22" t="s">
-        <v>770</v>
-      </c>
-      <c r="D76" s="23">
-        <v>27419925</v>
-      </c>
-      <c r="E76" s="24">
-        <v>29076</v>
-      </c>
-      <c r="F76" s="22" t="s">
-        <v>771</v>
-      </c>
-      <c r="G76" s="22" t="s">
+    <row r="76" spans="1:47" ht="39" thickBot="1">
+      <c r="A76" s="6">
+        <v>46266.867777777778</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="D76" s="8">
+        <v>29931700</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="G76" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H76" s="22" t="s">
-        <v>772</v>
-      </c>
-      <c r="I76" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="J76" s="22" t="s">
+      <c r="H76" s="8">
+        <v>3382406475</v>
+      </c>
+      <c r="I76" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J76" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K76" s="22" t="s">
-        <v>773</v>
-      </c>
-      <c r="L76" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="M76" s="22" t="s">
-        <v>775</v>
-      </c>
-      <c r="N76" s="22" t="s">
-        <v>776</v>
-      </c>
-      <c r="O76" s="25">
-        <v>36101</v>
-      </c>
-      <c r="P76" s="23">
-        <v>50</v>
-      </c>
-      <c r="Q76" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="R76" s="23">
-        <v>50</v>
-      </c>
-      <c r="S76" s="23">
+      <c r="K76" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M76" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="N76" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="O76" s="10">
+        <v>38853</v>
+      </c>
+      <c r="P76" s="8">
+        <v>42</v>
+      </c>
+      <c r="Q76" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R76" s="8">
         <v>44</v>
       </c>
-      <c r="T76" s="22" t="s">
-        <v>777</v>
-      </c>
-      <c r="U76" s="25">
-        <v>31613</v>
-      </c>
-      <c r="V76" s="23">
-        <v>32348195</v>
-      </c>
-      <c r="W76" s="22" t="s">
+      <c r="S76" s="8">
+        <v>42</v>
+      </c>
+      <c r="T76" s="11"/>
+      <c r="U76" s="11"/>
+      <c r="V76" s="11"/>
+      <c r="W76" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="X76" s="25">
-        <v>42087</v>
-      </c>
-      <c r="Y76" s="23">
-        <v>54615931</v>
-      </c>
-      <c r="Z76" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA76" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB76" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AC76" s="22" t="s">
+      <c r="X76" s="10">
+        <v>39932</v>
+      </c>
+      <c r="Y76" s="8">
+        <v>49448476</v>
+      </c>
+      <c r="Z76" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA76" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB76" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="AD76" s="25">
-        <v>44973</v>
-      </c>
-      <c r="AE76" s="23">
-        <v>59654188</v>
-      </c>
-      <c r="AF76" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AG76" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AH76" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AI76" s="26"/>
-      <c r="AJ76" s="26"/>
-      <c r="AK76" s="26"/>
-      <c r="AL76" s="26"/>
-      <c r="AM76" s="26"/>
-      <c r="AN76" s="26"/>
-      <c r="AO76" s="22" t="s">
+      <c r="AC76" s="7" t="s">
         <v>780</v>
       </c>
-      <c r="AP76" s="23">
-        <v>32348195</v>
-      </c>
-      <c r="AQ76" s="22" t="s">
-        <v>778</v>
-      </c>
-      <c r="AR76" s="23">
-        <v>54615931</v>
-      </c>
-      <c r="AS76" s="22" t="s">
-        <v>779</v>
-      </c>
-      <c r="AT76" s="23">
-        <v>59654188</v>
-      </c>
-      <c r="AU76" s="27">
-        <v>128</v>
+      <c r="AD76" s="10">
+        <v>43980</v>
+      </c>
+      <c r="AE76" s="8">
+        <v>58328238</v>
+      </c>
+      <c r="AF76" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG76" s="11"/>
+      <c r="AH76" s="11"/>
+      <c r="AI76" s="11"/>
+      <c r="AJ76" s="11"/>
+      <c r="AK76" s="11"/>
+      <c r="AL76" s="11"/>
+      <c r="AM76" s="11"/>
+      <c r="AN76" s="11"/>
+      <c r="AO76" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="AP76" s="8">
+        <v>49448476</v>
+      </c>
+      <c r="AQ76" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="AR76" s="8">
+        <v>58328238</v>
+      </c>
+      <c r="AS76" s="11"/>
+      <c r="AT76" s="11"/>
+      <c r="AU76" s="28">
+        <v>160</v>
       </c>
     </row>
-    <row r="77" spans="1:47" ht="39" thickBot="1">
+    <row r="77" spans="1:47" ht="26.25" thickBot="1">
       <c r="A77" s="6">
-        <v>46266.867777777778</v>
+        <v>46266.874895833331</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="D77" s="8">
-        <v>29931700</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>783</v>
+        <v>25773967</v>
+      </c>
+      <c r="E77" s="9">
+        <v>28292</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H77" s="8">
-        <v>3382406475</v>
+        <v>3382407085</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>264</v>
+        <v>471</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>34</v>
+        <v>789</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>316</v>
+        <v>790</v>
       </c>
       <c r="N77" s="7" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="O77" s="10">
-        <v>38853</v>
+        <v>43800</v>
       </c>
       <c r="P77" s="8">
-        <v>42</v>
-      </c>
-      <c r="Q77" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="Q77" s="8">
+        <v>6</v>
       </c>
       <c r="R77" s="8">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="S77" s="8">
         <v>42</v>
       </c>
-      <c r="T77" s="11"/>
-      <c r="U77" s="11"/>
-      <c r="V77" s="11"/>
+      <c r="T77" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="U77" s="10">
+        <v>29710</v>
+      </c>
+      <c r="V77" s="8">
+        <v>28577899</v>
+      </c>
       <c r="W77" s="7" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="X77" s="10">
-        <v>39932</v>
+        <v>38533</v>
       </c>
       <c r="Y77" s="8">
-        <v>49448476</v>
+        <v>46367971</v>
       </c>
       <c r="Z77" s="7" t="s">
         <v>40</v>
@@ -13347,20 +13277,12 @@
         <v>40</v>
       </c>
       <c r="AB77" s="7" t="s">
-        <v>787</v>
-      </c>
-      <c r="AC77" s="7" t="s">
-        <v>788</v>
-      </c>
-      <c r="AD77" s="10">
-        <v>43980</v>
-      </c>
-      <c r="AE77" s="8">
-        <v>58328238</v>
-      </c>
-      <c r="AF77" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="AC77" s="11"/>
+      <c r="AD77" s="11"/>
+      <c r="AE77" s="11"/>
+      <c r="AF77" s="11"/>
       <c r="AG77" s="11"/>
       <c r="AH77" s="11"/>
       <c r="AI77" s="11"/>
@@ -13370,96 +13292,100 @@
       <c r="AM77" s="11"/>
       <c r="AN77" s="11"/>
       <c r="AO77" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="AP77" s="8">
-        <v>49448476</v>
+        <v>587</v>
+      </c>
+      <c r="AP77" s="7" t="s">
+        <v>587</v>
       </c>
       <c r="AQ77" s="7" t="s">
-        <v>788</v>
-      </c>
-      <c r="AR77" s="8">
-        <v>58328238</v>
-      </c>
-      <c r="AS77" s="11"/>
-      <c r="AT77" s="11"/>
+        <v>587</v>
+      </c>
+      <c r="AR77" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="AS77" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="AT77" s="7" t="s">
+        <v>587</v>
+      </c>
       <c r="AU77" s="28">
-        <v>160</v>
+        <v>468</v>
       </c>
     </row>
-    <row r="78" spans="1:47" ht="217.5" thickBot="1">
+    <row r="78" spans="1:47" ht="39" thickBot="1">
       <c r="A78" s="21">
-        <v>46266.874803240738</v>
+        <v>46266.894270833334</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D78" s="23">
-        <v>21767045</v>
+        <v>34408628</v>
       </c>
       <c r="E78" s="24">
-        <v>25967</v>
+        <v>32954</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="H78" s="23">
-        <v>3382412350</v>
+        <v>3382445512</v>
       </c>
       <c r="I78" s="22" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="J78" s="22" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="K78" s="26"/>
       <c r="L78" s="22" t="s">
-        <v>793</v>
+        <v>230</v>
       </c>
       <c r="M78" s="22" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="N78" s="22" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="O78" s="25">
-        <v>43800</v>
-      </c>
-      <c r="P78" s="22" t="s">
-        <v>796</v>
+        <v>40182</v>
+      </c>
+      <c r="P78" s="23">
+        <v>46</v>
       </c>
       <c r="Q78" s="23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R78" s="23">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="S78" s="23">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="T78" s="22" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="U78" s="25">
-        <v>25856</v>
+        <v>32954</v>
       </c>
       <c r="V78" s="23">
-        <v>21534233</v>
+        <v>344408628</v>
       </c>
       <c r="W78" s="22" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="X78" s="25">
-        <v>37329</v>
+        <v>40149</v>
       </c>
       <c r="Y78" s="23">
-        <v>43843221</v>
+        <v>49817219</v>
       </c>
       <c r="Z78" s="22" t="s">
         <v>40</v>
@@ -13467,128 +13393,122 @@
       <c r="AA78" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AB78" s="22" t="s">
-        <v>799</v>
-      </c>
-      <c r="AC78" s="26"/>
-      <c r="AD78" s="26"/>
-      <c r="AE78" s="26"/>
-      <c r="AF78" s="26"/>
+      <c r="AB78" s="26"/>
+      <c r="AC78" s="22" t="s">
+        <v>801</v>
+      </c>
+      <c r="AD78" s="25">
+        <v>42385</v>
+      </c>
+      <c r="AE78" s="23">
+        <v>55214145</v>
+      </c>
+      <c r="AF78" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="AG78" s="26"/>
       <c r="AH78" s="26"/>
-      <c r="AI78" s="26"/>
-      <c r="AJ78" s="26"/>
-      <c r="AK78" s="26"/>
-      <c r="AL78" s="26"/>
+      <c r="AI78" s="22" t="s">
+        <v>802</v>
+      </c>
+      <c r="AJ78" s="25">
+        <v>44985</v>
+      </c>
+      <c r="AK78" s="23">
+        <v>59814004</v>
+      </c>
+      <c r="AL78" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="AM78" s="26"/>
       <c r="AN78" s="26"/>
       <c r="AO78" s="22" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="AP78" s="23">
-        <v>21767045</v>
+        <v>36174744</v>
       </c>
       <c r="AQ78" s="22" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="AR78" s="23">
-        <v>21534233</v>
+        <v>34408628</v>
       </c>
       <c r="AS78" s="22" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AT78" s="23">
-        <v>43843221</v>
+        <v>49817219</v>
       </c>
       <c r="AU78" s="27">
-        <v>465</v>
+        <v>601</v>
       </c>
     </row>
-    <row r="79" spans="1:47" ht="26.25" thickBot="1">
+    <row r="79" spans="1:47" ht="39" thickBot="1">
       <c r="A79" s="6">
-        <v>46266.874895833331</v>
+        <v>46266.911157407405</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D79" s="8">
-        <v>25773967</v>
+        <v>30623004</v>
       </c>
       <c r="E79" s="9">
-        <v>28292</v>
+        <v>30612</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H79" s="8">
-        <v>3382407085</v>
+        <v>3382483929</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>471</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="K79" s="11"/>
       <c r="L79" s="7" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="M79" s="7" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="N79" s="7" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="O79" s="10">
         <v>43800</v>
       </c>
       <c r="P79" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>5</v>
+      </c>
+      <c r="R79" s="8">
         <v>48</v>
       </c>
-      <c r="Q79" s="8">
-        <v>6</v>
-      </c>
-      <c r="R79" s="8">
-        <v>54</v>
-      </c>
       <c r="S79" s="8">
-        <v>42</v>
-      </c>
-      <c r="T79" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="U79" s="10">
-        <v>29710</v>
-      </c>
-      <c r="V79" s="8">
-        <v>28577899</v>
-      </c>
-      <c r="W79" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="X79" s="10">
-        <v>38533</v>
-      </c>
-      <c r="Y79" s="8">
-        <v>46367971</v>
-      </c>
-      <c r="Z79" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA79" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB79" s="7" t="s">
-        <v>230</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="T79" s="11"/>
+      <c r="U79" s="11"/>
+      <c r="V79" s="11"/>
+      <c r="W79" s="11"/>
+      <c r="X79" s="11"/>
+      <c r="Y79" s="11"/>
+      <c r="Z79" s="11"/>
+      <c r="AA79" s="11"/>
+      <c r="AB79" s="11"/>
       <c r="AC79" s="11"/>
       <c r="AD79" s="11"/>
       <c r="AE79" s="11"/>
@@ -13602,228 +13522,212 @@
       <c r="AM79" s="11"/>
       <c r="AN79" s="11"/>
       <c r="AO79" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="AP79" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="AQ79" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="AR79" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="AS79" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="AT79" s="7" t="s">
-        <v>587</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="AP79" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AQ79" s="11"/>
+      <c r="AR79" s="11"/>
+      <c r="AS79" s="11"/>
+      <c r="AT79" s="11"/>
       <c r="AU79" s="28">
-        <v>468</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="80" spans="1:47" ht="39" thickBot="1">
+    <row r="80" spans="1:47" ht="26.25" thickBot="1">
       <c r="A80" s="21">
-        <v>46266.894270833334</v>
+        <v>46266.911157407405</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>812</v>
-      </c>
-      <c r="D80" s="23">
-        <v>34408628</v>
+        <v>813</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>814</v>
       </c>
       <c r="E80" s="24">
-        <v>32954</v>
+        <v>32113</v>
       </c>
       <c r="F80" s="22" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="G80" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H80" s="23">
-        <v>3382445512</v>
+        <v>3382446755</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="J80" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="K80" s="26"/>
+        <v>83</v>
+      </c>
+      <c r="K80" s="22" t="s">
+        <v>471</v>
+      </c>
       <c r="L80" s="22" t="s">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="M80" s="22" t="s">
-        <v>814</v>
+        <v>327</v>
       </c>
       <c r="N80" s="22" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O80" s="25">
-        <v>40182</v>
+        <v>39203</v>
       </c>
       <c r="P80" s="23">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Q80" s="23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R80" s="23">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="S80" s="23">
-        <v>36</v>
-      </c>
-      <c r="T80" s="22" t="s">
-        <v>816</v>
-      </c>
-      <c r="U80" s="25">
-        <v>32954</v>
-      </c>
-      <c r="V80" s="23">
-        <v>344408628</v>
-      </c>
-      <c r="W80" s="22" t="s">
-        <v>817</v>
-      </c>
-      <c r="X80" s="25">
-        <v>40149</v>
-      </c>
-      <c r="Y80" s="23">
-        <v>49817219</v>
-      </c>
-      <c r="Z80" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA80" s="22" t="s">
-        <v>40</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="T80" s="26"/>
+      <c r="U80" s="26"/>
+      <c r="V80" s="26"/>
+      <c r="W80" s="26"/>
+      <c r="X80" s="26"/>
+      <c r="Y80" s="26"/>
+      <c r="Z80" s="26"/>
+      <c r="AA80" s="26"/>
       <c r="AB80" s="26"/>
-      <c r="AC80" s="22" t="s">
-        <v>818</v>
-      </c>
-      <c r="AD80" s="25">
-        <v>42385</v>
-      </c>
-      <c r="AE80" s="23">
-        <v>55214145</v>
-      </c>
-      <c r="AF80" s="22" t="s">
-        <v>40</v>
-      </c>
+      <c r="AC80" s="26"/>
+      <c r="AD80" s="26"/>
+      <c r="AE80" s="26"/>
+      <c r="AF80" s="26"/>
       <c r="AG80" s="26"/>
       <c r="AH80" s="26"/>
-      <c r="AI80" s="22" t="s">
-        <v>819</v>
-      </c>
-      <c r="AJ80" s="25">
-        <v>44985</v>
-      </c>
-      <c r="AK80" s="23">
-        <v>59814004</v>
-      </c>
-      <c r="AL80" s="22" t="s">
-        <v>40</v>
-      </c>
+      <c r="AI80" s="26"/>
+      <c r="AJ80" s="26"/>
+      <c r="AK80" s="26"/>
+      <c r="AL80" s="26"/>
       <c r="AM80" s="26"/>
       <c r="AN80" s="26"/>
       <c r="AO80" s="22" t="s">
+        <v>817</v>
+      </c>
+      <c r="AP80" s="22" t="s">
+        <v>818</v>
+      </c>
+      <c r="AQ80" s="26"/>
+      <c r="AR80" s="26"/>
+      <c r="AS80" s="26"/>
+      <c r="AT80" s="26"/>
+      <c r="AU80" s="27">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="81" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A81" s="6">
+        <v>46266.919317129628</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="AP80" s="23">
-        <v>36174744</v>
-      </c>
-      <c r="AQ80" s="22" t="s">
-        <v>816</v>
-      </c>
-      <c r="AR80" s="23">
-        <v>34408628</v>
-      </c>
-      <c r="AS80" s="22" t="s">
+      <c r="D81" s="8">
+        <v>23255051</v>
+      </c>
+      <c r="E81" s="9">
+        <v>26746</v>
+      </c>
+      <c r="F81" s="7" t="s">
         <v>821</v>
-      </c>
-      <c r="AT80" s="23">
-        <v>49817219</v>
-      </c>
-      <c r="AU80" s="27">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="81" spans="1:47" ht="39" thickBot="1">
-      <c r="A81" s="6">
-        <v>46266.911157407405</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="D81" s="8">
-        <v>30623004</v>
-      </c>
-      <c r="E81" s="9">
-        <v>30612</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>824</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H81" s="8">
-        <v>3382483929</v>
+        <v>3382458829</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K81" s="11"/>
+        <v>32</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>822</v>
+      </c>
       <c r="L81" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M81" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="N81" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="O81" s="10">
+        <v>35644</v>
+      </c>
+      <c r="P81" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q81" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="R81" s="8">
+        <v>44</v>
+      </c>
+      <c r="S81" s="8">
+        <v>40</v>
+      </c>
+      <c r="T81" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="M81" s="7" t="s">
+      <c r="U81" s="10">
+        <v>26908</v>
+      </c>
+      <c r="V81" s="8">
+        <v>23556106</v>
+      </c>
+      <c r="W81" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="N81" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="O81" s="10">
-        <v>43800</v>
-      </c>
-      <c r="P81" s="8">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>5</v>
-      </c>
-      <c r="R81" s="8">
-        <v>48</v>
-      </c>
-      <c r="S81" s="8">
-        <v>38</v>
-      </c>
-      <c r="T81" s="11"/>
-      <c r="U81" s="11"/>
-      <c r="V81" s="11"/>
-      <c r="W81" s="11"/>
-      <c r="X81" s="11"/>
-      <c r="Y81" s="11"/>
-      <c r="Z81" s="11"/>
-      <c r="AA81" s="11"/>
-      <c r="AB81" s="11"/>
-      <c r="AC81" s="11"/>
-      <c r="AD81" s="11"/>
-      <c r="AE81" s="11"/>
-      <c r="AF81" s="11"/>
-      <c r="AG81" s="11"/>
+      <c r="X81" s="10">
+        <v>37390</v>
+      </c>
+      <c r="Y81" s="8">
+        <v>43843249</v>
+      </c>
+      <c r="Z81" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA81" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB81" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="AC81" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="AD81" s="10">
+        <v>38574</v>
+      </c>
+      <c r="AE81" s="8">
+        <v>46368000</v>
+      </c>
+      <c r="AF81" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG81" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AH81" s="11"/>
       <c r="AI81" s="11"/>
       <c r="AJ81" s="11"/>
@@ -13832,92 +13736,128 @@
       <c r="AM81" s="11"/>
       <c r="AN81" s="11"/>
       <c r="AO81" s="7" t="s">
-        <v>827</v>
-      </c>
-      <c r="AP81" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="AP81" s="8">
+        <v>23556106</v>
+      </c>
+      <c r="AQ81" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="AR81" s="8">
+        <v>43843249</v>
+      </c>
+      <c r="AS81" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="AQ81" s="11"/>
-      <c r="AR81" s="11"/>
-      <c r="AS81" s="11"/>
-      <c r="AT81" s="11"/>
+      <c r="AT81" s="8">
+        <v>46368000</v>
+      </c>
       <c r="AU81" s="28">
-        <v>497</v>
+        <v>192</v>
       </c>
     </row>
-    <row r="82" spans="1:47" ht="26.25" thickBot="1">
+    <row r="82" spans="1:47" ht="39" thickBot="1">
       <c r="A82" s="21">
-        <v>46266.911157407405</v>
+        <v>46266.930150462962</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>830</v>
-      </c>
-      <c r="D82" s="22" t="s">
         <v>831</v>
       </c>
-      <c r="E82" s="24">
-        <v>32113</v>
+      <c r="D82" s="23">
+        <v>27863231</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>832</v>
       </c>
       <c r="F82" s="22" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G82" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H82" s="23">
-        <v>3382446755</v>
+        <v>3382574927</v>
       </c>
       <c r="I82" s="22" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="J82" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="K82" s="22" t="s">
-        <v>471</v>
-      </c>
+      <c r="K82" s="26"/>
       <c r="L82" s="22" t="s">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="M82" s="22" t="s">
-        <v>327</v>
+        <v>834</v>
       </c>
       <c r="N82" s="22" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="O82" s="25">
-        <v>39203</v>
-      </c>
-      <c r="P82" s="23">
-        <v>50</v>
-      </c>
-      <c r="Q82" s="23">
-        <v>8</v>
+        <v>37926</v>
+      </c>
+      <c r="P82" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q82" s="22" t="s">
+        <v>37</v>
       </c>
       <c r="R82" s="23">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="S82" s="23">
-        <v>41</v>
-      </c>
-      <c r="T82" s="26"/>
-      <c r="U82" s="26"/>
-      <c r="V82" s="26"/>
-      <c r="W82" s="26"/>
-      <c r="X82" s="26"/>
-      <c r="Y82" s="26"/>
-      <c r="Z82" s="26"/>
-      <c r="AA82" s="26"/>
-      <c r="AB82" s="26"/>
-      <c r="AC82" s="26"/>
-      <c r="AD82" s="26"/>
-      <c r="AE82" s="26"/>
-      <c r="AF82" s="26"/>
-      <c r="AG82" s="26"/>
-      <c r="AH82" s="26"/>
+        <v>40</v>
+      </c>
+      <c r="T82" s="22" t="s">
+        <v>836</v>
+      </c>
+      <c r="U82" s="25">
+        <v>31424</v>
+      </c>
+      <c r="V82" s="23">
+        <v>31970849</v>
+      </c>
+      <c r="W82" s="22" t="s">
+        <v>837</v>
+      </c>
+      <c r="X82" s="25">
+        <v>39530</v>
+      </c>
+      <c r="Y82" s="23">
+        <v>48063738</v>
+      </c>
+      <c r="Z82" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA82" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB82" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC82" s="22" t="s">
+        <v>838</v>
+      </c>
+      <c r="AD82" s="25">
+        <v>38154</v>
+      </c>
+      <c r="AE82" s="23">
+        <v>45827756</v>
+      </c>
+      <c r="AF82" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG82" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH82" s="22" t="s">
+        <v>230</v>
+      </c>
       <c r="AI82" s="26"/>
       <c r="AJ82" s="26"/>
       <c r="AK82" s="26"/>
@@ -13925,94 +13865,94 @@
       <c r="AM82" s="26"/>
       <c r="AN82" s="26"/>
       <c r="AO82" s="22" t="s">
-        <v>834</v>
-      </c>
-      <c r="AP82" s="22" t="s">
-        <v>835</v>
+        <v>839</v>
+      </c>
+      <c r="AP82" s="23">
+        <v>27863231</v>
       </c>
       <c r="AQ82" s="26"/>
       <c r="AR82" s="26"/>
       <c r="AS82" s="26"/>
       <c r="AT82" s="26"/>
       <c r="AU82" s="27">
-        <v>175</v>
+        <v>360</v>
       </c>
     </row>
     <row r="83" spans="1:47" ht="51.75" thickBot="1">
       <c r="A83" s="6">
-        <v>46266.919317129628</v>
+        <v>46266.940138888887</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D83" s="8">
-        <v>23255051</v>
+        <v>24352357</v>
       </c>
       <c r="E83" s="9">
-        <v>26746</v>
+        <v>27565</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H83" s="8">
-        <v>3382458829</v>
+      <c r="H83" s="7" t="s">
+        <v>843</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>840</v>
+        <v>706</v>
       </c>
       <c r="N83" s="7" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="O83" s="10">
-        <v>35644</v>
-      </c>
-      <c r="P83" s="7" t="s">
-        <v>233</v>
+        <v>40544</v>
+      </c>
+      <c r="P83" s="8">
+        <v>42</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>233</v>
+        <v>49</v>
       </c>
       <c r="R83" s="8">
         <v>44</v>
       </c>
       <c r="S83" s="8">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="T83" s="7" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="U83" s="10">
-        <v>26908</v>
+        <v>30449</v>
       </c>
       <c r="V83" s="8">
-        <v>23556106</v>
+        <v>29931746</v>
       </c>
       <c r="W83" s="7" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="X83" s="10">
-        <v>37390</v>
+        <v>37504</v>
       </c>
       <c r="Y83" s="8">
-        <v>43843249</v>
+        <v>44067873</v>
       </c>
       <c r="Z83" s="7" t="s">
         <v>40</v>
@@ -14021,16 +13961,16 @@
         <v>40</v>
       </c>
       <c r="AB83" s="7" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="AC83" s="7" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="AD83" s="10">
-        <v>38574</v>
+        <v>38390</v>
       </c>
       <c r="AE83" s="8">
-        <v>46368000</v>
+        <v>46299657</v>
       </c>
       <c r="AF83" s="7" t="s">
         <v>40</v>
@@ -14038,540 +13978,504 @@
       <c r="AG83" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AH83" s="11"/>
-      <c r="AI83" s="11"/>
-      <c r="AJ83" s="11"/>
-      <c r="AK83" s="11"/>
-      <c r="AL83" s="11"/>
-      <c r="AM83" s="11"/>
+      <c r="AH83" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="AI83" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="AJ83" s="10">
+        <v>40458</v>
+      </c>
+      <c r="AK83" s="8">
+        <v>50449155</v>
+      </c>
+      <c r="AL83" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM83" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AN83" s="11"/>
       <c r="AO83" s="7" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="AP83" s="8">
-        <v>23556106</v>
-      </c>
-      <c r="AQ83" s="7" t="s">
-        <v>843</v>
-      </c>
-      <c r="AR83" s="8">
-        <v>43843249</v>
-      </c>
-      <c r="AS83" s="7" t="s">
-        <v>845</v>
-      </c>
-      <c r="AT83" s="8">
-        <v>46368000</v>
-      </c>
+        <v>24362357</v>
+      </c>
+      <c r="AQ83" s="11"/>
+      <c r="AR83" s="11"/>
+      <c r="AS83" s="11"/>
+      <c r="AT83" s="11"/>
       <c r="AU83" s="28">
-        <v>192</v>
+        <v>391</v>
       </c>
     </row>
-    <row r="84" spans="1:47" ht="39" thickBot="1">
-      <c r="A84" s="21">
-        <v>46266.930150462962</v>
-      </c>
-      <c r="B84" s="22" t="s">
-        <v>847</v>
-      </c>
-      <c r="C84" s="22" t="s">
-        <v>848</v>
-      </c>
-      <c r="D84" s="23">
-        <v>27863231</v>
-      </c>
-      <c r="E84" s="22" t="s">
-        <v>849</v>
-      </c>
-      <c r="F84" s="22" t="s">
-        <v>850</v>
-      </c>
-      <c r="G84" s="22" t="s">
+    <row r="84" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A84" s="12">
+        <v>46266.960023148145</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>853</v>
+      </c>
+      <c r="D84" s="14">
+        <v>16879698</v>
+      </c>
+      <c r="E84" s="15">
+        <v>23667</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>854</v>
+      </c>
+      <c r="G84" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H84" s="23">
-        <v>3382574927</v>
-      </c>
-      <c r="I84" s="22" t="s">
+      <c r="H84" s="13" t="s">
+        <v>855</v>
+      </c>
+      <c r="I84" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J84" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="K84" s="26"/>
-      <c r="L84" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="M84" s="22" t="s">
-        <v>851</v>
-      </c>
-      <c r="N84" s="22" t="s">
-        <v>852</v>
-      </c>
-      <c r="O84" s="25">
-        <v>37926</v>
-      </c>
-      <c r="P84" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q84" s="22" t="s">
+      <c r="J84" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>604</v>
+      </c>
+      <c r="L84" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="M84" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="N84" s="13" t="s">
+        <v>856</v>
+      </c>
+      <c r="O84" s="16">
+        <v>36528</v>
+      </c>
+      <c r="P84" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q84" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R84" s="23">
-        <v>46</v>
-      </c>
-      <c r="S84" s="23">
-        <v>40</v>
-      </c>
-      <c r="T84" s="22" t="s">
-        <v>853</v>
-      </c>
-      <c r="U84" s="25">
-        <v>31424</v>
-      </c>
-      <c r="V84" s="23">
-        <v>31970849</v>
-      </c>
-      <c r="W84" s="22" t="s">
-        <v>854</v>
-      </c>
-      <c r="X84" s="25">
-        <v>39530</v>
-      </c>
-      <c r="Y84" s="23">
-        <v>48063738</v>
-      </c>
-      <c r="Z84" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA84" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB84" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC84" s="22" t="s">
-        <v>855</v>
-      </c>
-      <c r="AD84" s="25">
-        <v>38154</v>
-      </c>
-      <c r="AE84" s="23">
-        <v>45827756</v>
-      </c>
-      <c r="AF84" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG84" s="22" t="s">
+      <c r="R84" s="14">
+        <v>48</v>
+      </c>
+      <c r="S84" s="14">
+        <v>43</v>
+      </c>
+      <c r="T84" s="13" t="s">
+        <v>857</v>
+      </c>
+      <c r="U84" s="16">
+        <v>23373</v>
+      </c>
+      <c r="V84" s="14">
+        <v>16628010</v>
+      </c>
+      <c r="W84" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="X84" s="16">
+        <v>45020</v>
+      </c>
+      <c r="Y84" s="14">
+        <v>44773323</v>
+      </c>
+      <c r="Z84" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA84" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB84" s="13" t="s">
+        <v>859</v>
+      </c>
+      <c r="AC84" s="17"/>
+      <c r="AD84" s="17"/>
+      <c r="AE84" s="17"/>
+      <c r="AF84" s="17"/>
+      <c r="AG84" s="17"/>
+      <c r="AH84" s="17"/>
+      <c r="AI84" s="17"/>
+      <c r="AJ84" s="17"/>
+      <c r="AK84" s="17"/>
+      <c r="AL84" s="17"/>
+      <c r="AM84" s="17"/>
+      <c r="AN84" s="17"/>
+      <c r="AO84" s="13" t="s">
+        <v>857</v>
+      </c>
+      <c r="AP84" s="14">
+        <v>16628010</v>
+      </c>
+      <c r="AQ84" s="17"/>
+      <c r="AR84" s="17"/>
+      <c r="AS84" s="17"/>
+      <c r="AT84" s="17"/>
+      <c r="AU84" s="18">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="85" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A85" s="37">
+        <v>46267.319907407407</v>
+      </c>
+      <c r="B85" s="38" t="s">
+        <v>861</v>
+      </c>
+      <c r="C85" s="38" t="s">
+        <v>862</v>
+      </c>
+      <c r="D85" s="39">
+        <v>31905593</v>
+      </c>
+      <c r="E85" s="40">
+        <v>31402</v>
+      </c>
+      <c r="F85" s="38" t="s">
+        <v>863</v>
+      </c>
+      <c r="G85" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H85" s="39">
+        <v>3382508883</v>
+      </c>
+      <c r="I85" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="J85" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="K85" s="41"/>
+      <c r="L85" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="AH84" s="22" t="s">
+      <c r="M85" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="N85" s="38" t="s">
+        <v>433</v>
+      </c>
+      <c r="O85" s="42">
+        <v>43800</v>
+      </c>
+      <c r="P85" s="38" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q85" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="R85" s="39">
+        <v>48</v>
+      </c>
+      <c r="S85" s="39">
+        <v>39</v>
+      </c>
+      <c r="T85" s="38" t="s">
+        <v>865</v>
+      </c>
+      <c r="U85" s="42">
+        <v>30952</v>
+      </c>
+      <c r="V85" s="39">
+        <v>31035889</v>
+      </c>
+      <c r="W85" s="38" t="s">
+        <v>866</v>
+      </c>
+      <c r="X85" s="42">
+        <v>36990</v>
+      </c>
+      <c r="Y85" s="39">
+        <v>43284819</v>
+      </c>
+      <c r="Z85" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA85" s="41"/>
+      <c r="AB85" s="41"/>
+      <c r="AC85" s="38" t="s">
+        <v>867</v>
+      </c>
+      <c r="AD85" s="42">
+        <v>38036</v>
+      </c>
+      <c r="AE85" s="39">
+        <v>45493137</v>
+      </c>
+      <c r="AF85" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG85" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH85" s="38" t="s">
+        <v>499</v>
+      </c>
+      <c r="AI85" s="38" t="s">
+        <v>868</v>
+      </c>
+      <c r="AJ85" s="42">
+        <v>38762</v>
+      </c>
+      <c r="AK85" s="39">
+        <v>46998246</v>
+      </c>
+      <c r="AL85" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM85" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN85" s="38" t="s">
+        <v>499</v>
+      </c>
+      <c r="AO85" s="38" t="s">
+        <v>866</v>
+      </c>
+      <c r="AP85" s="39">
+        <v>43284819</v>
+      </c>
+      <c r="AQ85" s="38" t="s">
+        <v>868</v>
+      </c>
+      <c r="AR85" s="39">
+        <v>46998246</v>
+      </c>
+      <c r="AS85" s="38" t="s">
+        <v>867</v>
+      </c>
+      <c r="AT85" s="39">
+        <v>45493137</v>
+      </c>
+      <c r="AU85" s="43">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="86" spans="1:47" ht="39" thickBot="1">
+      <c r="A86" s="21">
+        <v>46267.322500000002</v>
+      </c>
+      <c r="B86" s="22" t="s">
+        <v>869</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>870</v>
+      </c>
+      <c r="D86" s="23">
+        <v>37902957</v>
+      </c>
+      <c r="E86" s="24">
+        <v>34750</v>
+      </c>
+      <c r="F86" s="22" t="s">
+        <v>871</v>
+      </c>
+      <c r="G86" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H86" s="23">
+        <v>3382447170</v>
+      </c>
+      <c r="I86" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J86" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K86" s="26"/>
+      <c r="L86" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M86" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="N86" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="O86" s="25">
+        <v>44531</v>
+      </c>
+      <c r="P86" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q86" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="R86" s="23">
+        <v>50</v>
+      </c>
+      <c r="S86" s="23">
+        <v>37</v>
+      </c>
+      <c r="T86" s="26"/>
+      <c r="U86" s="26"/>
+      <c r="V86" s="26"/>
+      <c r="W86" s="26"/>
+      <c r="X86" s="26"/>
+      <c r="Y86" s="26"/>
+      <c r="Z86" s="26"/>
+      <c r="AA86" s="26"/>
+      <c r="AB86" s="26"/>
+      <c r="AC86" s="26"/>
+      <c r="AD86" s="26"/>
+      <c r="AE86" s="26"/>
+      <c r="AF86" s="26"/>
+      <c r="AG86" s="26"/>
+      <c r="AH86" s="26"/>
+      <c r="AI86" s="26"/>
+      <c r="AJ86" s="26"/>
+      <c r="AK86" s="26"/>
+      <c r="AL86" s="26"/>
+      <c r="AM86" s="26"/>
+      <c r="AN86" s="26"/>
+      <c r="AO86" s="22" t="s">
+        <v>873</v>
+      </c>
+      <c r="AP86" s="23">
+        <v>14934566</v>
+      </c>
+      <c r="AQ86" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="AR86" s="23">
+        <v>16879655</v>
+      </c>
+      <c r="AS86" s="26"/>
+      <c r="AT86" s="26"/>
+      <c r="AU86" s="27">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="87" spans="1:47" ht="77.25" thickBot="1">
+      <c r="A87" s="6">
+        <v>46267.328703703701</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="D87" s="8">
+        <v>26318862</v>
+      </c>
+      <c r="E87" s="9">
+        <v>28492</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H87" s="8">
+        <v>3382576242</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>878</v>
+      </c>
+      <c r="L87" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="AI84" s="26"/>
-      <c r="AJ84" s="26"/>
-      <c r="AK84" s="26"/>
-      <c r="AL84" s="26"/>
-      <c r="AM84" s="26"/>
-      <c r="AN84" s="26"/>
-      <c r="AO84" s="22" t="s">
-        <v>856</v>
-      </c>
-      <c r="AP84" s="23">
-        <v>27863231</v>
-      </c>
-      <c r="AQ84" s="26"/>
-      <c r="AR84" s="26"/>
-      <c r="AS84" s="26"/>
-      <c r="AT84" s="26"/>
-      <c r="AU84" s="27">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="85" spans="1:47" ht="51.75" thickBot="1">
-      <c r="A85" s="6">
-        <v>46266.940138888887</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>857</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="D85" s="8">
-        <v>24352357</v>
-      </c>
-      <c r="E85" s="9">
-        <v>27565</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>859</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>860</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J85" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K85" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="L85" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M85" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="N85" s="7" t="s">
-        <v>862</v>
-      </c>
-      <c r="O85" s="10">
-        <v>40544</v>
-      </c>
-      <c r="P85" s="8">
-        <v>42</v>
-      </c>
-      <c r="Q85" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="R85" s="8">
-        <v>44</v>
-      </c>
-      <c r="S85" s="8">
-        <v>43</v>
-      </c>
-      <c r="T85" s="7" t="s">
-        <v>863</v>
-      </c>
-      <c r="U85" s="10">
-        <v>30449</v>
-      </c>
-      <c r="V85" s="8">
-        <v>29931746</v>
-      </c>
-      <c r="W85" s="7" t="s">
-        <v>864</v>
-      </c>
-      <c r="X85" s="10">
-        <v>37504</v>
-      </c>
-      <c r="Y85" s="8">
-        <v>44067873</v>
-      </c>
-      <c r="Z85" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA85" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB85" s="7" t="s">
-        <v>865</v>
-      </c>
-      <c r="AC85" s="7" t="s">
-        <v>866</v>
-      </c>
-      <c r="AD85" s="10">
-        <v>38390</v>
-      </c>
-      <c r="AE85" s="8">
-        <v>46299657</v>
-      </c>
-      <c r="AF85" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG85" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH85" s="7" t="s">
-        <v>867</v>
-      </c>
-      <c r="AI85" s="7" t="s">
-        <v>868</v>
-      </c>
-      <c r="AJ85" s="10">
-        <v>40458</v>
-      </c>
-      <c r="AK85" s="8">
-        <v>50449155</v>
-      </c>
-      <c r="AL85" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM85" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN85" s="11"/>
-      <c r="AO85" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="AP85" s="8">
-        <v>24362357</v>
-      </c>
-      <c r="AQ85" s="11"/>
-      <c r="AR85" s="11"/>
-      <c r="AS85" s="11"/>
-      <c r="AT85" s="11"/>
-      <c r="AU85" s="28">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="86" spans="1:47" ht="51.75" thickBot="1">
-      <c r="A86" s="12">
-        <v>46266.960023148145</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>869</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>870</v>
-      </c>
-      <c r="D86" s="14">
-        <v>16879698</v>
-      </c>
-      <c r="E86" s="15">
-        <v>23667</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>871</v>
-      </c>
-      <c r="G86" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H86" s="13" t="s">
-        <v>872</v>
-      </c>
-      <c r="I86" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J86" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K86" s="13" t="s">
-        <v>604</v>
-      </c>
-      <c r="L86" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="M86" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="N86" s="13" t="s">
-        <v>873</v>
-      </c>
-      <c r="O86" s="16">
-        <v>36528</v>
-      </c>
-      <c r="P86" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q86" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="R86" s="14">
-        <v>48</v>
-      </c>
-      <c r="S86" s="14">
-        <v>43</v>
-      </c>
-      <c r="T86" s="13" t="s">
-        <v>874</v>
-      </c>
-      <c r="U86" s="16">
-        <v>23373</v>
-      </c>
-      <c r="V86" s="14">
-        <v>16628010</v>
-      </c>
-      <c r="W86" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="X86" s="16">
-        <v>45020</v>
-      </c>
-      <c r="Y86" s="14">
-        <v>44773323</v>
-      </c>
-      <c r="Z86" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA86" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB86" s="13" t="s">
-        <v>876</v>
-      </c>
-      <c r="AC86" s="17"/>
-      <c r="AD86" s="17"/>
-      <c r="AE86" s="17"/>
-      <c r="AF86" s="17"/>
-      <c r="AG86" s="17"/>
-      <c r="AH86" s="17"/>
-      <c r="AI86" s="17"/>
-      <c r="AJ86" s="17"/>
-      <c r="AK86" s="17"/>
-      <c r="AL86" s="17"/>
-      <c r="AM86" s="17"/>
-      <c r="AN86" s="17"/>
-      <c r="AO86" s="13" t="s">
-        <v>874</v>
-      </c>
-      <c r="AP86" s="14">
-        <v>16628010</v>
-      </c>
-      <c r="AQ86" s="17"/>
-      <c r="AR86" s="17"/>
-      <c r="AS86" s="17"/>
-      <c r="AT86" s="17"/>
-      <c r="AU86" s="18">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="87" spans="1:47" ht="26.25" thickBot="1">
-      <c r="A87" s="37">
-        <v>46267.319907407407</v>
-      </c>
-      <c r="B87" s="38" t="s">
-        <v>878</v>
-      </c>
-      <c r="C87" s="38" t="s">
+      <c r="M87" s="7" t="s">
         <v>879</v>
       </c>
-      <c r="D87" s="39">
-        <v>31905593</v>
-      </c>
-      <c r="E87" s="40">
-        <v>31402</v>
-      </c>
-      <c r="F87" s="38" t="s">
+      <c r="N87" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="O87" s="10">
+        <v>36101</v>
+      </c>
+      <c r="P87" s="7" t="s">
         <v>880</v>
       </c>
-      <c r="G87" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H87" s="39">
-        <v>3382508883</v>
-      </c>
-      <c r="I87" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="J87" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="K87" s="41"/>
-      <c r="L87" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="M87" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="N87" s="38" t="s">
-        <v>433</v>
-      </c>
-      <c r="O87" s="42">
-        <v>43800</v>
-      </c>
-      <c r="P87" s="38" t="s">
+      <c r="Q87" s="7" t="s">
+        <v>880</v>
+      </c>
+      <c r="R87" s="7" t="s">
         <v>881</v>
       </c>
-      <c r="Q87" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="R87" s="39">
-        <v>48</v>
-      </c>
-      <c r="S87" s="39">
+      <c r="S87" s="8">
         <v>39</v>
       </c>
-      <c r="T87" s="38" t="s">
+      <c r="T87" s="11"/>
+      <c r="U87" s="11"/>
+      <c r="V87" s="11"/>
+      <c r="W87" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="U87" s="42">
-        <v>30952</v>
-      </c>
-      <c r="V87" s="39">
-        <v>31035889</v>
-      </c>
-      <c r="W87" s="38" t="s">
+      <c r="X87" s="10">
+        <v>37692</v>
+      </c>
+      <c r="Y87" s="8">
+        <v>44773350</v>
+      </c>
+      <c r="Z87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC87" s="7" t="s">
         <v>883</v>
       </c>
-      <c r="X87" s="42">
-        <v>36990</v>
-      </c>
-      <c r="Y87" s="39">
-        <v>43284819</v>
-      </c>
-      <c r="Z87" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA87" s="41"/>
-      <c r="AB87" s="41"/>
-      <c r="AC87" s="38" t="s">
+      <c r="AD87" s="10">
+        <v>39397</v>
+      </c>
+      <c r="AE87" s="8">
+        <v>47779544</v>
+      </c>
+      <c r="AF87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH87" s="11"/>
+      <c r="AI87" s="11"/>
+      <c r="AJ87" s="11"/>
+      <c r="AK87" s="11"/>
+      <c r="AL87" s="11"/>
+      <c r="AM87" s="11"/>
+      <c r="AN87" s="11"/>
+      <c r="AO87" s="7" t="s">
         <v>884</v>
       </c>
-      <c r="AD87" s="42">
-        <v>38036</v>
-      </c>
-      <c r="AE87" s="39">
-        <v>45493137</v>
-      </c>
-      <c r="AF87" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG87" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH87" s="38" t="s">
-        <v>499</v>
-      </c>
-      <c r="AI87" s="38" t="s">
+      <c r="AP87" s="8">
+        <v>47779544</v>
+      </c>
+      <c r="AQ87" s="7" t="s">
         <v>885</v>
       </c>
-      <c r="AJ87" s="42">
-        <v>38762</v>
-      </c>
-      <c r="AK87" s="39">
-        <v>46998246</v>
-      </c>
-      <c r="AL87" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM87" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN87" s="38" t="s">
-        <v>499</v>
-      </c>
-      <c r="AO87" s="38" t="s">
-        <v>883</v>
-      </c>
-      <c r="AP87" s="39">
-        <v>43284819</v>
-      </c>
-      <c r="AQ87" s="38" t="s">
-        <v>885</v>
-      </c>
-      <c r="AR87" s="39">
-        <v>46998246</v>
-      </c>
-      <c r="AS87" s="38" t="s">
-        <v>884</v>
-      </c>
-      <c r="AT87" s="39">
-        <v>45493137</v>
-      </c>
-      <c r="AU87" s="43">
-        <v>475</v>
+      <c r="AR87" s="8">
+        <v>44773350</v>
+      </c>
+      <c r="AS87" s="11"/>
+      <c r="AT87" s="11"/>
+      <c r="AU87" s="29">
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:47" ht="39" thickBot="1">
       <c r="A88" s="21">
-        <v>46267.322500000002</v>
+        <v>46267.331782407404</v>
       </c>
       <c r="B88" s="22" t="s">
         <v>886</v>
@@ -14580,10 +14484,10 @@
         <v>887</v>
       </c>
       <c r="D88" s="23">
-        <v>37902957</v>
+        <v>26870693</v>
       </c>
       <c r="E88" s="24">
-        <v>34750</v>
+        <v>28809</v>
       </c>
       <c r="F88" s="22" t="s">
         <v>888</v>
@@ -14592,53 +14496,81 @@
         <v>30</v>
       </c>
       <c r="H88" s="23">
-        <v>3382447170</v>
+        <v>3382676481</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J88" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="K88" s="26"/>
+        <v>32</v>
+      </c>
+      <c r="K88" s="22" t="s">
+        <v>889</v>
+      </c>
       <c r="L88" s="22" t="s">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="M88" s="22" t="s">
-        <v>360</v>
+        <v>879</v>
       </c>
       <c r="N88" s="22" t="s">
-        <v>889</v>
+        <v>433</v>
       </c>
       <c r="O88" s="25">
-        <v>44531</v>
+        <v>38477</v>
       </c>
       <c r="P88" s="22" t="s">
-        <v>37</v>
+        <v>464</v>
       </c>
       <c r="Q88" s="22" t="s">
-        <v>37</v>
+        <v>464</v>
       </c>
       <c r="R88" s="23">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="S88" s="23">
         <v>37</v>
       </c>
-      <c r="T88" s="26"/>
-      <c r="U88" s="26"/>
-      <c r="V88" s="26"/>
-      <c r="W88" s="26"/>
-      <c r="X88" s="26"/>
-      <c r="Y88" s="26"/>
-      <c r="Z88" s="26"/>
+      <c r="T88" s="22" t="s">
+        <v>890</v>
+      </c>
+      <c r="U88" s="25">
+        <v>24667</v>
+      </c>
+      <c r="V88" s="23">
+        <v>17881776</v>
+      </c>
+      <c r="W88" s="22" t="s">
+        <v>891</v>
+      </c>
+      <c r="X88" s="25">
+        <v>28809</v>
+      </c>
+      <c r="Y88" s="23">
+        <v>26870693</v>
+      </c>
+      <c r="Z88" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="AA88" s="26"/>
-      <c r="AB88" s="26"/>
-      <c r="AC88" s="26"/>
-      <c r="AD88" s="26"/>
-      <c r="AE88" s="26"/>
-      <c r="AF88" s="26"/>
-      <c r="AG88" s="26"/>
+      <c r="AB88" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC88" s="22" t="s">
+        <v>892</v>
+      </c>
+      <c r="AD88" s="25">
+        <v>37357</v>
+      </c>
+      <c r="AE88" s="23">
+        <v>43843231</v>
+      </c>
+      <c r="AF88" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG88" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="AH88" s="26"/>
       <c r="AI88" s="26"/>
       <c r="AJ88" s="26"/>
@@ -14647,117 +14579,95 @@
       <c r="AM88" s="26"/>
       <c r="AN88" s="26"/>
       <c r="AO88" s="22" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AP88" s="23">
-        <v>14934566</v>
+        <v>43843231</v>
       </c>
       <c r="AQ88" s="22" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="AR88" s="23">
-        <v>16879655</v>
+        <v>53777121</v>
       </c>
       <c r="AS88" s="26"/>
       <c r="AT88" s="26"/>
       <c r="AU88" s="27">
-        <v>531</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:47" ht="77.25" thickBot="1">
+    <row r="89" spans="1:47" ht="51.75" thickBot="1">
       <c r="A89" s="6">
-        <v>46267.328703703701</v>
+        <v>46267.333715277775</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="D89" s="8">
-        <v>26318862</v>
+        <v>895</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>896</v>
       </c>
       <c r="E89" s="9">
-        <v>28492</v>
+        <v>30455</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H89" s="8">
-        <v>3382576242</v>
+        <v>3382677500</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="J89" s="7" t="s">
         <v>59</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="M89" s="7" t="s">
-        <v>896</v>
+        <v>310</v>
       </c>
       <c r="N89" s="7" t="s">
-        <v>433</v>
+        <v>899</v>
       </c>
       <c r="O89" s="10">
-        <v>36101</v>
-      </c>
-      <c r="P89" s="7" t="s">
-        <v>897</v>
+        <v>43800</v>
+      </c>
+      <c r="P89" s="8">
+        <v>40</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>897</v>
-      </c>
-      <c r="R89" s="7" t="s">
-        <v>898</v>
+        <v>304</v>
+      </c>
+      <c r="R89" s="8">
+        <v>42</v>
       </c>
       <c r="S89" s="8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="T89" s="11"/>
       <c r="U89" s="11"/>
       <c r="V89" s="11"/>
-      <c r="W89" s="7" t="s">
-        <v>899</v>
-      </c>
-      <c r="X89" s="10">
-        <v>37692</v>
-      </c>
-      <c r="Y89" s="8">
-        <v>44773350</v>
-      </c>
-      <c r="Z89" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA89" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB89" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC89" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="AD89" s="10">
-        <v>39397</v>
-      </c>
-      <c r="AE89" s="8">
-        <v>47779544</v>
-      </c>
-      <c r="AF89" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG89" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="W89" s="11"/>
+      <c r="X89" s="11"/>
+      <c r="Y89" s="11"/>
+      <c r="Z89" s="11"/>
+      <c r="AA89" s="11"/>
+      <c r="AB89" s="11"/>
+      <c r="AC89" s="11"/>
+      <c r="AD89" s="11"/>
+      <c r="AE89" s="11"/>
+      <c r="AF89" s="11"/>
+      <c r="AG89" s="11"/>
       <c r="AH89" s="11"/>
       <c r="AI89" s="11"/>
       <c r="AJ89" s="11"/>
@@ -14766,47 +14676,43 @@
       <c r="AM89" s="11"/>
       <c r="AN89" s="11"/>
       <c r="AO89" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="AP89" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="AP89" s="8">
-        <v>47779544</v>
-      </c>
-      <c r="AQ89" s="7" t="s">
-        <v>902</v>
-      </c>
-      <c r="AR89" s="8">
-        <v>44773350</v>
-      </c>
+      <c r="AQ89" s="11"/>
+      <c r="AR89" s="11"/>
       <c r="AS89" s="11"/>
       <c r="AT89" s="11"/>
-      <c r="AU89" s="29">
-        <v>62</v>
+      <c r="AU89" s="28">
+        <v>469</v>
       </c>
     </row>
     <row r="90" spans="1:47" ht="39" thickBot="1">
       <c r="A90" s="21">
-        <v>46267.331782407404</v>
+        <v>46267.345034722224</v>
       </c>
       <c r="B90" s="22" t="s">
+        <v>902</v>
+      </c>
+      <c r="C90" s="22" t="s">
         <v>903</v>
       </c>
-      <c r="C90" s="22" t="s">
+      <c r="D90" s="23">
+        <v>26207742</v>
+      </c>
+      <c r="E90" s="24">
+        <v>28551</v>
+      </c>
+      <c r="F90" s="22" t="s">
         <v>904</v>
-      </c>
-      <c r="D90" s="23">
-        <v>26870693</v>
-      </c>
-      <c r="E90" s="24">
-        <v>28809</v>
-      </c>
-      <c r="F90" s="22" t="s">
-        <v>905</v>
       </c>
       <c r="G90" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H90" s="23">
-        <v>3382676481</v>
+        <v>3382677239</v>
       </c>
       <c r="I90" s="22" t="s">
         <v>63</v>
@@ -14815,65 +14721,67 @@
         <v>32</v>
       </c>
       <c r="K90" s="22" t="s">
+        <v>905</v>
+      </c>
+      <c r="L90" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M90" s="22" t="s">
         <v>906</v>
       </c>
-      <c r="L90" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="M90" s="22" t="s">
-        <v>896</v>
-      </c>
       <c r="N90" s="22" t="s">
-        <v>433</v>
+        <v>251</v>
       </c>
       <c r="O90" s="25">
-        <v>38477</v>
-      </c>
-      <c r="P90" s="22" t="s">
-        <v>464</v>
+        <v>37377</v>
+      </c>
+      <c r="P90" s="23">
+        <v>36</v>
       </c>
       <c r="Q90" s="22" t="s">
-        <v>464</v>
+        <v>49</v>
       </c>
       <c r="R90" s="23">
+        <v>42</v>
+      </c>
+      <c r="S90" s="23">
         <v>36</v>
-      </c>
-      <c r="S90" s="23">
-        <v>37</v>
       </c>
       <c r="T90" s="22" t="s">
         <v>907</v>
       </c>
-      <c r="U90" s="25">
-        <v>24667</v>
+      <c r="U90" s="23" t="s">
+        <v>908</v>
       </c>
       <c r="V90" s="23">
-        <v>17881776</v>
+        <v>25773990</v>
       </c>
       <c r="W90" s="22" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="X90" s="25">
-        <v>28809</v>
+        <v>38057</v>
       </c>
       <c r="Y90" s="23">
-        <v>26870693</v>
+        <v>45508086</v>
       </c>
       <c r="Z90" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AA90" s="26"/>
+      <c r="AA90" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="AB90" s="22" t="s">
-        <v>40</v>
+        <v>910</v>
       </c>
       <c r="AC90" s="22" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="AD90" s="25">
-        <v>37357</v>
+        <v>39365</v>
       </c>
       <c r="AE90" s="23">
-        <v>43843231</v>
+        <v>47779509</v>
       </c>
       <c r="AF90" s="22" t="s">
         <v>40</v>
@@ -14881,7 +14789,9 @@
       <c r="AG90" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AH90" s="26"/>
+      <c r="AH90" s="22" t="s">
+        <v>912</v>
+      </c>
       <c r="AI90" s="26"/>
       <c r="AJ90" s="26"/>
       <c r="AK90" s="26"/>
@@ -14889,71 +14799,67 @@
       <c r="AM90" s="26"/>
       <c r="AN90" s="26"/>
       <c r="AO90" s="22" t="s">
-        <v>909</v>
-      </c>
-      <c r="AP90" s="23">
-        <v>43843231</v>
-      </c>
-      <c r="AQ90" s="22" t="s">
-        <v>910</v>
-      </c>
-      <c r="AR90" s="23">
-        <v>53777121</v>
-      </c>
+        <v>913</v>
+      </c>
+      <c r="AP90" s="22" t="s">
+        <v>913</v>
+      </c>
+      <c r="AQ90" s="26"/>
+      <c r="AR90" s="26"/>
       <c r="AS90" s="26"/>
       <c r="AT90" s="26"/>
       <c r="AU90" s="27">
-        <v>46</v>
+        <v>226</v>
       </c>
     </row>
     <row r="91" spans="1:47" ht="51.75" thickBot="1">
       <c r="A91" s="6">
-        <v>46267.333715277775</v>
+        <v>46267.351435185185</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E91" s="9">
-        <v>30455</v>
+        <v>24855</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="H91" s="8">
-        <v>3382677500</v>
+        <v>30</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>918</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J91" s="7" t="s">
         <v>59</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>915</v>
+        <v>236</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>341</v>
+        <v>230</v>
       </c>
       <c r="M91" s="7" t="s">
-        <v>310</v>
+        <v>879</v>
       </c>
       <c r="N91" s="7" t="s">
-        <v>916</v>
+        <v>433</v>
       </c>
       <c r="O91" s="10">
-        <v>43800</v>
-      </c>
-      <c r="P91" s="8">
-        <v>40</v>
+        <v>41804</v>
+      </c>
+      <c r="P91" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="Q91" s="7" t="s">
         <v>304</v>
@@ -14962,17 +14868,31 @@
         <v>42</v>
       </c>
       <c r="S91" s="8">
-        <v>41</v>
-      </c>
-      <c r="T91" s="11"/>
-      <c r="U91" s="11"/>
-      <c r="V91" s="11"/>
-      <c r="W91" s="11"/>
-      <c r="X91" s="11"/>
-      <c r="Y91" s="11"/>
+        <v>38</v>
+      </c>
+      <c r="T91" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="U91" s="10">
+        <v>22948</v>
+      </c>
+      <c r="V91" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="W91" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="X91" s="10">
+        <v>37325</v>
+      </c>
+      <c r="Y91" s="8" t="s">
+        <v>922</v>
+      </c>
       <c r="Z91" s="11"/>
       <c r="AA91" s="11"/>
-      <c r="AB91" s="11"/>
+      <c r="AB91" s="7" t="s">
+        <v>923</v>
+      </c>
       <c r="AC91" s="11"/>
       <c r="AD91" s="11"/>
       <c r="AE91" s="11"/>
@@ -14986,122 +14906,116 @@
       <c r="AM91" s="11"/>
       <c r="AN91" s="11"/>
       <c r="AO91" s="7" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="AP91" s="8" t="s">
-        <v>918</v>
-      </c>
-      <c r="AQ91" s="11"/>
-      <c r="AR91" s="11"/>
-      <c r="AS91" s="11"/>
-      <c r="AT91" s="11"/>
+        <v>922</v>
+      </c>
+      <c r="AQ91" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="AR91" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="AS91" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="AT91" s="8" t="s">
+        <v>920</v>
+      </c>
       <c r="AU91" s="28">
-        <v>469</v>
+        <v>535</v>
       </c>
     </row>
     <row r="92" spans="1:47" ht="39" thickBot="1">
       <c r="A92" s="21">
-        <v>46267.345034722224</v>
+        <v>46267.368414351855</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="D92" s="23">
-        <v>26207742</v>
+        <v>37902945</v>
       </c>
       <c r="E92" s="24">
-        <v>28551</v>
+        <v>34745</v>
       </c>
       <c r="F92" s="22" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="G92" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H92" s="23">
-        <v>3382677239</v>
+        <v>3382480954</v>
       </c>
       <c r="I92" s="22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="J92" s="22" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="K92" s="22" t="s">
-        <v>922</v>
+        <v>264</v>
       </c>
       <c r="L92" s="22" t="s">
-        <v>34</v>
+        <v>221</v>
       </c>
       <c r="M92" s="22" t="s">
-        <v>923</v>
+        <v>879</v>
       </c>
       <c r="N92" s="22" t="s">
         <v>251</v>
       </c>
       <c r="O92" s="25">
-        <v>37377</v>
+        <v>44531</v>
       </c>
       <c r="P92" s="23">
-        <v>36</v>
-      </c>
-      <c r="Q92" s="22" t="s">
-        <v>49</v>
+        <v>2</v>
+      </c>
+      <c r="Q92" s="23">
+        <v>2</v>
       </c>
       <c r="R92" s="23">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="S92" s="23">
         <v>36</v>
       </c>
       <c r="T92" s="22" t="s">
-        <v>924</v>
-      </c>
-      <c r="U92" s="23" t="s">
-        <v>925</v>
+        <v>930</v>
+      </c>
+      <c r="U92" s="25">
+        <v>36519</v>
       </c>
       <c r="V92" s="23">
-        <v>25773990</v>
+        <v>41654843</v>
       </c>
       <c r="W92" s="22" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="X92" s="25">
-        <v>38057</v>
+        <v>43836</v>
       </c>
       <c r="Y92" s="23">
-        <v>45508086</v>
+        <v>57460994</v>
       </c>
       <c r="Z92" s="22" t="s">
         <v>40</v>
       </c>
       <c r="AA92" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB92" s="22" t="s">
-        <v>927</v>
-      </c>
-      <c r="AC92" s="22" t="s">
-        <v>928</v>
-      </c>
-      <c r="AD92" s="25">
-        <v>39365</v>
-      </c>
-      <c r="AE92" s="23">
-        <v>47779509</v>
-      </c>
-      <c r="AF92" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG92" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH92" s="22" t="s">
-        <v>929</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="AB92" s="26"/>
+      <c r="AC92" s="26"/>
+      <c r="AD92" s="26"/>
+      <c r="AE92" s="26"/>
+      <c r="AF92" s="26"/>
+      <c r="AG92" s="26"/>
+      <c r="AH92" s="26"/>
       <c r="AI92" s="26"/>
       <c r="AJ92" s="26"/>
       <c r="AK92" s="26"/>
@@ -15109,34 +15023,34 @@
       <c r="AM92" s="26"/>
       <c r="AN92" s="26"/>
       <c r="AO92" s="22" t="s">
-        <v>930</v>
-      </c>
-      <c r="AP92" s="22" t="s">
-        <v>930</v>
+        <v>931</v>
+      </c>
+      <c r="AP92" s="23">
+        <v>57460994</v>
       </c>
       <c r="AQ92" s="26"/>
       <c r="AR92" s="26"/>
       <c r="AS92" s="26"/>
       <c r="AT92" s="26"/>
       <c r="AU92" s="27">
-        <v>226</v>
+        <v>523</v>
       </c>
     </row>
-    <row r="93" spans="1:47" ht="51.75" thickBot="1">
+    <row r="93" spans="1:47" ht="26.25" thickBot="1">
       <c r="A93" s="6">
-        <v>46267.351435185185</v>
+        <v>46267.401921296296</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>932</v>
-      </c>
-      <c r="D93" s="8" t="s">
         <v>933</v>
       </c>
+      <c r="D93" s="8">
+        <v>30623205</v>
+      </c>
       <c r="E93" s="9">
-        <v>24855</v>
+        <v>30838</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>934</v>
@@ -15144,8 +15058,8 @@
       <c r="G93" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H93" s="7" t="s">
-        <v>935</v>
+      <c r="H93" s="8">
+        <v>3382449200</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>63</v>
@@ -15153,20 +15067,18 @@
       <c r="J93" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K93" s="7" t="s">
-        <v>236</v>
-      </c>
+      <c r="K93" s="11"/>
       <c r="L93" s="7" t="s">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="M93" s="7" t="s">
-        <v>896</v>
+        <v>316</v>
       </c>
       <c r="N93" s="7" t="s">
-        <v>433</v>
+        <v>726</v>
       </c>
       <c r="O93" s="10">
-        <v>41804</v>
+        <v>38844</v>
       </c>
       <c r="P93" s="7" t="s">
         <v>304</v>
@@ -15178,31 +15090,31 @@
         <v>42</v>
       </c>
       <c r="S93" s="8">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="T93" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="U93" s="10">
+        <v>31450</v>
+      </c>
+      <c r="V93" s="8">
+        <v>32171175</v>
+      </c>
+      <c r="W93" s="7" t="s">
         <v>936</v>
       </c>
-      <c r="U93" s="10">
-        <v>22948</v>
-      </c>
-      <c r="V93" s="8" t="s">
-        <v>937</v>
-      </c>
-      <c r="W93" s="7" t="s">
-        <v>938</v>
-      </c>
       <c r="X93" s="10">
-        <v>37325</v>
-      </c>
-      <c r="Y93" s="8" t="s">
-        <v>939</v>
-      </c>
-      <c r="Z93" s="11"/>
+        <v>42450</v>
+      </c>
+      <c r="Y93" s="8">
+        <v>55403727</v>
+      </c>
+      <c r="Z93" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AA93" s="11"/>
-      <c r="AB93" s="7" t="s">
-        <v>940</v>
-      </c>
+      <c r="AB93" s="11"/>
       <c r="AC93" s="11"/>
       <c r="AD93" s="11"/>
       <c r="AE93" s="11"/>
@@ -15216,51 +15128,47 @@
       <c r="AM93" s="11"/>
       <c r="AN93" s="11"/>
       <c r="AO93" s="7" t="s">
-        <v>941</v>
-      </c>
-      <c r="AP93" s="8" t="s">
-        <v>939</v>
+        <v>937</v>
+      </c>
+      <c r="AP93" s="8">
+        <v>32171135</v>
       </c>
       <c r="AQ93" s="7" t="s">
-        <v>942</v>
-      </c>
-      <c r="AR93" s="8" t="s">
-        <v>943</v>
-      </c>
-      <c r="AS93" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="AT93" s="8" t="s">
-        <v>937</v>
-      </c>
+        <v>938</v>
+      </c>
+      <c r="AR93" s="8">
+        <v>55403727</v>
+      </c>
+      <c r="AS93" s="11"/>
+      <c r="AT93" s="11"/>
       <c r="AU93" s="28">
-        <v>535</v>
+        <v>292</v>
       </c>
     </row>
     <row r="94" spans="1:47" ht="39" thickBot="1">
       <c r="A94" s="21">
-        <v>46267.368414351855</v>
+        <v>46267.445509259262</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="D94" s="23">
-        <v>37902945</v>
+        <v>37902967</v>
       </c>
       <c r="E94" s="24">
-        <v>34745</v>
+        <v>34782</v>
       </c>
       <c r="F94" s="22" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>30</v>
+        <v>942</v>
       </c>
       <c r="H94" s="23">
-        <v>3382480954</v>
+        <v>3382505842</v>
       </c>
       <c r="I94" s="22" t="s">
         <v>58</v>
@@ -15268,26 +15176,24 @@
       <c r="J94" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="K94" s="22" t="s">
-        <v>264</v>
-      </c>
+      <c r="K94" s="26"/>
       <c r="L94" s="22" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="M94" s="22" t="s">
-        <v>896</v>
+        <v>943</v>
       </c>
       <c r="N94" s="22" t="s">
-        <v>251</v>
+        <v>583</v>
       </c>
       <c r="O94" s="25">
-        <v>44531</v>
-      </c>
-      <c r="P94" s="23">
-        <v>2</v>
-      </c>
-      <c r="Q94" s="23">
-        <v>2</v>
+        <v>44896</v>
+      </c>
+      <c r="P94" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q94" s="22" t="s">
+        <v>464</v>
       </c>
       <c r="R94" s="23">
         <v>38</v>
@@ -15296,28 +15202,24 @@
         <v>36</v>
       </c>
       <c r="T94" s="22" t="s">
-        <v>947</v>
-      </c>
-      <c r="U94" s="25">
-        <v>36519</v>
-      </c>
-      <c r="V94" s="23">
-        <v>41654843</v>
-      </c>
+        <v>944</v>
+      </c>
+      <c r="U94" s="26"/>
+      <c r="V94" s="26"/>
       <c r="W94" s="22" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="X94" s="25">
-        <v>43836</v>
+        <v>41433</v>
       </c>
       <c r="Y94" s="23">
-        <v>57460994</v>
+        <v>53269509</v>
       </c>
       <c r="Z94" s="22" t="s">
         <v>40</v>
       </c>
       <c r="AA94" s="22" t="s">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="AB94" s="26"/>
       <c r="AC94" s="26"/>
@@ -15333,96 +15235,84 @@
       <c r="AM94" s="26"/>
       <c r="AN94" s="26"/>
       <c r="AO94" s="22" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="AP94" s="23">
-        <v>57460994</v>
+        <v>16615259</v>
       </c>
       <c r="AQ94" s="26"/>
       <c r="AR94" s="26"/>
       <c r="AS94" s="26"/>
       <c r="AT94" s="26"/>
       <c r="AU94" s="27">
-        <v>523</v>
+        <v>576</v>
       </c>
     </row>
-    <row r="95" spans="1:47" ht="26.25" thickBot="1">
+    <row r="95" spans="1:47" ht="39" thickBot="1">
       <c r="A95" s="6">
-        <v>46267.401921296296</v>
+        <v>46267.544548611113</v>
       </c>
       <c r="B95" s="7" t="s">
+        <v>947</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>948</v>
+      </c>
+      <c r="D95" s="8">
+        <v>35250245</v>
+      </c>
+      <c r="E95" s="9">
+        <v>33154</v>
+      </c>
+      <c r="F95" s="7" t="s">
         <v>949</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>950</v>
-      </c>
-      <c r="D95" s="8">
-        <v>30623205</v>
-      </c>
-      <c r="E95" s="9">
-        <v>30838</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>951</v>
       </c>
       <c r="G95" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H95" s="8">
-        <v>3382449200</v>
+      <c r="H95" s="7" t="s">
+        <v>950</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K95" s="11"/>
+        <v>83</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>353</v>
+      </c>
       <c r="L95" s="7" t="s">
-        <v>34</v>
+        <v>951</v>
       </c>
       <c r="M95" s="7" t="s">
-        <v>316</v>
+        <v>706</v>
       </c>
       <c r="N95" s="7" t="s">
-        <v>726</v>
+        <v>952</v>
       </c>
       <c r="O95" s="10">
-        <v>38844</v>
-      </c>
-      <c r="P95" s="7" t="s">
-        <v>304</v>
+        <v>43800</v>
+      </c>
+      <c r="P95" s="8">
+        <v>42</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>304</v>
+        <v>233</v>
       </c>
       <c r="R95" s="8">
+        <v>44</v>
+      </c>
+      <c r="S95" s="8">
         <v>42</v>
       </c>
-      <c r="S95" s="8">
-        <v>41</v>
-      </c>
-      <c r="T95" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="U95" s="10">
-        <v>31450</v>
-      </c>
-      <c r="V95" s="8">
-        <v>32171175</v>
-      </c>
-      <c r="W95" s="7" t="s">
-        <v>953</v>
-      </c>
-      <c r="X95" s="10">
-        <v>42450</v>
-      </c>
-      <c r="Y95" s="8">
-        <v>55403727</v>
-      </c>
-      <c r="Z95" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="T95" s="11"/>
+      <c r="U95" s="11"/>
+      <c r="V95" s="11"/>
+      <c r="W95" s="11"/>
+      <c r="X95" s="11"/>
+      <c r="Y95" s="11"/>
+      <c r="Z95" s="11"/>
       <c r="AA95" s="11"/>
       <c r="AB95" s="11"/>
       <c r="AC95" s="11"/>
@@ -15438,833 +15328,855 @@
       <c r="AM95" s="11"/>
       <c r="AN95" s="11"/>
       <c r="AO95" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AP95" s="8">
-        <v>32171135</v>
-      </c>
-      <c r="AQ95" s="7" t="s">
-        <v>955</v>
-      </c>
-      <c r="AR95" s="8">
-        <v>55403727</v>
-      </c>
+        <v>20233218</v>
+      </c>
+      <c r="AQ95" s="11"/>
+      <c r="AR95" s="11"/>
       <c r="AS95" s="11"/>
       <c r="AT95" s="11"/>
       <c r="AU95" s="28">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="96" spans="1:47" ht="90" thickBot="1">
+      <c r="A96" s="6">
+        <v>46267.633715277778</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>955</v>
+      </c>
+      <c r="D96" s="8">
+        <v>32195807</v>
+      </c>
+      <c r="E96" s="9">
+        <v>31552</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="H96" s="8">
+        <v>3382579046</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K96" s="11"/>
+      <c r="L96" s="7" t="s">
+        <v>958</v>
+      </c>
+      <c r="M96" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="N96" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="O96" s="10">
+        <v>40575</v>
+      </c>
+      <c r="P96" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q96" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R96" s="8">
+        <v>42</v>
+      </c>
+      <c r="S96" s="8">
+        <v>39</v>
+      </c>
+      <c r="T96" s="11"/>
+      <c r="U96" s="11"/>
+      <c r="V96" s="11"/>
+      <c r="W96" s="11"/>
+      <c r="X96" s="11"/>
+      <c r="Y96" s="11"/>
+      <c r="Z96" s="11"/>
+      <c r="AA96" s="11"/>
+      <c r="AB96" s="11"/>
+      <c r="AC96" s="11"/>
+      <c r="AD96" s="11"/>
+      <c r="AE96" s="11"/>
+      <c r="AF96" s="11"/>
+      <c r="AG96" s="11"/>
+      <c r="AH96" s="11"/>
+      <c r="AI96" s="11"/>
+      <c r="AJ96" s="11"/>
+      <c r="AK96" s="11"/>
+      <c r="AL96" s="11"/>
+      <c r="AM96" s="11"/>
+      <c r="AN96" s="11"/>
+      <c r="AO96" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="AP96" s="8">
+        <v>36997389</v>
+      </c>
+      <c r="AQ96" s="11"/>
+      <c r="AR96" s="11"/>
+      <c r="AS96" s="11"/>
+      <c r="AT96" s="11"/>
+      <c r="AU96" s="28">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="97" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A97" s="21">
+        <v>46267.693356481483</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>961</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>962</v>
+      </c>
+      <c r="D97" s="23">
+        <v>24918176</v>
+      </c>
+      <c r="E97" s="25">
+        <v>27848</v>
+      </c>
+      <c r="F97" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="G97" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H97" s="23">
+        <v>406517</v>
+      </c>
+      <c r="I97" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J97" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K97" s="22" t="s">
+        <v>964</v>
+      </c>
+      <c r="L97" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="M97" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="N97" s="22" t="s">
+        <v>966</v>
+      </c>
+      <c r="O97" s="25">
+        <v>36395</v>
+      </c>
+      <c r="P97" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q97" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="R97" s="23">
+        <v>48</v>
+      </c>
+      <c r="S97" s="23">
+        <v>43</v>
+      </c>
+      <c r="T97" s="22" t="s">
+        <v>967</v>
+      </c>
+      <c r="U97" s="25">
+        <v>28571</v>
+      </c>
+      <c r="V97" s="23">
+        <v>26318956</v>
+      </c>
+      <c r="W97" s="22" t="s">
+        <v>968</v>
+      </c>
+      <c r="X97" s="25">
+        <v>40819</v>
+      </c>
+      <c r="Y97" s="23">
+        <v>51356911</v>
+      </c>
+      <c r="Z97" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA97" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB97" s="26"/>
+      <c r="AC97" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="AD97" s="25">
+        <v>43335</v>
+      </c>
+      <c r="AE97" s="23">
+        <v>56965095</v>
+      </c>
+      <c r="AF97" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG97" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH97" s="26"/>
+      <c r="AI97" s="26"/>
+      <c r="AJ97" s="26"/>
+      <c r="AK97" s="26"/>
+      <c r="AL97" s="26"/>
+      <c r="AM97" s="26"/>
+      <c r="AN97" s="26"/>
+      <c r="AO97" s="22" t="s">
+        <v>967</v>
+      </c>
+      <c r="AP97" s="23">
+        <v>26318956</v>
+      </c>
+      <c r="AQ97" s="22" t="s">
+        <v>968</v>
+      </c>
+      <c r="AR97" s="23">
+        <v>51356911</v>
+      </c>
+      <c r="AS97" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="AT97" s="23">
+        <v>56965095</v>
+      </c>
+      <c r="AU97" s="27">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="98" spans="1:47" ht="268.5" thickBot="1">
+      <c r="A98" s="6">
+        <v>46267.85565972222</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="D98" s="8">
+        <v>21767045</v>
+      </c>
+      <c r="E98" s="9">
+        <v>25967</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H98" s="8">
+        <v>3382412350</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K98" s="11"/>
+      <c r="L98" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="M98" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="N98" s="7" t="s">
+        <v>972</v>
+      </c>
+      <c r="O98" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P98" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q98" s="8">
+        <v>10</v>
+      </c>
+      <c r="R98" s="8">
+        <v>60</v>
+      </c>
+      <c r="S98" s="8">
+        <v>41</v>
+      </c>
+      <c r="T98" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="U98" s="10">
+        <v>25856</v>
+      </c>
+      <c r="V98" s="8">
+        <v>21534233</v>
+      </c>
+      <c r="W98" s="11"/>
+      <c r="X98" s="11"/>
+      <c r="Y98" s="11"/>
+      <c r="Z98" s="11"/>
+      <c r="AA98" s="11"/>
+      <c r="AB98" s="11"/>
+      <c r="AC98" s="11"/>
+      <c r="AD98" s="11"/>
+      <c r="AE98" s="11"/>
+      <c r="AF98" s="11"/>
+      <c r="AG98" s="11"/>
+      <c r="AH98" s="11"/>
+      <c r="AI98" s="11"/>
+      <c r="AJ98" s="11"/>
+      <c r="AK98" s="11"/>
+      <c r="AL98" s="11"/>
+      <c r="AM98" s="11"/>
+      <c r="AN98" s="11"/>
+      <c r="AO98" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="AP98" s="8">
+        <v>43843221</v>
+      </c>
+      <c r="AQ98" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="AR98" s="8">
+        <v>37902726</v>
+      </c>
+      <c r="AS98" s="7" t="s">
+        <v>975</v>
+      </c>
+      <c r="AT98" s="8">
+        <v>42127983</v>
+      </c>
+      <c r="AU98" s="28">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="99" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A99" s="21">
+        <v>46267.866631944446</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>976</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>977</v>
+      </c>
+      <c r="D99" s="23" t="s">
+        <v>978</v>
+      </c>
+      <c r="E99" s="24">
+        <v>28718</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>979</v>
+      </c>
+      <c r="G99" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99" s="23">
+        <v>3382670588</v>
+      </c>
+      <c r="I99" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J99" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K99" s="26"/>
+      <c r="L99" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="M99" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="N99" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="O99" s="25">
+        <v>36535</v>
+      </c>
+      <c r="P99" s="23">
+        <v>60</v>
+      </c>
+      <c r="Q99" s="44">
+        <v>46304</v>
+      </c>
+      <c r="R99" s="23">
+        <v>58</v>
+      </c>
+      <c r="S99" s="22" t="s">
+        <v>981</v>
+      </c>
+      <c r="T99" s="22" t="s">
+        <v>982</v>
+      </c>
+      <c r="U99" s="25">
+        <v>27155</v>
+      </c>
+      <c r="V99" s="23">
+        <v>23667798</v>
+      </c>
+      <c r="W99" s="22" t="s">
+        <v>983</v>
+      </c>
+      <c r="X99" s="25">
+        <v>36347</v>
+      </c>
+      <c r="Y99" s="23">
+        <v>41654681</v>
+      </c>
+      <c r="Z99" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA99" s="26"/>
+      <c r="AB99" s="26"/>
+      <c r="AC99" s="26"/>
+      <c r="AD99" s="26"/>
+      <c r="AE99" s="26"/>
+      <c r="AF99" s="26"/>
+      <c r="AG99" s="26"/>
+      <c r="AH99" s="26"/>
+      <c r="AI99" s="26"/>
+      <c r="AJ99" s="26"/>
+      <c r="AK99" s="26"/>
+      <c r="AL99" s="26"/>
+      <c r="AM99" s="26"/>
+      <c r="AN99" s="26"/>
+      <c r="AO99" s="22" t="s">
+        <v>982</v>
+      </c>
+      <c r="AP99" s="23">
+        <v>23667798</v>
+      </c>
+      <c r="AQ99" s="22" t="s">
+        <v>984</v>
+      </c>
+      <c r="AR99" s="23">
+        <v>41654681</v>
+      </c>
+      <c r="AS99" s="22" t="s">
+        <v>985</v>
+      </c>
+      <c r="AT99" s="23">
+        <v>37902946</v>
+      </c>
+      <c r="AU99" s="27">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="100" spans="1:47" ht="39" thickBot="1">
+      <c r="A100" s="6">
+        <v>46267.902268518519</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>986</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>987</v>
+      </c>
+      <c r="D100" s="8">
+        <v>37295744</v>
+      </c>
+      <c r="E100" s="9">
+        <v>34379</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H100" s="8">
+        <v>3382506150</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K100" s="11"/>
+      <c r="L100" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M100" s="7" t="s">
+        <v>989</v>
+      </c>
+      <c r="N100" s="7" t="s">
+        <v>990</v>
+      </c>
+      <c r="O100" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P100" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q100" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="R100" s="8">
+        <v>40</v>
+      </c>
+      <c r="S100" s="8">
+        <v>40</v>
+      </c>
+      <c r="T100" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="U100" s="10">
+        <v>36667</v>
+      </c>
+      <c r="V100" s="8">
+        <v>42127944</v>
+      </c>
+      <c r="W100" s="7" t="s">
+        <v>992</v>
+      </c>
+      <c r="X100" s="10">
+        <v>41396</v>
+      </c>
+      <c r="Y100" s="8">
+        <v>53180910</v>
+      </c>
+      <c r="Z100" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA100" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB100" s="11"/>
+      <c r="AC100" s="11"/>
+      <c r="AD100" s="11"/>
+      <c r="AE100" s="11"/>
+      <c r="AF100" s="11"/>
+      <c r="AG100" s="11"/>
+      <c r="AH100" s="11"/>
+      <c r="AI100" s="11"/>
+      <c r="AJ100" s="11"/>
+      <c r="AK100" s="11"/>
+      <c r="AL100" s="11"/>
+      <c r="AM100" s="11"/>
+      <c r="AN100" s="11"/>
+      <c r="AO100" s="7" t="s">
+        <v>993</v>
+      </c>
+      <c r="AP100" s="8">
+        <v>53180910</v>
+      </c>
+      <c r="AQ100" s="11"/>
+      <c r="AR100" s="11"/>
+      <c r="AS100" s="11"/>
+      <c r="AT100" s="11"/>
+      <c r="AU100" s="28">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="101" spans="1:47" ht="39" thickBot="1">
+      <c r="A101" s="12">
+        <v>46268.024733796294</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="D101" s="14">
+        <v>34175564</v>
+      </c>
+      <c r="E101" s="15">
+        <v>32752</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="G101" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H101" s="14">
+        <v>3382406506</v>
+      </c>
+      <c r="I101" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J101" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="K101" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="L101" s="13" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="96" spans="1:47" ht="39" thickBot="1">
-      <c r="A96" s="21">
-        <v>46267.445509259262</v>
-      </c>
-      <c r="B96" s="22" t="s">
-        <v>956</v>
-      </c>
-      <c r="C96" s="22" t="s">
-        <v>957</v>
-      </c>
-      <c r="D96" s="23">
-        <v>37902967</v>
-      </c>
-      <c r="E96" s="24">
-        <v>34782</v>
-      </c>
-      <c r="F96" s="22" t="s">
-        <v>958</v>
-      </c>
-      <c r="G96" s="22" t="s">
-        <v>959</v>
-      </c>
-      <c r="H96" s="23">
-        <v>3382505842</v>
-      </c>
-      <c r="I96" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J96" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="K96" s="26"/>
-      <c r="L96" s="22" t="s">
+      <c r="M101" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="N101" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="O101" s="16">
+        <v>44531</v>
+      </c>
+      <c r="P101" s="14">
+        <v>44</v>
+      </c>
+      <c r="Q101" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="R101" s="14">
+        <v>50</v>
+      </c>
+      <c r="S101" s="14">
+        <v>45</v>
+      </c>
+      <c r="T101" s="17"/>
+      <c r="U101" s="17"/>
+      <c r="V101" s="17"/>
+      <c r="W101" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="X101" s="16">
+        <v>42619</v>
+      </c>
+      <c r="Y101" s="14">
+        <v>55798119</v>
+      </c>
+      <c r="Z101" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA101" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="M96" s="22" t="s">
-        <v>960</v>
-      </c>
-      <c r="N96" s="22" t="s">
-        <v>583</v>
-      </c>
-      <c r="O96" s="25">
-        <v>44896</v>
-      </c>
-      <c r="P96" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="Q96" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="R96" s="23">
-        <v>38</v>
-      </c>
-      <c r="S96" s="23">
-        <v>36</v>
-      </c>
-      <c r="T96" s="22" t="s">
-        <v>961</v>
-      </c>
-      <c r="U96" s="26"/>
-      <c r="V96" s="26"/>
-      <c r="W96" s="22" t="s">
-        <v>962</v>
-      </c>
-      <c r="X96" s="25">
-        <v>41433</v>
-      </c>
-      <c r="Y96" s="23">
-        <v>53269509</v>
-      </c>
-      <c r="Z96" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA96" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB96" s="26"/>
-      <c r="AC96" s="26"/>
-      <c r="AD96" s="26"/>
-      <c r="AE96" s="26"/>
-      <c r="AF96" s="26"/>
-      <c r="AG96" s="26"/>
-      <c r="AH96" s="26"/>
-      <c r="AI96" s="26"/>
-      <c r="AJ96" s="26"/>
-      <c r="AK96" s="26"/>
-      <c r="AL96" s="26"/>
-      <c r="AM96" s="26"/>
-      <c r="AN96" s="26"/>
-      <c r="AO96" s="22" t="s">
-        <v>963</v>
-      </c>
-      <c r="AP96" s="23">
-        <v>16615259</v>
-      </c>
-      <c r="AQ96" s="26"/>
-      <c r="AR96" s="26"/>
-      <c r="AS96" s="26"/>
-      <c r="AT96" s="26"/>
-      <c r="AU96" s="27">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="97" spans="1:47" ht="39" thickBot="1">
-      <c r="A97" s="6">
-        <v>46267.544548611113</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>965</v>
-      </c>
-      <c r="D97" s="8">
-        <v>35250245</v>
-      </c>
-      <c r="E97" s="9">
-        <v>33154</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>966</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>967</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="L97" s="7" t="s">
-        <v>968</v>
-      </c>
-      <c r="M97" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="N97" s="7" t="s">
-        <v>969</v>
-      </c>
-      <c r="O97" s="10">
-        <v>43800</v>
-      </c>
-      <c r="P97" s="8">
-        <v>42</v>
-      </c>
-      <c r="Q97" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="R97" s="8">
-        <v>44</v>
-      </c>
-      <c r="S97" s="8">
-        <v>42</v>
-      </c>
-      <c r="T97" s="11"/>
-      <c r="U97" s="11"/>
-      <c r="V97" s="11"/>
-      <c r="W97" s="11"/>
-      <c r="X97" s="11"/>
-      <c r="Y97" s="11"/>
-      <c r="Z97" s="11"/>
-      <c r="AA97" s="11"/>
-      <c r="AB97" s="11"/>
-      <c r="AC97" s="11"/>
-      <c r="AD97" s="11"/>
-      <c r="AE97" s="11"/>
-      <c r="AF97" s="11"/>
-      <c r="AG97" s="11"/>
-      <c r="AH97" s="11"/>
-      <c r="AI97" s="11"/>
-      <c r="AJ97" s="11"/>
-      <c r="AK97" s="11"/>
-      <c r="AL97" s="11"/>
-      <c r="AM97" s="11"/>
-      <c r="AN97" s="11"/>
-      <c r="AO97" s="7" t="s">
-        <v>970</v>
-      </c>
-      <c r="AP97" s="8">
-        <v>20233218</v>
-      </c>
-      <c r="AQ97" s="11"/>
-      <c r="AR97" s="11"/>
-      <c r="AS97" s="11"/>
-      <c r="AT97" s="11"/>
-      <c r="AU97" s="28">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="98" spans="1:47" ht="26.25" thickBot="1">
-      <c r="A98" s="21">
-        <v>46267.600081018521</v>
-      </c>
-      <c r="B98" s="22" t="s">
-        <v>971</v>
-      </c>
-      <c r="C98" s="22" t="s">
-        <v>972</v>
-      </c>
-      <c r="D98" s="23">
-        <v>40277764</v>
-      </c>
-      <c r="E98" s="24">
-        <v>35823</v>
-      </c>
-      <c r="F98" s="22" t="s">
-        <v>973</v>
-      </c>
-      <c r="G98" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H98" s="23">
-        <v>3382462643</v>
-      </c>
-      <c r="I98" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J98" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="K98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="L98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="M98" s="22" t="s">
-        <v>851</v>
-      </c>
-      <c r="N98" s="22" t="s">
-        <v>974</v>
-      </c>
-      <c r="O98" s="25">
-        <v>46267</v>
-      </c>
-      <c r="P98" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q98" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="R98" s="23">
-        <v>40</v>
-      </c>
-      <c r="S98" s="23">
-        <v>41</v>
-      </c>
-      <c r="T98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="U98" s="26"/>
-      <c r="V98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="W98" s="26"/>
-      <c r="X98" s="26"/>
-      <c r="Y98" s="26"/>
-      <c r="Z98" s="26"/>
-      <c r="AA98" s="26"/>
-      <c r="AB98" s="26"/>
-      <c r="AC98" s="26"/>
-      <c r="AD98" s="26"/>
-      <c r="AE98" s="26"/>
-      <c r="AF98" s="26"/>
-      <c r="AG98" s="26"/>
-      <c r="AH98" s="26"/>
-      <c r="AI98" s="26"/>
-      <c r="AJ98" s="26"/>
-      <c r="AK98" s="26"/>
-      <c r="AL98" s="26"/>
-      <c r="AM98" s="26"/>
-      <c r="AN98" s="26"/>
-      <c r="AO98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="AP98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="AR98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="AS98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="AT98" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="AU98" s="27">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="99" spans="1:47" ht="90" thickBot="1">
-      <c r="A99" s="6">
-        <v>46267.633715277778</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>975</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>976</v>
-      </c>
-      <c r="D99" s="8">
-        <v>32195807</v>
-      </c>
-      <c r="E99" s="9">
-        <v>31552</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>977</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>978</v>
-      </c>
-      <c r="H99" s="8">
-        <v>3382579046</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K99" s="11"/>
-      <c r="L99" s="7" t="s">
-        <v>979</v>
-      </c>
-      <c r="M99" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="N99" s="7" t="s">
-        <v>980</v>
-      </c>
-      <c r="O99" s="10">
-        <v>40575</v>
-      </c>
-      <c r="P99" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q99" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="R99" s="8">
-        <v>42</v>
-      </c>
-      <c r="S99" s="8">
-        <v>39</v>
-      </c>
-      <c r="T99" s="11"/>
-      <c r="U99" s="11"/>
-      <c r="V99" s="11"/>
-      <c r="W99" s="11"/>
-      <c r="X99" s="11"/>
-      <c r="Y99" s="11"/>
-      <c r="Z99" s="11"/>
-      <c r="AA99" s="11"/>
-      <c r="AB99" s="11"/>
-      <c r="AC99" s="11"/>
-      <c r="AD99" s="11"/>
-      <c r="AE99" s="11"/>
-      <c r="AF99" s="11"/>
-      <c r="AG99" s="11"/>
-      <c r="AH99" s="11"/>
-      <c r="AI99" s="11"/>
-      <c r="AJ99" s="11"/>
-      <c r="AK99" s="11"/>
-      <c r="AL99" s="11"/>
-      <c r="AM99" s="11"/>
-      <c r="AN99" s="11"/>
-      <c r="AO99" s="7" t="s">
-        <v>981</v>
-      </c>
-      <c r="AP99" s="8">
-        <v>36997389</v>
-      </c>
-      <c r="AQ99" s="11"/>
-      <c r="AR99" s="11"/>
-      <c r="AS99" s="11"/>
-      <c r="AT99" s="11"/>
-      <c r="AU99" s="28">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="100" spans="1:47" ht="51.75" thickBot="1">
-      <c r="A100" s="21">
-        <v>46267.693356481483</v>
-      </c>
-      <c r="B100" s="22" t="s">
-        <v>982</v>
-      </c>
-      <c r="C100" s="22" t="s">
-        <v>983</v>
-      </c>
-      <c r="D100" s="23">
-        <v>24918176</v>
-      </c>
-      <c r="E100" s="25">
-        <v>27848</v>
-      </c>
-      <c r="F100" s="22" t="s">
-        <v>984</v>
-      </c>
-      <c r="G100" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H100" s="23">
-        <v>406517</v>
-      </c>
-      <c r="I100" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J100" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="K100" s="22" t="s">
-        <v>985</v>
-      </c>
-      <c r="L100" s="22" t="s">
-        <v>986</v>
-      </c>
-      <c r="M100" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="N100" s="22" t="s">
-        <v>987</v>
-      </c>
-      <c r="O100" s="25">
-        <v>36395</v>
-      </c>
-      <c r="P100" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q100" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="R100" s="23">
-        <v>48</v>
-      </c>
-      <c r="S100" s="23">
-        <v>43</v>
-      </c>
-      <c r="T100" s="22" t="s">
-        <v>988</v>
-      </c>
-      <c r="U100" s="25">
-        <v>28571</v>
-      </c>
-      <c r="V100" s="23">
-        <v>26318956</v>
-      </c>
-      <c r="W100" s="22" t="s">
-        <v>989</v>
-      </c>
-      <c r="X100" s="25">
-        <v>40819</v>
-      </c>
-      <c r="Y100" s="23">
-        <v>51356911</v>
-      </c>
-      <c r="Z100" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA100" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB100" s="26"/>
-      <c r="AC100" s="22" t="s">
-        <v>990</v>
-      </c>
-      <c r="AD100" s="25">
-        <v>43335</v>
-      </c>
-      <c r="AE100" s="23">
-        <v>56965095</v>
-      </c>
-      <c r="AF100" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG100" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AH100" s="26"/>
-      <c r="AI100" s="26"/>
-      <c r="AJ100" s="26"/>
-      <c r="AK100" s="26"/>
-      <c r="AL100" s="26"/>
-      <c r="AM100" s="26"/>
-      <c r="AN100" s="26"/>
-      <c r="AO100" s="22" t="s">
-        <v>988</v>
-      </c>
-      <c r="AP100" s="23">
-        <v>26318956</v>
-      </c>
-      <c r="AQ100" s="22" t="s">
-        <v>989</v>
-      </c>
-      <c r="AR100" s="23">
-        <v>51356911</v>
-      </c>
-      <c r="AS100" s="22" t="s">
-        <v>990</v>
-      </c>
-      <c r="AT100" s="23">
-        <v>56965095</v>
-      </c>
-      <c r="AU100" s="27">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="101" spans="1:47" ht="268.5" thickBot="1">
-      <c r="A101" s="6">
-        <v>46267.85565972222</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>790</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="D101" s="8">
-        <v>21767045</v>
-      </c>
-      <c r="E101" s="9">
-        <v>25967</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>991</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H101" s="8">
-        <v>3382412350</v>
-      </c>
-      <c r="I101" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K101" s="11"/>
-      <c r="L101" s="7" t="s">
-        <v>793</v>
-      </c>
-      <c r="M101" s="7" t="s">
-        <v>992</v>
-      </c>
-      <c r="N101" s="7" t="s">
-        <v>993</v>
-      </c>
-      <c r="O101" s="10">
-        <v>43800</v>
-      </c>
-      <c r="P101" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="Q101" s="8">
-        <v>10</v>
-      </c>
-      <c r="R101" s="8">
-        <v>60</v>
-      </c>
-      <c r="S101" s="8">
-        <v>41</v>
-      </c>
-      <c r="T101" s="7" t="s">
-        <v>797</v>
-      </c>
-      <c r="U101" s="10">
-        <v>25856</v>
-      </c>
-      <c r="V101" s="8">
-        <v>21534233</v>
-      </c>
-      <c r="W101" s="11"/>
-      <c r="X101" s="11"/>
-      <c r="Y101" s="11"/>
-      <c r="Z101" s="11"/>
-      <c r="AA101" s="11"/>
-      <c r="AB101" s="11"/>
-      <c r="AC101" s="11"/>
-      <c r="AD101" s="11"/>
-      <c r="AE101" s="11"/>
-      <c r="AF101" s="11"/>
-      <c r="AG101" s="11"/>
-      <c r="AH101" s="11"/>
-      <c r="AI101" s="11"/>
-      <c r="AJ101" s="11"/>
-      <c r="AK101" s="11"/>
-      <c r="AL101" s="11"/>
-      <c r="AM101" s="11"/>
-      <c r="AN101" s="11"/>
-      <c r="AO101" s="7" t="s">
-        <v>994</v>
-      </c>
-      <c r="AP101" s="8">
-        <v>43843221</v>
-      </c>
-      <c r="AQ101" s="7" t="s">
-        <v>995</v>
-      </c>
-      <c r="AR101" s="8">
-        <v>37902726</v>
-      </c>
-      <c r="AS101" s="7" t="s">
-        <v>996</v>
-      </c>
-      <c r="AT101" s="8">
-        <v>42127983</v>
-      </c>
-      <c r="AU101" s="28">
-        <v>465</v>
+      <c r="AB101" s="17"/>
+      <c r="AC101" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="AD101" s="16">
+        <v>44590</v>
+      </c>
+      <c r="AE101" s="14">
+        <v>59103651</v>
+      </c>
+      <c r="AF101" s="17"/>
+      <c r="AG101" s="17"/>
+      <c r="AH101" s="17"/>
+      <c r="AI101" s="17"/>
+      <c r="AJ101" s="17"/>
+      <c r="AK101" s="17"/>
+      <c r="AL101" s="17"/>
+      <c r="AM101" s="17"/>
+      <c r="AN101" s="17"/>
+      <c r="AO101" s="13" t="s">
+        <v>999</v>
+      </c>
+      <c r="AP101" s="14">
+        <v>39049433</v>
+      </c>
+      <c r="AQ101" s="17"/>
+      <c r="AR101" s="17"/>
+      <c r="AS101" s="17"/>
+      <c r="AT101" s="17"/>
+      <c r="AU101" s="18">
+        <v>512</v>
       </c>
     </row>
     <row r="102" spans="1:47" ht="26.25" thickBot="1">
-      <c r="A102" s="21">
-        <v>46267.866631944446</v>
-      </c>
-      <c r="B102" s="22" t="s">
-        <v>997</v>
-      </c>
-      <c r="C102" s="22" t="s">
-        <v>998</v>
-      </c>
-      <c r="D102" s="23" t="s">
-        <v>999</v>
-      </c>
-      <c r="E102" s="24">
-        <v>28718</v>
-      </c>
-      <c r="F102" s="22" t="s">
+      <c r="A102" s="45">
+        <v>46268.375891203701</v>
+      </c>
+      <c r="B102" s="46" t="s">
         <v>1000</v>
       </c>
-      <c r="G102" s="22" t="s">
+      <c r="C102" s="46" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D102" s="47">
+        <v>36421488</v>
+      </c>
+      <c r="E102" s="48">
+        <v>33677</v>
+      </c>
+      <c r="F102" s="46" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G102" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="H102" s="23">
-        <v>3382670588</v>
-      </c>
-      <c r="I102" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="J102" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="K102" s="26"/>
-      <c r="L102" s="22" t="s">
-        <v>509</v>
-      </c>
-      <c r="M102" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="N102" s="22" t="s">
-        <v>1001</v>
-      </c>
-      <c r="O102" s="25">
-        <v>36535</v>
-      </c>
-      <c r="P102" s="23">
-        <v>60</v>
-      </c>
-      <c r="Q102" s="44">
-        <v>46304</v>
-      </c>
-      <c r="R102" s="23">
+      <c r="H102" s="47">
+        <v>3382481763</v>
+      </c>
+      <c r="I102" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="S102" s="22" t="s">
-        <v>1002</v>
-      </c>
-      <c r="T102" s="22" t="s">
+      <c r="J102" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="K102" s="49"/>
+      <c r="L102" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="M102" s="46" t="s">
         <v>1003</v>
       </c>
-      <c r="U102" s="25">
-        <v>27155</v>
-      </c>
-      <c r="V102" s="23">
-        <v>23667798</v>
-      </c>
-      <c r="W102" s="22" t="s">
+      <c r="N102" s="46" t="s">
         <v>1004</v>
       </c>
-      <c r="X102" s="25">
-        <v>36347</v>
-      </c>
-      <c r="Y102" s="23">
-        <v>41654681</v>
-      </c>
-      <c r="Z102" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA102" s="26"/>
-      <c r="AB102" s="26"/>
-      <c r="AC102" s="26"/>
-      <c r="AD102" s="26"/>
-      <c r="AE102" s="26"/>
-      <c r="AF102" s="26"/>
-      <c r="AG102" s="26"/>
-      <c r="AH102" s="26"/>
-      <c r="AI102" s="26"/>
-      <c r="AJ102" s="26"/>
-      <c r="AK102" s="26"/>
-      <c r="AL102" s="26"/>
-      <c r="AM102" s="26"/>
-      <c r="AN102" s="26"/>
-      <c r="AO102" s="22" t="s">
-        <v>1003</v>
-      </c>
-      <c r="AP102" s="23">
-        <v>23667798</v>
-      </c>
-      <c r="AQ102" s="22" t="s">
+      <c r="O102" s="50">
+        <v>46268</v>
+      </c>
+      <c r="P102" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q102" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="R102" s="47">
+        <v>44</v>
+      </c>
+      <c r="S102" s="47">
+        <v>43</v>
+      </c>
+      <c r="T102" s="49"/>
+      <c r="U102" s="49"/>
+      <c r="V102" s="49"/>
+      <c r="W102" s="46" t="s">
         <v>1005</v>
       </c>
-      <c r="AR102" s="23">
-        <v>41654681</v>
-      </c>
-      <c r="AS102" s="22" t="s">
+      <c r="X102" s="50">
+        <v>42688</v>
+      </c>
+      <c r="Y102" s="47">
+        <v>55718259</v>
+      </c>
+      <c r="Z102" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA102" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB102" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC102" s="46" t="s">
         <v>1006</v>
       </c>
-      <c r="AT102" s="23">
-        <v>37902946</v>
-      </c>
-      <c r="AU102" s="27">
-        <v>298</v>
+      <c r="AD102" s="50">
+        <v>43641</v>
+      </c>
+      <c r="AE102" s="47">
+        <v>57460864</v>
+      </c>
+      <c r="AF102" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG102" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH102" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI102" s="49"/>
+      <c r="AJ102" s="49"/>
+      <c r="AK102" s="49"/>
+      <c r="AL102" s="49"/>
+      <c r="AM102" s="49"/>
+      <c r="AN102" s="49"/>
+      <c r="AO102" s="46" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AP102" s="47">
+        <v>16628087</v>
+      </c>
+      <c r="AQ102" s="49"/>
+      <c r="AR102" s="49"/>
+      <c r="AS102" s="49"/>
+      <c r="AT102" s="49"/>
+      <c r="AU102" s="51">
+        <v>447</v>
       </c>
     </row>
     <row r="103" spans="1:47" ht="39" thickBot="1">
       <c r="A103" s="6">
-        <v>46267.902268518519</v>
+        <v>46268.520219907405</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D103" s="8">
-        <v>37295744</v>
+        <v>16370636</v>
       </c>
       <c r="E103" s="9">
-        <v>34379</v>
+        <v>23246</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G103" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H103" s="8">
-        <v>3382506150</v>
+        <v>3382454153</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>58</v>
+        <v>1011</v>
       </c>
       <c r="J103" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K103" s="11"/>
+      <c r="K103" s="7" t="s">
+        <v>450</v>
+      </c>
       <c r="L103" s="7" t="s">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="M103" s="7" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="N103" s="7" t="s">
-        <v>1011</v>
+        <v>451</v>
       </c>
       <c r="O103" s="10">
-        <v>43800</v>
+        <v>44531</v>
       </c>
       <c r="P103" s="7" t="s">
-        <v>464</v>
+        <v>233</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>464</v>
+        <v>233</v>
       </c>
       <c r="R103" s="8">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="S103" s="8">
-        <v>40</v>
-      </c>
-      <c r="T103" s="7" t="s">
-        <v>1012</v>
-      </c>
-      <c r="U103" s="10">
-        <v>36667</v>
-      </c>
-      <c r="V103" s="8">
-        <v>42127944</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="T103" s="11"/>
+      <c r="U103" s="11"/>
+      <c r="V103" s="11"/>
       <c r="W103" s="7" t="s">
         <v>1013</v>
       </c>
       <c r="X103" s="10">
-        <v>41396</v>
+        <v>29943</v>
       </c>
       <c r="Y103" s="8">
-        <v>53180910</v>
+        <v>29562033</v>
       </c>
       <c r="Z103" s="7" t="s">
         <v>40</v>
@@ -16272,463 +16184,489 @@
       <c r="AA103" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB103" s="11"/>
-      <c r="AC103" s="11"/>
-      <c r="AD103" s="11"/>
-      <c r="AE103" s="11"/>
-      <c r="AF103" s="11"/>
-      <c r="AG103" s="11"/>
-      <c r="AH103" s="11"/>
-      <c r="AI103" s="11"/>
-      <c r="AJ103" s="11"/>
-      <c r="AK103" s="11"/>
-      <c r="AL103" s="11"/>
-      <c r="AM103" s="11"/>
-      <c r="AN103" s="11"/>
+      <c r="AB103" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC103" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AD103" s="10">
+        <v>32000</v>
+      </c>
+      <c r="AE103" s="8">
+        <v>32901199</v>
+      </c>
+      <c r="AF103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH103" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI103" s="7" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AJ103" s="10">
+        <v>31221</v>
+      </c>
+      <c r="AK103" s="8">
+        <v>31592067</v>
+      </c>
+      <c r="AL103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN103" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="AO103" s="7" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="AP103" s="8">
-        <v>53180910</v>
-      </c>
-      <c r="AQ103" s="11"/>
-      <c r="AR103" s="11"/>
-      <c r="AS103" s="11"/>
-      <c r="AT103" s="11"/>
-      <c r="AU103" s="28">
-        <v>483</v>
+        <v>32901199</v>
+      </c>
+      <c r="AQ103" s="7" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AR103" s="8">
+        <v>29562033</v>
+      </c>
+      <c r="AS103" s="7" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AT103" s="8">
+        <v>32348129</v>
+      </c>
+      <c r="AU103" s="29">
+        <v>547</v>
       </c>
     </row>
-    <row r="104" spans="1:47" ht="39" thickBot="1">
-      <c r="A104" s="12">
-        <v>46268.024733796294</v>
-      </c>
-      <c r="B104" s="13" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D104" s="14">
-        <v>34175564</v>
-      </c>
-      <c r="E104" s="15">
-        <v>32752</v>
-      </c>
-      <c r="F104" s="13" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G104" s="13" t="s">
+    <row r="104" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A104" s="6">
+        <v>46268.616111111114</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D104" s="8">
+        <v>36997404</v>
+      </c>
+      <c r="E104" s="9">
+        <v>34037</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H104" s="8">
+        <v>3382418740</v>
+      </c>
+      <c r="I104" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K104" s="11"/>
+      <c r="L104" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M104" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="N104" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="O104" s="10">
+        <v>44531</v>
+      </c>
+      <c r="P104" s="8">
+        <v>42</v>
+      </c>
+      <c r="Q104" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="R104" s="8">
+        <v>44</v>
+      </c>
+      <c r="S104" s="8">
+        <v>42</v>
+      </c>
+      <c r="T104" s="11"/>
+      <c r="U104" s="11"/>
+      <c r="V104" s="11"/>
+      <c r="W104" s="11"/>
+      <c r="X104" s="11"/>
+      <c r="Y104" s="11"/>
+      <c r="Z104" s="11"/>
+      <c r="AA104" s="11"/>
+      <c r="AB104" s="11"/>
+      <c r="AC104" s="11"/>
+      <c r="AD104" s="11"/>
+      <c r="AE104" s="11"/>
+      <c r="AF104" s="11"/>
+      <c r="AG104" s="11"/>
+      <c r="AH104" s="11"/>
+      <c r="AI104" s="11"/>
+      <c r="AJ104" s="11"/>
+      <c r="AK104" s="11"/>
+      <c r="AL104" s="11"/>
+      <c r="AM104" s="11"/>
+      <c r="AN104" s="11"/>
+      <c r="AO104" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AP104" s="8">
+        <v>17758389</v>
+      </c>
+      <c r="AQ104" s="11"/>
+      <c r="AR104" s="11"/>
+      <c r="AS104" s="11"/>
+      <c r="AT104" s="11"/>
+      <c r="AU104" s="28">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="105" spans="1:47" ht="77.25" thickBot="1">
+      <c r="A105" s="12">
+        <v>46268.67827546296</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C105" s="13" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D105" s="14">
+        <v>25323779</v>
+      </c>
+      <c r="E105" s="15">
+        <v>27907</v>
+      </c>
+      <c r="F105" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G105" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H104" s="14">
-        <v>3382406506</v>
-      </c>
-      <c r="I104" s="13" t="s">
+      <c r="H105" s="13" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I105" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J104" s="13" t="s">
+      <c r="J105" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="K104" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="L104" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="M104" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="N104" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="O104" s="16">
-        <v>44531</v>
-      </c>
-      <c r="P104" s="14">
+      <c r="K105" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="L105" s="13" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M105" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="N105" s="13" t="s">
+        <v>1034</v>
+      </c>
+      <c r="O105" s="16">
+        <v>38749</v>
+      </c>
+      <c r="P105" s="14">
+        <v>3</v>
+      </c>
+      <c r="Q105" s="14">
+        <v>3</v>
+      </c>
+      <c r="R105" s="14">
         <v>44</v>
       </c>
-      <c r="Q104" s="13" t="s">
+      <c r="S105" s="14">
+        <v>37</v>
+      </c>
+      <c r="T105" s="13" t="s">
+        <v>1035</v>
+      </c>
+      <c r="U105" s="16">
+        <v>28562</v>
+      </c>
+      <c r="V105" s="14">
+        <v>26318934</v>
+      </c>
+      <c r="W105" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="X105" s="16">
+        <v>34744</v>
+      </c>
+      <c r="Y105" s="14">
+        <v>37902940</v>
+      </c>
+      <c r="Z105" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA105" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105" s="13" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AC105" s="13" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AD105" s="16">
+        <v>42272</v>
+      </c>
+      <c r="AE105" s="14">
+        <v>55096607</v>
+      </c>
+      <c r="AF105" s="17"/>
+      <c r="AG105" s="17"/>
+      <c r="AH105" s="17"/>
+      <c r="AI105" s="17"/>
+      <c r="AJ105" s="17"/>
+      <c r="AK105" s="17"/>
+      <c r="AL105" s="17"/>
+      <c r="AM105" s="17"/>
+      <c r="AN105" s="17"/>
+      <c r="AO105" s="13" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AP105" s="14">
+        <v>37902940</v>
+      </c>
+      <c r="AQ105" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AR105" s="14">
+        <v>55096607</v>
+      </c>
+      <c r="AS105" s="13" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AT105" s="14">
+        <v>26318934</v>
+      </c>
+      <c r="AU105" s="18">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="106" spans="1:47" ht="102.75" thickBot="1">
+      <c r="A106" s="37">
+        <v>46269.356238425928</v>
+      </c>
+      <c r="B106" s="38" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C106" s="38" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D106" s="39">
+        <v>22797159</v>
+      </c>
+      <c r="E106" s="40">
+        <v>26618</v>
+      </c>
+      <c r="F106" s="38" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G106" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H106" s="38" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I106" s="38" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J106" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="K106" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="L106" s="38" t="s">
+        <v>1046</v>
+      </c>
+      <c r="M106" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="N106" s="38" t="s">
+        <v>1047</v>
+      </c>
+      <c r="O106" s="42">
+        <v>38450</v>
+      </c>
+      <c r="P106" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="R104" s="14">
+      <c r="Q106" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="R106" s="39">
         <v>50</v>
       </c>
-      <c r="S104" s="14">
-        <v>45</v>
-      </c>
-      <c r="T104" s="17"/>
-      <c r="U104" s="17"/>
-      <c r="V104" s="17"/>
-      <c r="W104" s="13" t="s">
-        <v>1018</v>
-      </c>
-      <c r="X104" s="16">
-        <v>42619</v>
-      </c>
-      <c r="Y104" s="14">
-        <v>55798119</v>
-      </c>
-      <c r="Z104" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA104" s="13" t="s">
+      <c r="S106" s="39">
+        <v>40</v>
+      </c>
+      <c r="T106" s="41"/>
+      <c r="U106" s="41"/>
+      <c r="V106" s="41"/>
+      <c r="W106" s="38" t="s">
+        <v>1048</v>
+      </c>
+      <c r="X106" s="42">
+        <v>35662</v>
+      </c>
+      <c r="Y106" s="39">
+        <v>40277591</v>
+      </c>
+      <c r="Z106" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA106" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB106" s="38" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AC106" s="38" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AD106" s="42">
+        <v>38995</v>
+      </c>
+      <c r="AE106" s="39">
+        <v>47329419</v>
+      </c>
+      <c r="AF106" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG106" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH106" s="38" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AI106" s="38" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AJ106" s="42">
+        <v>44952</v>
+      </c>
+      <c r="AK106" s="39">
+        <v>59654163</v>
+      </c>
+      <c r="AL106" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="AB104" s="17"/>
-      <c r="AC104" s="13" t="s">
-        <v>1019</v>
-      </c>
-      <c r="AD104" s="16">
-        <v>44590</v>
-      </c>
-      <c r="AE104" s="14">
-        <v>59103651</v>
-      </c>
-      <c r="AF104" s="17"/>
-      <c r="AG104" s="17"/>
-      <c r="AH104" s="17"/>
-      <c r="AI104" s="17"/>
-      <c r="AJ104" s="17"/>
-      <c r="AK104" s="17"/>
-      <c r="AL104" s="17"/>
-      <c r="AM104" s="17"/>
-      <c r="AN104" s="17"/>
-      <c r="AO104" s="13" t="s">
-        <v>1020</v>
-      </c>
-      <c r="AP104" s="14">
-        <v>39049433</v>
-      </c>
-      <c r="AQ104" s="17"/>
-      <c r="AR104" s="17"/>
-      <c r="AS104" s="17"/>
-      <c r="AT104" s="17"/>
-      <c r="AU104" s="18">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="105" spans="1:47" ht="26.25" thickBot="1">
-      <c r="A105" s="45">
-        <v>46268.375891203701</v>
-      </c>
-      <c r="B105" s="46" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C105" s="46" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D105" s="47">
-        <v>36421488</v>
-      </c>
-      <c r="E105" s="48">
-        <v>33677</v>
-      </c>
-      <c r="F105" s="46" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G105" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="H105" s="47">
-        <v>3382481763</v>
-      </c>
-      <c r="I105" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="J105" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="K105" s="49"/>
-      <c r="L105" s="46" t="s">
+      <c r="AM106" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="M105" s="46" t="s">
-        <v>1024</v>
-      </c>
-      <c r="N105" s="46" t="s">
-        <v>1025</v>
-      </c>
-      <c r="O105" s="50">
-        <v>46268</v>
-      </c>
-      <c r="P105" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q105" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="R105" s="47">
-        <v>44</v>
-      </c>
-      <c r="S105" s="47">
-        <v>43</v>
-      </c>
-      <c r="T105" s="49"/>
-      <c r="U105" s="49"/>
-      <c r="V105" s="49"/>
-      <c r="W105" s="46" t="s">
-        <v>1026</v>
-      </c>
-      <c r="X105" s="50">
-        <v>42688</v>
-      </c>
-      <c r="Y105" s="47">
-        <v>55718259</v>
-      </c>
-      <c r="Z105" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA105" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB105" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="AC105" s="46" t="s">
-        <v>1027</v>
-      </c>
-      <c r="AD105" s="50">
-        <v>43641</v>
-      </c>
-      <c r="AE105" s="47">
-        <v>57460864</v>
-      </c>
-      <c r="AF105" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG105" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="AH105" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="AI105" s="49"/>
-      <c r="AJ105" s="49"/>
-      <c r="AK105" s="49"/>
-      <c r="AL105" s="49"/>
-      <c r="AM105" s="49"/>
-      <c r="AN105" s="49"/>
-      <c r="AO105" s="46" t="s">
-        <v>1028</v>
-      </c>
-      <c r="AP105" s="47">
-        <v>16628087</v>
-      </c>
-      <c r="AQ105" s="49"/>
-      <c r="AR105" s="49"/>
-      <c r="AS105" s="49"/>
-      <c r="AT105" s="49"/>
-      <c r="AU105" s="51">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="106" spans="1:47" ht="39" thickBot="1">
-      <c r="A106" s="6">
-        <v>46268.520219907405</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D106" s="8">
-        <v>16370636</v>
-      </c>
-      <c r="E106" s="9">
-        <v>23246</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H106" s="8">
-        <v>3382454153</v>
-      </c>
-      <c r="I106" s="7" t="s">
-        <v>1032</v>
-      </c>
-      <c r="J106" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K106" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="L106" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="M106" s="7" t="s">
-        <v>1033</v>
-      </c>
-      <c r="N106" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="O106" s="10">
-        <v>44531</v>
-      </c>
-      <c r="P106" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q106" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="R106" s="8">
-        <v>46</v>
-      </c>
-      <c r="S106" s="8">
-        <v>38</v>
-      </c>
-      <c r="T106" s="11"/>
-      <c r="U106" s="11"/>
-      <c r="V106" s="11"/>
-      <c r="W106" s="7" t="s">
-        <v>1034</v>
-      </c>
-      <c r="X106" s="10">
-        <v>29943</v>
-      </c>
-      <c r="Y106" s="8">
-        <v>29562033</v>
-      </c>
-      <c r="Z106" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA106" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB106" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="AC106" s="7" t="s">
-        <v>1035</v>
-      </c>
-      <c r="AD106" s="10">
-        <v>32000</v>
-      </c>
-      <c r="AE106" s="8">
-        <v>32901199</v>
-      </c>
-      <c r="AF106" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG106" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH106" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="AI106" s="7" t="s">
-        <v>1036</v>
-      </c>
-      <c r="AJ106" s="10">
-        <v>31221</v>
-      </c>
-      <c r="AK106" s="8">
-        <v>31592067</v>
-      </c>
-      <c r="AL106" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM106" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN106" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="AO106" s="7" t="s">
-        <v>1037</v>
-      </c>
-      <c r="AP106" s="8">
-        <v>32901199</v>
-      </c>
-      <c r="AQ106" s="7" t="s">
-        <v>1034</v>
-      </c>
-      <c r="AR106" s="8">
-        <v>29562033</v>
-      </c>
-      <c r="AS106" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="AT106" s="8">
-        <v>32348129</v>
-      </c>
-      <c r="AU106" s="29">
-        <v>547</v>
+      <c r="AN106" s="41"/>
+      <c r="AO106" s="38" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AP106" s="39">
+        <v>40277591</v>
+      </c>
+      <c r="AQ106" s="38" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AR106" s="39">
+        <v>47329419</v>
+      </c>
+      <c r="AS106" s="41"/>
+      <c r="AT106" s="41"/>
+      <c r="AU106" s="43">
+        <v>351</v>
       </c>
     </row>
     <row r="107" spans="1:47" ht="39" thickBot="1">
       <c r="A107" s="21">
-        <v>46268.581157407411</v>
+        <v>46269.427708333336</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="D107" s="23">
-        <v>27060256</v>
+        <v>31116949</v>
       </c>
       <c r="E107" s="24">
-        <v>28858</v>
+        <v>31085</v>
       </c>
       <c r="F107" s="22" t="s">
-        <v>1041</v>
+        <v>1055</v>
       </c>
       <c r="G107" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="H107" s="23">
-        <v>3382460661</v>
+      <c r="H107" s="22" t="s">
+        <v>1056</v>
       </c>
       <c r="I107" s="22" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="J107" s="22" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="K107" s="22" t="s">
-        <v>230</v>
+        <v>1057</v>
       </c>
       <c r="L107" s="22" t="s">
         <v>230</v>
       </c>
       <c r="M107" s="22" t="s">
-        <v>560</v>
+        <v>1058</v>
       </c>
       <c r="N107" s="22" t="s">
-        <v>1042</v>
+        <v>232</v>
       </c>
       <c r="O107" s="25">
-        <v>44896</v>
+        <v>38412</v>
       </c>
       <c r="P107" s="23">
-        <v>3</v>
-      </c>
-      <c r="Q107" s="23">
-        <v>3</v>
+        <v>48</v>
+      </c>
+      <c r="Q107" s="22" t="s">
+        <v>37</v>
       </c>
       <c r="R107" s="23">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="S107" s="23">
-        <v>38</v>
-      </c>
-      <c r="T107" s="26"/>
-      <c r="U107" s="26"/>
-      <c r="V107" s="26"/>
+        <v>40</v>
+      </c>
+      <c r="T107" s="22" t="s">
+        <v>1059</v>
+      </c>
+      <c r="U107" s="25">
+        <v>29776</v>
+      </c>
+      <c r="V107" s="23">
+        <v>28572997</v>
+      </c>
       <c r="W107" s="22" t="s">
-        <v>1043</v>
+        <v>1060</v>
       </c>
       <c r="X107" s="25">
-        <v>35543</v>
+        <v>40646</v>
       </c>
       <c r="Y107" s="23">
-        <v>40277508</v>
+        <v>50923407</v>
       </c>
       <c r="Z107" s="22" t="s">
         <v>40</v>
@@ -16740,19 +16678,19 @@
         <v>230</v>
       </c>
       <c r="AC107" s="22" t="s">
-        <v>1044</v>
+        <v>1061</v>
       </c>
       <c r="AD107" s="25">
-        <v>37775</v>
+        <v>41926</v>
       </c>
       <c r="AE107" s="23">
-        <v>44810216</v>
+        <v>54202483</v>
       </c>
       <c r="AF107" s="22" t="s">
         <v>40</v>
       </c>
       <c r="AG107" s="22" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="AH107" s="22" t="s">
         <v>230</v>
@@ -16764,445 +16702,481 @@
       <c r="AM107" s="26"/>
       <c r="AN107" s="26"/>
       <c r="AO107" s="22" t="s">
-        <v>1043</v>
-      </c>
-      <c r="AP107" s="23">
-        <v>40277508</v>
+        <v>230</v>
+      </c>
+      <c r="AP107" s="22" t="s">
+        <v>230</v>
       </c>
       <c r="AQ107" s="22" t="s">
-        <v>1044</v>
-      </c>
-      <c r="AR107" s="23">
-        <v>44810216</v>
-      </c>
-      <c r="AS107" s="26"/>
-      <c r="AT107" s="26"/>
+        <v>230</v>
+      </c>
+      <c r="AR107" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AS107" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AT107" s="22" t="s">
+        <v>230</v>
+      </c>
       <c r="AU107" s="27">
-        <v>606</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:47" ht="51.75" thickBot="1">
       <c r="A108" s="6">
-        <v>46268.616111111114</v>
+        <v>46269.740752314814</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>1045</v>
+        <v>1062</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>1046</v>
+        <v>1063</v>
       </c>
       <c r="D108" s="8">
-        <v>36997404</v>
+        <v>27865190</v>
       </c>
       <c r="E108" s="9">
-        <v>34037</v>
+        <v>29722</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>1047</v>
+        <v>1064</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>1048</v>
+        <v>30</v>
       </c>
       <c r="H108" s="8">
-        <v>3382418740</v>
+        <v>3382676882</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="J108" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K108" s="11"/>
+      <c r="K108" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="L108" s="7" t="s">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="M108" s="7" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="N108" s="7" t="s">
-        <v>1050</v>
+        <v>1066</v>
       </c>
       <c r="O108" s="10">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="P108" s="8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>304</v>
+        <v>49</v>
       </c>
       <c r="R108" s="8">
         <v>44</v>
       </c>
       <c r="S108" s="8">
-        <v>42</v>
-      </c>
-      <c r="T108" s="11"/>
-      <c r="U108" s="11"/>
-      <c r="V108" s="11"/>
-      <c r="W108" s="11"/>
-      <c r="X108" s="11"/>
-      <c r="Y108" s="11"/>
-      <c r="Z108" s="11"/>
-      <c r="AA108" s="11"/>
+        <v>38</v>
+      </c>
+      <c r="T108" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="U108" s="10">
+        <v>29720</v>
+      </c>
+      <c r="V108" s="8">
+        <v>28301047</v>
+      </c>
+      <c r="W108" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="X108" s="10">
+        <v>36349</v>
+      </c>
+      <c r="Y108" s="8">
+        <v>41654702</v>
+      </c>
+      <c r="Z108" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA108" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB108" s="11"/>
-      <c r="AC108" s="11"/>
-      <c r="AD108" s="11"/>
-      <c r="AE108" s="11"/>
-      <c r="AF108" s="11"/>
-      <c r="AG108" s="11"/>
-      <c r="AH108" s="11"/>
-      <c r="AI108" s="11"/>
-      <c r="AJ108" s="11"/>
-      <c r="AK108" s="11"/>
-      <c r="AL108" s="11"/>
-      <c r="AM108" s="11"/>
+      <c r="AC108" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AD108" s="10">
+        <v>36732</v>
+      </c>
+      <c r="AE108" s="8">
+        <v>42127997</v>
+      </c>
+      <c r="AF108" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG108" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH108" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AI108" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AJ108" s="10">
+        <v>38056</v>
+      </c>
+      <c r="AK108" s="8">
+        <v>45508102</v>
+      </c>
+      <c r="AL108" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM108" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AN108" s="11"/>
       <c r="AO108" s="7" t="s">
-        <v>1051</v>
+        <v>1072</v>
       </c>
       <c r="AP108" s="8">
-        <v>17758389</v>
-      </c>
-      <c r="AQ108" s="11"/>
-      <c r="AR108" s="11"/>
-      <c r="AS108" s="11"/>
-      <c r="AT108" s="11"/>
+        <v>41654702</v>
+      </c>
+      <c r="AQ108" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AR108" s="8">
+        <v>42127997</v>
+      </c>
+      <c r="AS108" s="7" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AT108" s="8">
+        <v>45508102</v>
+      </c>
       <c r="AU108" s="28">
-        <v>521</v>
+        <v>594</v>
       </c>
     </row>
-    <row r="109" spans="1:47" ht="77.25" thickBot="1">
-      <c r="A109" s="12">
-        <v>46268.67827546296</v>
-      </c>
-      <c r="B109" s="13" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C109" s="13" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D109" s="14">
-        <v>25323779</v>
-      </c>
-      <c r="E109" s="15">
-        <v>27907</v>
-      </c>
-      <c r="F109" s="13" t="s">
-        <v>1054</v>
-      </c>
-      <c r="G109" s="13" t="s">
+    <row r="109" spans="1:47" ht="39" thickBot="1">
+      <c r="A109" s="21">
+        <v>46271.867939814816</v>
+      </c>
+      <c r="B109" s="22" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D109" s="23">
+        <v>21416800</v>
+      </c>
+      <c r="E109" s="24">
+        <v>25619</v>
+      </c>
+      <c r="F109" s="22" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G109" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="H109" s="13" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I109" s="13" t="s">
+      <c r="H109" s="23">
+        <v>3382458324</v>
+      </c>
+      <c r="I109" s="22" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J109" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K109" s="22" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L109" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M109" s="22" t="s">
+        <v>1077</v>
+      </c>
+      <c r="N109" s="22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="O109" s="25">
+        <v>34578</v>
+      </c>
+      <c r="P109" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q109" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R109" s="23">
+        <v>40</v>
+      </c>
+      <c r="S109" s="23">
+        <v>38</v>
+      </c>
+      <c r="T109" s="26"/>
+      <c r="U109" s="26"/>
+      <c r="V109" s="26"/>
+      <c r="W109" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="X109" s="25">
+        <v>36453</v>
+      </c>
+      <c r="Y109" s="23">
+        <v>41654791</v>
+      </c>
+      <c r="Z109" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA109" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB109" s="22" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AC109" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AD109" s="25">
+        <v>41191</v>
+      </c>
+      <c r="AE109" s="23">
+        <v>52633659</v>
+      </c>
+      <c r="AF109" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG109" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH109" s="26"/>
+      <c r="AI109" s="26"/>
+      <c r="AJ109" s="26"/>
+      <c r="AK109" s="26"/>
+      <c r="AL109" s="26"/>
+      <c r="AM109" s="26"/>
+      <c r="AN109" s="26"/>
+      <c r="AO109" s="22" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AP109" s="23">
+        <v>41654791</v>
+      </c>
+      <c r="AQ109" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AR109" s="23">
+        <v>52633659</v>
+      </c>
+      <c r="AS109" s="26"/>
+      <c r="AT109" s="26"/>
+      <c r="AU109" s="27">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:47" ht="39" thickBot="1">
+      <c r="A110" s="6">
+        <v>46272.572465277779</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D110" s="8">
+        <v>27060256</v>
+      </c>
+      <c r="E110" s="9">
+        <v>28858</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H110" s="8">
+        <v>3382460661</v>
+      </c>
+      <c r="I110" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J109" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="K109" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="L109" s="13" t="s">
-        <v>1056</v>
-      </c>
-      <c r="M109" s="13" t="s">
-        <v>1057</v>
-      </c>
-      <c r="N109" s="13" t="s">
-        <v>1058</v>
-      </c>
-      <c r="O109" s="16">
-        <v>38749</v>
-      </c>
-      <c r="P109" s="14">
+      <c r="J110" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K110" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L110" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M110" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="N110" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="O110" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P110" s="8">
         <v>3</v>
       </c>
-      <c r="Q109" s="14">
+      <c r="Q110" s="8">
         <v>3</v>
       </c>
-      <c r="R109" s="14">
-        <v>44</v>
-      </c>
-      <c r="S109" s="14">
-        <v>37</v>
-      </c>
-      <c r="T109" s="13" t="s">
-        <v>1059</v>
-      </c>
-      <c r="U109" s="16">
-        <v>28562</v>
-      </c>
-      <c r="V109" s="14">
-        <v>26318934</v>
-      </c>
-      <c r="W109" s="13" t="s">
-        <v>1060</v>
-      </c>
-      <c r="X109" s="16">
-        <v>34744</v>
-      </c>
-      <c r="Y109" s="14">
-        <v>37902940</v>
-      </c>
-      <c r="Z109" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA109" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB109" s="13" t="s">
-        <v>1061</v>
-      </c>
-      <c r="AC109" s="13" t="s">
-        <v>1062</v>
-      </c>
-      <c r="AD109" s="16">
-        <v>42272</v>
-      </c>
-      <c r="AE109" s="14">
-        <v>55096607</v>
-      </c>
-      <c r="AF109" s="17"/>
-      <c r="AG109" s="17"/>
-      <c r="AH109" s="17"/>
-      <c r="AI109" s="17"/>
-      <c r="AJ109" s="17"/>
-      <c r="AK109" s="17"/>
-      <c r="AL109" s="17"/>
-      <c r="AM109" s="17"/>
-      <c r="AN109" s="17"/>
-      <c r="AO109" s="13" t="s">
-        <v>1063</v>
-      </c>
-      <c r="AP109" s="14">
-        <v>37902940</v>
-      </c>
-      <c r="AQ109" s="13" t="s">
-        <v>1064</v>
-      </c>
-      <c r="AR109" s="14">
-        <v>55096607</v>
-      </c>
-      <c r="AS109" s="13" t="s">
-        <v>1065</v>
-      </c>
-      <c r="AT109" s="14">
-        <v>26318934</v>
-      </c>
-      <c r="AU109" s="18">
-        <v>267</v>
+      <c r="R110" s="8">
+        <v>42</v>
+      </c>
+      <c r="S110" s="8">
+        <v>38</v>
+      </c>
+      <c r="T110" s="11"/>
+      <c r="U110" s="11"/>
+      <c r="V110" s="11"/>
+      <c r="W110" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="X110" s="10">
+        <v>35543</v>
+      </c>
+      <c r="Y110" s="8">
+        <v>40277508</v>
+      </c>
+      <c r="Z110" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA110" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB110" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC110" s="7" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AD110" s="10">
+        <v>37775</v>
+      </c>
+      <c r="AE110" s="8">
+        <v>44810215</v>
+      </c>
+      <c r="AF110" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG110" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH110" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI110" s="11"/>
+      <c r="AJ110" s="11"/>
+      <c r="AK110" s="11"/>
+      <c r="AL110" s="11"/>
+      <c r="AM110" s="11"/>
+      <c r="AN110" s="11"/>
+      <c r="AO110" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AP110" s="8">
+        <v>40277508</v>
+      </c>
+      <c r="AQ110" s="7" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AR110" s="8">
+        <v>44810216</v>
+      </c>
+      <c r="AS110" s="11"/>
+      <c r="AT110" s="11"/>
+      <c r="AU110" s="28">
+        <v>606</v>
       </c>
     </row>
-    <row r="110" spans="1:47" ht="102.75" thickBot="1">
-      <c r="A110" s="37">
-        <v>46269.356238425928</v>
-      </c>
-      <c r="B110" s="38" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C110" s="38" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D110" s="39">
-        <v>22797159</v>
-      </c>
-      <c r="E110" s="40">
-        <v>26618</v>
-      </c>
-      <c r="F110" s="38" t="s">
-        <v>1068</v>
-      </c>
-      <c r="G110" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H110" s="38" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I110" s="38" t="s">
-        <v>1032</v>
-      </c>
-      <c r="J110" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="K110" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="L110" s="38" t="s">
-        <v>1070</v>
-      </c>
-      <c r="M110" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="N110" s="38" t="s">
-        <v>1071</v>
-      </c>
-      <c r="O110" s="42">
-        <v>38450</v>
-      </c>
-      <c r="P110" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q110" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="R110" s="39">
-        <v>50</v>
-      </c>
-      <c r="S110" s="39">
-        <v>40</v>
-      </c>
-      <c r="T110" s="41"/>
-      <c r="U110" s="41"/>
-      <c r="V110" s="41"/>
-      <c r="W110" s="38" t="s">
-        <v>1072</v>
-      </c>
-      <c r="X110" s="42">
-        <v>35662</v>
-      </c>
-      <c r="Y110" s="39">
-        <v>40277591</v>
-      </c>
-      <c r="Z110" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA110" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB110" s="38" t="s">
-        <v>1073</v>
-      </c>
-      <c r="AC110" s="38" t="s">
-        <v>1074</v>
-      </c>
-      <c r="AD110" s="42">
-        <v>38995</v>
-      </c>
-      <c r="AE110" s="39">
-        <v>47329419</v>
-      </c>
-      <c r="AF110" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG110" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH110" s="38" t="s">
-        <v>1075</v>
-      </c>
-      <c r="AI110" s="38" t="s">
-        <v>1076</v>
-      </c>
-      <c r="AJ110" s="42">
-        <v>44952</v>
-      </c>
-      <c r="AK110" s="39">
-        <v>59654163</v>
-      </c>
-      <c r="AL110" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="AM110" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="AN110" s="41"/>
-      <c r="AO110" s="38" t="s">
-        <v>1072</v>
-      </c>
-      <c r="AP110" s="39">
-        <v>40277591</v>
-      </c>
-      <c r="AQ110" s="38" t="s">
-        <v>1074</v>
-      </c>
-      <c r="AR110" s="39">
-        <v>47329419</v>
-      </c>
-      <c r="AS110" s="41"/>
-      <c r="AT110" s="41"/>
-      <c r="AU110" s="43">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="111" spans="1:47" ht="39" thickBot="1">
+    <row r="111" spans="1:47" ht="51.75" thickBot="1">
       <c r="A111" s="21">
-        <v>46269.427708333336</v>
+        <v>46273.383287037039</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C111" s="22" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="D111" s="23">
-        <v>31116949</v>
+        <v>30399457</v>
       </c>
       <c r="E111" s="24">
-        <v>31085</v>
+        <v>29996</v>
       </c>
       <c r="F111" s="22" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="G111" s="22" t="s">
         <v>30</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="I111" s="22" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="J111" s="22" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="K111" s="22" t="s">
-        <v>1081</v>
+        <v>230</v>
       </c>
       <c r="L111" s="22" t="s">
         <v>230</v>
       </c>
       <c r="M111" s="22" t="s">
-        <v>1082</v>
+        <v>327</v>
       </c>
       <c r="N111" s="22" t="s">
-        <v>232</v>
+        <v>1089</v>
       </c>
       <c r="O111" s="25">
-        <v>38412</v>
+        <v>44896</v>
       </c>
       <c r="P111" s="23">
-        <v>48</v>
-      </c>
-      <c r="Q111" s="22" t="s">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="Q111" s="23">
+        <v>5</v>
       </c>
       <c r="R111" s="23">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="S111" s="23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T111" s="22" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="U111" s="25">
-        <v>29776</v>
+        <v>25850</v>
       </c>
       <c r="V111" s="23">
-        <v>28572997</v>
+        <v>21555550</v>
       </c>
       <c r="W111" s="22" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="X111" s="25">
-        <v>40646</v>
+        <v>37432</v>
       </c>
       <c r="Y111" s="23">
-        <v>50923407</v>
+        <v>43843291</v>
       </c>
       <c r="Z111" s="22" t="s">
         <v>40</v>
@@ -17210,263 +17184,241 @@
       <c r="AA111" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AB111" s="22" t="s">
-        <v>230</v>
-      </c>
+      <c r="AB111" s="26"/>
       <c r="AC111" s="22" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="AD111" s="25">
-        <v>41926</v>
+        <v>38062</v>
       </c>
       <c r="AE111" s="23">
-        <v>54202483</v>
+        <v>45508098</v>
       </c>
       <c r="AF111" s="22" t="s">
         <v>40</v>
       </c>
       <c r="AG111" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AH111" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AI111" s="26"/>
-      <c r="AJ111" s="26"/>
-      <c r="AK111" s="26"/>
-      <c r="AL111" s="26"/>
-      <c r="AM111" s="26"/>
+        <v>40</v>
+      </c>
+      <c r="AH111" s="26"/>
+      <c r="AI111" s="22" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AJ111" s="25">
+        <v>38853</v>
+      </c>
+      <c r="AK111" s="23">
+        <v>47107320</v>
+      </c>
+      <c r="AL111" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM111" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="AN111" s="26"/>
       <c r="AO111" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AP111" s="22" t="s">
-        <v>230</v>
+        <v>1091</v>
+      </c>
+      <c r="AP111" s="23">
+        <v>43843291</v>
       </c>
       <c r="AQ111" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AR111" s="22" t="s">
-        <v>230</v>
+        <v>1093</v>
+      </c>
+      <c r="AR111" s="23">
+        <v>47107320</v>
       </c>
       <c r="AS111" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AT111" s="22" t="s">
-        <v>230</v>
+        <v>1092</v>
+      </c>
+      <c r="AT111" s="23">
+        <v>45508098</v>
       </c>
       <c r="AU111" s="27">
-        <v>250</v>
+        <v>603</v>
       </c>
     </row>
-    <row r="112" spans="1:47" ht="51.75" thickBot="1">
+    <row r="112" spans="1:47" ht="39" thickBot="1">
       <c r="A112" s="6">
-        <v>46269.740752314814</v>
+        <v>46273.391805555555</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="D112" s="8">
-        <v>27865190</v>
-      </c>
-      <c r="E112" s="9">
-        <v>29722</v>
+        <v>18001714</v>
+      </c>
+      <c r="E112" s="8">
+        <v>19021967</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="G112" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H112" s="8">
-        <v>3382676882</v>
+        <v>3382409515</v>
       </c>
       <c r="I112" s="7" t="s">
         <v>31</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K112" s="7" t="s">
-        <v>264</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="K112" s="11"/>
       <c r="L112" s="7" t="s">
         <v>230</v>
       </c>
       <c r="M112" s="7" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="N112" s="7" t="s">
-        <v>1090</v>
+        <v>316</v>
       </c>
       <c r="O112" s="10">
-        <v>44896</v>
+        <v>37075</v>
       </c>
       <c r="P112" s="8">
-        <v>40</v>
-      </c>
-      <c r="Q112" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="Q112" s="8">
+        <v>52</v>
       </c>
       <c r="R112" s="8">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="S112" s="8">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="T112" s="7" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="U112" s="10">
-        <v>29720</v>
+        <v>26860</v>
       </c>
       <c r="V112" s="8">
-        <v>28301047</v>
+        <v>23255156</v>
       </c>
       <c r="W112" s="7" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="X112" s="10">
-        <v>36349</v>
+        <v>35901</v>
       </c>
       <c r="Y112" s="8">
-        <v>41654702</v>
+        <v>40959346</v>
       </c>
       <c r="Z112" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AA112" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AA112" s="11"/>
       <c r="AB112" s="11"/>
-      <c r="AC112" s="7" t="s">
-        <v>1093</v>
-      </c>
-      <c r="AD112" s="10">
-        <v>36732</v>
-      </c>
-      <c r="AE112" s="8">
-        <v>42127997</v>
-      </c>
-      <c r="AF112" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG112" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH112" s="7" t="s">
-        <v>1094</v>
-      </c>
-      <c r="AI112" s="7" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AJ112" s="10">
-        <v>38056</v>
-      </c>
-      <c r="AK112" s="8">
-        <v>45508102</v>
-      </c>
-      <c r="AL112" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM112" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AC112" s="11"/>
+      <c r="AD112" s="11"/>
+      <c r="AE112" s="11"/>
+      <c r="AF112" s="11"/>
+      <c r="AG112" s="11"/>
+      <c r="AH112" s="11"/>
+      <c r="AI112" s="11"/>
+      <c r="AJ112" s="11"/>
+      <c r="AK112" s="11"/>
+      <c r="AL112" s="11"/>
+      <c r="AM112" s="11"/>
       <c r="AN112" s="11"/>
       <c r="AO112" s="7" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="AP112" s="8">
-        <v>41654702</v>
-      </c>
-      <c r="AQ112" s="7" t="s">
-        <v>1093</v>
-      </c>
-      <c r="AR112" s="8">
-        <v>42127997</v>
-      </c>
-      <c r="AS112" s="7" t="s">
-        <v>1095</v>
-      </c>
-      <c r="AT112" s="8">
-        <v>45508102</v>
-      </c>
+        <v>23255156</v>
+      </c>
+      <c r="AQ112" s="11"/>
+      <c r="AR112" s="11"/>
+      <c r="AS112" s="11"/>
+      <c r="AT112" s="11"/>
       <c r="AU112" s="28">
-        <v>594</v>
+        <v>327</v>
       </c>
     </row>
-    <row r="113" spans="1:47" ht="39" thickBot="1">
+    <row r="113" spans="1:47" ht="26.25" thickBot="1">
       <c r="A113" s="21">
-        <v>46271.867939814816</v>
+        <v>46273.624247685184</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D113" s="23">
-        <v>21416800</v>
+        <v>21767041</v>
       </c>
       <c r="E113" s="24">
-        <v>25619</v>
+        <v>25976</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="G113" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="H113" s="23">
-        <v>3382458324</v>
+      <c r="H113" s="22" t="s">
+        <v>1104</v>
       </c>
       <c r="I113" s="22" t="s">
-        <v>1032</v>
+        <v>31</v>
       </c>
       <c r="J113" s="22" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="K113" s="22" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="L113" s="22" t="s">
         <v>230</v>
       </c>
       <c r="M113" s="22" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="N113" s="22" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="O113" s="25">
-        <v>34578</v>
+        <v>39449</v>
       </c>
       <c r="P113" s="22" t="s">
-        <v>304</v>
+        <v>49</v>
       </c>
       <c r="Q113" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="R113" s="23">
-        <v>40</v>
+        <v>49</v>
+      </c>
+      <c r="R113" s="22" t="s">
+        <v>49</v>
       </c>
       <c r="S113" s="23">
-        <v>38</v>
-      </c>
-      <c r="T113" s="26"/>
-      <c r="U113" s="26"/>
-      <c r="V113" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="T113" s="22" t="s">
+        <v>1107</v>
+      </c>
+      <c r="U113" s="25">
+        <v>25490</v>
+      </c>
+      <c r="V113" s="23">
+        <v>20703838</v>
+      </c>
       <c r="W113" s="22" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="X113" s="25">
-        <v>36453</v>
+        <v>35028</v>
       </c>
       <c r="Y113" s="23">
-        <v>41654791</v>
+        <v>39049283</v>
       </c>
       <c r="Z113" s="22" t="s">
         <v>40</v>
@@ -17475,16 +17427,16 @@
         <v>40</v>
       </c>
       <c r="AB113" s="22" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="AC113" s="22" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="AD113" s="25">
-        <v>41191</v>
+        <v>36770</v>
       </c>
       <c r="AE113" s="23">
-        <v>52633659</v>
+        <v>42532435</v>
       </c>
       <c r="AF113" s="22" t="s">
         <v>40</v>
@@ -17492,100 +17444,124 @@
       <c r="AG113" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AH113" s="26"/>
-      <c r="AI113" s="26"/>
-      <c r="AJ113" s="26"/>
-      <c r="AK113" s="26"/>
-      <c r="AL113" s="26"/>
-      <c r="AM113" s="26"/>
-      <c r="AN113" s="26"/>
+      <c r="AH113" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AI113" s="22" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AJ113" s="25">
+        <v>16681</v>
+      </c>
+      <c r="AK113" s="23" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AL113" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM113" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN113" s="22" t="s">
+        <v>230</v>
+      </c>
       <c r="AO113" s="22" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="AP113" s="23">
-        <v>41654791</v>
+        <v>20703838</v>
       </c>
       <c r="AQ113" s="22" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="AR113" s="23">
-        <v>52633659</v>
-      </c>
-      <c r="AS113" s="26"/>
-      <c r="AT113" s="26"/>
+        <v>39049283</v>
+      </c>
+      <c r="AS113" s="22" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AT113" s="23">
+        <v>42532435</v>
+      </c>
       <c r="AU113" s="27">
-        <v>24</v>
+        <v>177</v>
       </c>
     </row>
-    <row r="114" spans="1:47" ht="39" thickBot="1">
+    <row r="114" spans="1:47" ht="64.5" thickBot="1">
       <c r="A114" s="6">
-        <v>46272.572465277779</v>
+        <v>46273.680868055555</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>1039</v>
+        <v>1114</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>1040</v>
+        <v>1115</v>
       </c>
       <c r="D114" s="8">
-        <v>27060256</v>
+        <v>21767233</v>
       </c>
       <c r="E114" s="9">
-        <v>28858</v>
+        <v>26231</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>1106</v>
+        <v>1116</v>
       </c>
       <c r="G114" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H114" s="8">
-        <v>3382460661</v>
+        <v>3382446330</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>230</v>
+        <v>1117</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="M114" s="7" t="s">
-        <v>560</v>
+        <v>349</v>
       </c>
       <c r="N114" s="7" t="s">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="O114" s="10">
-        <v>44896</v>
-      </c>
-      <c r="P114" s="8">
-        <v>3</v>
-      </c>
-      <c r="Q114" s="8">
-        <v>3</v>
+        <v>33574</v>
+      </c>
+      <c r="P114" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q114" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="R114" s="8">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="S114" s="8">
-        <v>38</v>
-      </c>
-      <c r="T114" s="11"/>
-      <c r="U114" s="11"/>
-      <c r="V114" s="11"/>
+        <v>41</v>
+      </c>
+      <c r="T114" s="7" t="s">
+        <v>1119</v>
+      </c>
+      <c r="U114" s="10">
+        <v>29009</v>
+      </c>
+      <c r="V114" s="8">
+        <v>27419861</v>
+      </c>
       <c r="W114" s="7" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
       <c r="X114" s="10">
-        <v>35543</v>
+        <v>39071</v>
       </c>
       <c r="Y114" s="8">
-        <v>40277508</v>
+        <v>47508181</v>
       </c>
       <c r="Z114" s="7" t="s">
         <v>40</v>
@@ -17593,17 +17569,15 @@
       <c r="AA114" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB114" s="7" t="s">
-        <v>230</v>
-      </c>
+      <c r="AB114" s="11"/>
       <c r="AC114" s="7" t="s">
-        <v>1044</v>
+        <v>1121</v>
       </c>
       <c r="AD114" s="10">
-        <v>37775</v>
+        <v>40188</v>
       </c>
       <c r="AE114" s="8">
-        <v>44810215</v>
+        <v>49817254</v>
       </c>
       <c r="AF114" s="7" t="s">
         <v>40</v>
@@ -17611,9 +17585,7 @@
       <c r="AG114" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AH114" s="7" t="s">
-        <v>230</v>
-      </c>
+      <c r="AH114" s="11"/>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="11"/>
       <c r="AK114" s="11"/>
@@ -17621,659 +17593,24 @@
       <c r="AM114" s="11"/>
       <c r="AN114" s="11"/>
       <c r="AO114" s="7" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="AP114" s="8">
-        <v>40277508</v>
+        <v>27419861</v>
       </c>
       <c r="AQ114" s="7" t="s">
-        <v>1044</v>
+        <v>1122</v>
       </c>
       <c r="AR114" s="8">
-        <v>44810216</v>
-      </c>
-      <c r="AS114" s="11"/>
-      <c r="AT114" s="11"/>
+        <v>47508181</v>
+      </c>
+      <c r="AS114" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AT114" s="8">
+        <v>49817254</v>
+      </c>
       <c r="AU114" s="28">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="115" spans="1:47" ht="51.75" thickBot="1">
-      <c r="A115" s="21">
-        <v>46273.383287037039</v>
-      </c>
-      <c r="B115" s="22" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C115" s="22" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D115" s="23">
-        <v>30399457</v>
-      </c>
-      <c r="E115" s="24">
-        <v>29996</v>
-      </c>
-      <c r="F115" s="22" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G115" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H115" s="22" t="s">
-        <v>1112</v>
-      </c>
-      <c r="I115" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J115" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="K115" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="L115" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="M115" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="N115" s="22" t="s">
-        <v>1113</v>
-      </c>
-      <c r="O115" s="25">
-        <v>44896</v>
-      </c>
-      <c r="P115" s="23">
-        <v>44</v>
-      </c>
-      <c r="Q115" s="23">
-        <v>5</v>
-      </c>
-      <c r="R115" s="23">
-        <v>44</v>
-      </c>
-      <c r="S115" s="23">
-        <v>38</v>
-      </c>
-      <c r="T115" s="22" t="s">
-        <v>1114</v>
-      </c>
-      <c r="U115" s="25">
-        <v>25850</v>
-      </c>
-      <c r="V115" s="23">
-        <v>21555550</v>
-      </c>
-      <c r="W115" s="22" t="s">
-        <v>1115</v>
-      </c>
-      <c r="X115" s="25">
-        <v>37432</v>
-      </c>
-      <c r="Y115" s="23">
-        <v>43843291</v>
-      </c>
-      <c r="Z115" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA115" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB115" s="26"/>
-      <c r="AC115" s="22" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AD115" s="25">
-        <v>38062</v>
-      </c>
-      <c r="AE115" s="23">
-        <v>45508098</v>
-      </c>
-      <c r="AF115" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG115" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH115" s="26"/>
-      <c r="AI115" s="22" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AJ115" s="25">
-        <v>38853</v>
-      </c>
-      <c r="AK115" s="23">
-        <v>47107320</v>
-      </c>
-      <c r="AL115" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM115" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN115" s="26"/>
-      <c r="AO115" s="22" t="s">
-        <v>1115</v>
-      </c>
-      <c r="AP115" s="23">
-        <v>43843291</v>
-      </c>
-      <c r="AQ115" s="22" t="s">
-        <v>1117</v>
-      </c>
-      <c r="AR115" s="23">
-        <v>47107320</v>
-      </c>
-      <c r="AS115" s="22" t="s">
-        <v>1116</v>
-      </c>
-      <c r="AT115" s="23">
-        <v>45508098</v>
-      </c>
-      <c r="AU115" s="27">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="116" spans="1:47" ht="39" thickBot="1">
-      <c r="A116" s="6">
-        <v>46273.391805555555</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D116" s="8">
-        <v>18001714</v>
-      </c>
-      <c r="E116" s="8">
-        <v>19021967</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H116" s="8">
-        <v>3382409515</v>
-      </c>
-      <c r="I116" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J116" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K116" s="11"/>
-      <c r="L116" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="M116" s="7" t="s">
-        <v>1121</v>
-      </c>
-      <c r="N116" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="O116" s="10">
-        <v>37075</v>
-      </c>
-      <c r="P116" s="8">
-        <v>52</v>
-      </c>
-      <c r="Q116" s="8">
-        <v>52</v>
-      </c>
-      <c r="R116" s="8">
-        <v>52</v>
-      </c>
-      <c r="S116" s="8">
-        <v>45</v>
-      </c>
-      <c r="T116" s="7" t="s">
-        <v>1122</v>
-      </c>
-      <c r="U116" s="10">
-        <v>26860</v>
-      </c>
-      <c r="V116" s="8">
-        <v>23255156</v>
-      </c>
-      <c r="W116" s="7" t="s">
-        <v>1123</v>
-      </c>
-      <c r="X116" s="10">
-        <v>35901</v>
-      </c>
-      <c r="Y116" s="8">
-        <v>40959346</v>
-      </c>
-      <c r="Z116" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA116" s="11"/>
-      <c r="AB116" s="11"/>
-      <c r="AC116" s="11"/>
-      <c r="AD116" s="11"/>
-      <c r="AE116" s="11"/>
-      <c r="AF116" s="11"/>
-      <c r="AG116" s="11"/>
-      <c r="AH116" s="11"/>
-      <c r="AI116" s="11"/>
-      <c r="AJ116" s="11"/>
-      <c r="AK116" s="11"/>
-      <c r="AL116" s="11"/>
-      <c r="AM116" s="11"/>
-      <c r="AN116" s="11"/>
-      <c r="AO116" s="7" t="s">
-        <v>1124</v>
-      </c>
-      <c r="AP116" s="8">
-        <v>23255156</v>
-      </c>
-      <c r="AQ116" s="11"/>
-      <c r="AR116" s="11"/>
-      <c r="AS116" s="11"/>
-      <c r="AT116" s="11"/>
-      <c r="AU116" s="28">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="117" spans="1:47" ht="26.25" thickBot="1">
-      <c r="A117" s="21">
-        <v>46273.624247685184</v>
-      </c>
-      <c r="B117" s="22" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C117" s="22" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D117" s="23">
-        <v>21767041</v>
-      </c>
-      <c r="E117" s="24">
-        <v>25976</v>
-      </c>
-      <c r="F117" s="22" t="s">
-        <v>1127</v>
-      </c>
-      <c r="G117" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H117" s="22" t="s">
-        <v>1128</v>
-      </c>
-      <c r="I117" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J117" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="K117" s="22" t="s">
-        <v>1129</v>
-      </c>
-      <c r="L117" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="M117" s="22" t="s">
-        <v>1130</v>
-      </c>
-      <c r="N117" s="22" t="s">
-        <v>1129</v>
-      </c>
-      <c r="O117" s="25">
-        <v>39449</v>
-      </c>
-      <c r="P117" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q117" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="R117" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="S117" s="23">
-        <v>36</v>
-      </c>
-      <c r="T117" s="22" t="s">
-        <v>1131</v>
-      </c>
-      <c r="U117" s="25">
-        <v>25490</v>
-      </c>
-      <c r="V117" s="23">
-        <v>20703838</v>
-      </c>
-      <c r="W117" s="22" t="s">
-        <v>1132</v>
-      </c>
-      <c r="X117" s="25">
-        <v>35028</v>
-      </c>
-      <c r="Y117" s="23">
-        <v>39049283</v>
-      </c>
-      <c r="Z117" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA117" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB117" s="22" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AC117" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AD117" s="25">
-        <v>36770</v>
-      </c>
-      <c r="AE117" s="23">
-        <v>42532435</v>
-      </c>
-      <c r="AF117" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG117" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH117" s="22" t="s">
-        <v>1133</v>
-      </c>
-      <c r="AI117" s="22" t="s">
-        <v>1135</v>
-      </c>
-      <c r="AJ117" s="25">
-        <v>16681</v>
-      </c>
-      <c r="AK117" s="23" t="s">
-        <v>1136</v>
-      </c>
-      <c r="AL117" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM117" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AN117" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="AO117" s="22" t="s">
-        <v>1131</v>
-      </c>
-      <c r="AP117" s="23">
-        <v>20703838</v>
-      </c>
-      <c r="AQ117" s="22" t="s">
-        <v>1137</v>
-      </c>
-      <c r="AR117" s="23">
-        <v>39049283</v>
-      </c>
-      <c r="AS117" s="22" t="s">
-        <v>1134</v>
-      </c>
-      <c r="AT117" s="23">
-        <v>42532435</v>
-      </c>
-      <c r="AU117" s="27">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="118" spans="1:47" ht="64.5" thickBot="1">
-      <c r="A118" s="6">
-        <v>46273.680868055555</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D118" s="8">
-        <v>21767233</v>
-      </c>
-      <c r="E118" s="9">
-        <v>26231</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H118" s="8">
-        <v>3382446330</v>
-      </c>
-      <c r="I118" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J118" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K118" s="7" t="s">
-        <v>1141</v>
-      </c>
-      <c r="L118" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M118" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="N118" s="7" t="s">
-        <v>1142</v>
-      </c>
-      <c r="O118" s="10">
-        <v>33574</v>
-      </c>
-      <c r="P118" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q118" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="R118" s="8">
-        <v>48</v>
-      </c>
-      <c r="S118" s="8">
-        <v>41</v>
-      </c>
-      <c r="T118" s="7" t="s">
-        <v>1143</v>
-      </c>
-      <c r="U118" s="10">
-        <v>29009</v>
-      </c>
-      <c r="V118" s="8">
-        <v>27419861</v>
-      </c>
-      <c r="W118" s="7" t="s">
-        <v>1144</v>
-      </c>
-      <c r="X118" s="10">
-        <v>39071</v>
-      </c>
-      <c r="Y118" s="8">
-        <v>47508181</v>
-      </c>
-      <c r="Z118" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA118" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB118" s="11"/>
-      <c r="AC118" s="7" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AD118" s="10">
-        <v>40188</v>
-      </c>
-      <c r="AE118" s="8">
-        <v>49817254</v>
-      </c>
-      <c r="AF118" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG118" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH118" s="11"/>
-      <c r="AI118" s="11"/>
-      <c r="AJ118" s="11"/>
-      <c r="AK118" s="11"/>
-      <c r="AL118" s="11"/>
-      <c r="AM118" s="11"/>
-      <c r="AN118" s="11"/>
-      <c r="AO118" s="7" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AP118" s="8">
-        <v>27419861</v>
-      </c>
-      <c r="AQ118" s="7" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AR118" s="8">
-        <v>47508181</v>
-      </c>
-      <c r="AS118" s="7" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AT118" s="8">
-        <v>49817254</v>
-      </c>
-      <c r="AU118" s="28">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="119" spans="1:47" ht="64.5" thickBot="1">
-      <c r="A119" s="12">
-        <v>46273.692303240743</v>
-      </c>
-      <c r="B119" s="13" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C119" s="13" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D119" s="14">
-        <v>21767233</v>
-      </c>
-      <c r="E119" s="15">
-        <v>26231</v>
-      </c>
-      <c r="F119" s="13" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H119" s="14">
-        <v>3382446330</v>
-      </c>
-      <c r="I119" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J119" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K119" s="13" t="s">
-        <v>1141</v>
-      </c>
-      <c r="L119" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="M119" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="N119" s="13" t="s">
-        <v>1142</v>
-      </c>
-      <c r="O119" s="16">
-        <v>33574</v>
-      </c>
-      <c r="P119" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q119" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="R119" s="14">
-        <v>48</v>
-      </c>
-      <c r="S119" s="14">
-        <v>41</v>
-      </c>
-      <c r="T119" s="13" t="s">
-        <v>1143</v>
-      </c>
-      <c r="U119" s="16">
-        <v>29009</v>
-      </c>
-      <c r="V119" s="14">
-        <v>27419861</v>
-      </c>
-      <c r="W119" s="13" t="s">
-        <v>1144</v>
-      </c>
-      <c r="X119" s="16">
-        <v>39071</v>
-      </c>
-      <c r="Y119" s="14">
-        <v>47508181</v>
-      </c>
-      <c r="Z119" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA119" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB119" s="17"/>
-      <c r="AC119" s="13" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AD119" s="16">
-        <v>40189</v>
-      </c>
-      <c r="AE119" s="14">
-        <v>49817254</v>
-      </c>
-      <c r="AF119" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG119" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AH119" s="17"/>
-      <c r="AI119" s="17"/>
-      <c r="AJ119" s="17"/>
-      <c r="AK119" s="17"/>
-      <c r="AL119" s="17"/>
-      <c r="AM119" s="17"/>
-      <c r="AN119" s="17"/>
-      <c r="AO119" s="13" t="s">
-        <v>1143</v>
-      </c>
-      <c r="AP119" s="14">
-        <v>27419861</v>
-      </c>
-      <c r="AQ119" s="13" t="s">
-        <v>1146</v>
-      </c>
-      <c r="AR119" s="14">
-        <v>47508181</v>
-      </c>
-      <c r="AS119" s="13" t="s">
-        <v>1145</v>
-      </c>
-      <c r="AT119" s="14">
-        <v>49817254</v>
-      </c>
-      <c r="AU119" s="18">
         <v>47</v>
       </c>
     </row>

--- a/declara.xlsx
+++ b/declara.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="1320">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -3383,6 +3383,597 @@
   </si>
   <si>
     <t>Facundo Carlos Gianolio</t>
+  </si>
+  <si>
+    <t>vaninaortiz042@gmail.com</t>
+  </si>
+  <si>
+    <t>Ortiz Silvia Vanina</t>
+  </si>
+  <si>
+    <t>30 06 1983</t>
+  </si>
+  <si>
+    <t>Lavalleja 776</t>
+  </si>
+  <si>
+    <t>3382 462773</t>
+  </si>
+  <si>
+    <t>Espacio verde</t>
+  </si>
+  <si>
+    <t>lorenasebrero@gmail.com</t>
+  </si>
+  <si>
+    <t>Moreno lorena</t>
+  </si>
+  <si>
+    <t>Arenales 1200</t>
+  </si>
+  <si>
+    <t>alesosaa1977@gmail.com</t>
+  </si>
+  <si>
+    <t>Sosa Alejandra Daniela</t>
+  </si>
+  <si>
+    <t>Carballeira 792</t>
+  </si>
+  <si>
+    <t>Tiroides. Trastorno de ansiedad. Pánico</t>
+  </si>
+  <si>
+    <t>Inspector de tránsito y inspección</t>
+  </si>
+  <si>
+    <t>rzanelli2@gmail.com</t>
+  </si>
+  <si>
+    <t>Zanelli Ruben Oscar</t>
+  </si>
+  <si>
+    <t>Rivadavia 69</t>
+  </si>
+  <si>
+    <t>Tecnico en Administracion de Empresas</t>
+  </si>
+  <si>
+    <t>gabybarroso244@gmail.com</t>
+  </si>
+  <si>
+    <t>Barroso María Gabriela</t>
+  </si>
+  <si>
+    <t>Formosa 43</t>
+  </si>
+  <si>
+    <t>Obra y servicios</t>
+  </si>
+  <si>
+    <t>Residuos</t>
+  </si>
+  <si>
+    <t>beto.galli35@gmail.com</t>
+  </si>
+  <si>
+    <t>Alberto domingo galli</t>
+  </si>
+  <si>
+    <t>Santa rosa 72</t>
+  </si>
+  <si>
+    <t>fffflor22@gmail.com</t>
+  </si>
+  <si>
+    <t>Rodriguez Florencia Magali</t>
+  </si>
+  <si>
+    <t>Dean Funes 435</t>
+  </si>
+  <si>
+    <t>Licencia de Conducir</t>
+  </si>
+  <si>
+    <t>danielalucena44@gmail.com</t>
+  </si>
+  <si>
+    <t>Daniela Paola Lucena</t>
+  </si>
+  <si>
+    <t>Brown 50</t>
+  </si>
+  <si>
+    <t>Tec RRHH / Docente</t>
+  </si>
+  <si>
+    <t>Oficina de Empleo</t>
+  </si>
+  <si>
+    <t>andrelei2017@gmail.com</t>
+  </si>
+  <si>
+    <t>Leite Andrea</t>
+  </si>
+  <si>
+    <t>Jujuy 328</t>
+  </si>
+  <si>
+    <t>Docenre/ tec en adm.de empresas</t>
+  </si>
+  <si>
+    <t>Of.de empleo</t>
+  </si>
+  <si>
+    <t>rojasyonatan92@gmail.com</t>
+  </si>
+  <si>
+    <t>Rojas Jonatan</t>
+  </si>
+  <si>
+    <t>Boulevard Belgrano 895</t>
+  </si>
+  <si>
+    <t>Espacios verde</t>
+  </si>
+  <si>
+    <t>Mantenimiento</t>
+  </si>
+  <si>
+    <t>pedrogustavo.salinas@gmail.com</t>
+  </si>
+  <si>
+    <t>salinas silva Pedro gustavo</t>
+  </si>
+  <si>
+    <t>alixe Pero 1118</t>
+  </si>
+  <si>
+    <t>secundario completo</t>
+  </si>
+  <si>
+    <t>ipertenso</t>
+  </si>
+  <si>
+    <t>inspeccion gral</t>
+  </si>
+  <si>
+    <t>jefe oficina</t>
+  </si>
+  <si>
+    <t>marcosriveros013@gmail.com</t>
+  </si>
+  <si>
+    <t>Riveros Marcos anibal</t>
+  </si>
+  <si>
+    <t>Bárbara isla 435</t>
+  </si>
+  <si>
+    <t>Técnico radio TV cromatico</t>
+  </si>
+  <si>
+    <t>Espacios verdes</t>
+  </si>
+  <si>
+    <t>Mantenimientos</t>
+  </si>
+  <si>
+    <t>tejadadiegomauricio@gmail.com</t>
+  </si>
+  <si>
+    <t>Tejada Diego</t>
+  </si>
+  <si>
+    <t>Magallanes 402</t>
+  </si>
+  <si>
+    <t>Tecnico en computación</t>
+  </si>
+  <si>
+    <t>Scoliosis</t>
+  </si>
+  <si>
+    <t>Operador/examinador</t>
+  </si>
+  <si>
+    <t>briangrassisrufino@gmail.com</t>
+  </si>
+  <si>
+    <t>Grassis Brian</t>
+  </si>
+  <si>
+    <t>Colon 956</t>
+  </si>
+  <si>
+    <t>Centro de Monitoreo</t>
+  </si>
+  <si>
+    <t>marianaariasreyna@gmail.com</t>
+  </si>
+  <si>
+    <t>Arias Mariana</t>
+  </si>
+  <si>
+    <t>Primero de Mayo 566</t>
+  </si>
+  <si>
+    <t>Prof.de EGB y Prof de Nivel Inicial</t>
+  </si>
+  <si>
+    <t>..</t>
+  </si>
+  <si>
+    <t>Centro de Acción Familiar</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>luisinap19@gmail.com</t>
+  </si>
+  <si>
+    <t>Perez Luisina</t>
+  </si>
+  <si>
+    <t>31 de agosto de 1991</t>
+  </si>
+  <si>
+    <t>Santa Fe 485</t>
+  </si>
+  <si>
+    <t>Profesora de Educación Secundaria en Historia y Profesora de Educación Secundaria en Geografía</t>
+  </si>
+  <si>
+    <t>Centro Cultural</t>
+  </si>
+  <si>
+    <t>zeballezraul@gmail.com</t>
+  </si>
+  <si>
+    <t>Zeballez Raul Ernesto</t>
+  </si>
+  <si>
+    <t>19 01 1995</t>
+  </si>
+  <si>
+    <t>Julián sosa 770</t>
+  </si>
+  <si>
+    <t>Recolección de residuos domiciliario</t>
+  </si>
+  <si>
+    <t>maxisalzar2021@gmail.com</t>
+  </si>
+  <si>
+    <t>Salazar maximiliano</t>
+  </si>
+  <si>
+    <t>Remedios de escalada 555</t>
+  </si>
+  <si>
+    <t>Varices</t>
+  </si>
+  <si>
+    <t>Varias</t>
+  </si>
+  <si>
+    <t>42 pampero</t>
+  </si>
+  <si>
+    <t>mdlf546@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucero Fernando</t>
+  </si>
+  <si>
+    <t>1 de mayo 370</t>
+  </si>
+  <si>
+    <t>Recolección de residuos</t>
+  </si>
+  <si>
+    <t>Colero</t>
+  </si>
+  <si>
+    <t>gonzalezsergiod65@gmail.com</t>
+  </si>
+  <si>
+    <t>González Sergio Daniel</t>
+  </si>
+  <si>
+    <t>06 de octubre 1965</t>
+  </si>
+  <si>
+    <t>Carballeira 1360</t>
+  </si>
+  <si>
+    <t>Corralón taller</t>
+  </si>
+  <si>
+    <t>Soldador</t>
+  </si>
+  <si>
+    <t>sg9451148@gmail.com</t>
+  </si>
+  <si>
+    <t>Gutiérrez Susana</t>
+  </si>
+  <si>
+    <t>Rio negro 1166</t>
+  </si>
+  <si>
+    <t>Curso. Auxiliar de sala maternal</t>
+  </si>
+  <si>
+    <t>Ipertensa</t>
+  </si>
+  <si>
+    <t>Centro acción familiar</t>
+  </si>
+  <si>
+    <t>Auxiliar de docente</t>
+  </si>
+  <si>
+    <t>walterygii53@gmail.com</t>
+  </si>
+  <si>
+    <t>Martín Walter Adolfo</t>
+  </si>
+  <si>
+    <t>Santa rosa 391</t>
+  </si>
+  <si>
+    <t>Alérgico</t>
+  </si>
+  <si>
+    <t>cristianvara10@gmail.com</t>
+  </si>
+  <si>
+    <t>Vara Cristian Alberto</t>
+  </si>
+  <si>
+    <t>Maestro rufinense 26</t>
+  </si>
+  <si>
+    <t>Chofer residuos</t>
+  </si>
+  <si>
+    <t>maximiliano.mp6@gmail.com</t>
+  </si>
+  <si>
+    <t>Chacon maximiliano</t>
+  </si>
+  <si>
+    <t>Catamarca 1330</t>
+  </si>
+  <si>
+    <t>Voluminosos</t>
+  </si>
+  <si>
+    <t>Galassi marcos tomas</t>
+  </si>
+  <si>
+    <t>Galassi Barbarita guadalupe</t>
+  </si>
+  <si>
+    <t>Galassi Ulises benjamin</t>
+  </si>
+  <si>
+    <t>Ortiz Vanina silvia</t>
+  </si>
+  <si>
+    <t>Sebrero facundo</t>
+  </si>
+  <si>
+    <t>Sebrero mateo</t>
+  </si>
+  <si>
+    <t>Sebrero milagros</t>
+  </si>
+  <si>
+    <t>SEBRERO luciana</t>
+  </si>
+  <si>
+    <t>Sebrero luciana</t>
+  </si>
+  <si>
+    <t>Sosa Emiliano Héctor</t>
+  </si>
+  <si>
+    <t>Pardo Arai lucila</t>
+  </si>
+  <si>
+    <t>Pardo Nicolás jeremías Yamil</t>
+  </si>
+  <si>
+    <t>Pardo Miqueas Josué jonas</t>
+  </si>
+  <si>
+    <t>Graciela Mirian Tarfa</t>
+  </si>
+  <si>
+    <t>Zanelli Tarfa Lucas</t>
+  </si>
+  <si>
+    <t>Graciela Miriam Tarfa</t>
+  </si>
+  <si>
+    <t>Leonor Gisela Urquiza</t>
+  </si>
+  <si>
+    <t>Alan benjamín barroso</t>
+  </si>
+  <si>
+    <t>Jeremías Rodrigo Urquiza</t>
+  </si>
+  <si>
+    <t>Lucía Belén Urquiza</t>
+  </si>
+  <si>
+    <t>Silvana Mariela lopez</t>
+  </si>
+  <si>
+    <t>Romero Rodriguez Pierina Elena</t>
+  </si>
+  <si>
+    <t>FernandoCalzia</t>
+  </si>
+  <si>
+    <t>Calzia Lucas</t>
+  </si>
+  <si>
+    <t>Estudiante Abogacia</t>
+  </si>
+  <si>
+    <t>Valentina Calzia</t>
+  </si>
+  <si>
+    <t>Tec Radióloga</t>
+  </si>
+  <si>
+    <t>Fernando Calzia</t>
+  </si>
+  <si>
+    <t>Calzia Valentina</t>
+  </si>
+  <si>
+    <t>Leite Alvaro Patricio</t>
+  </si>
+  <si>
+    <t>Sicologia (en curso)</t>
+  </si>
+  <si>
+    <t>Alvaro Patricio Leite</t>
+  </si>
+  <si>
+    <t>Nadie</t>
+  </si>
+  <si>
+    <t>Rojas josefina</t>
+  </si>
+  <si>
+    <t>Josefina rojas</t>
+  </si>
+  <si>
+    <t>Verónica Valeria robledo</t>
+  </si>
+  <si>
+    <t>Renata Marisol salinas Robledo</t>
+  </si>
+  <si>
+    <t>técnica de diseño graficO</t>
+  </si>
+  <si>
+    <t>tomas salinas robledo</t>
+  </si>
+  <si>
+    <t>Renata Marisol salinas robleso</t>
+  </si>
+  <si>
+    <t>tomas salinas</t>
+  </si>
+  <si>
+    <t>——————</t>
+  </si>
+  <si>
+    <t>Tejada benjamin</t>
+  </si>
+  <si>
+    <t>Benjamín tejada</t>
+  </si>
+  <si>
+    <t>Ameri Daiana</t>
+  </si>
+  <si>
+    <t>Grassis Maria Amapola</t>
+  </si>
+  <si>
+    <t>Maria Amapola Grassis</t>
+  </si>
+  <si>
+    <t>Daiana Ameri</t>
+  </si>
+  <si>
+    <t>Cristian Valentin Comellas</t>
+  </si>
+  <si>
+    <t>Comellas Arias Alfonsina</t>
+  </si>
+  <si>
+    <t>Nivel Primario</t>
+  </si>
+  <si>
+    <t>Comellas Arias Felipe</t>
+  </si>
+  <si>
+    <t>Nivel Inicial</t>
+  </si>
+  <si>
+    <t>Servera Facundo</t>
+  </si>
+  <si>
+    <t>Servera Valentino</t>
+  </si>
+  <si>
+    <t>Maria de los angeles balmaceda</t>
+  </si>
+  <si>
+    <t>Zeballez amparo</t>
+  </si>
+  <si>
+    <t>Zeballez pilar</t>
+  </si>
+  <si>
+    <t>Amparo zeballez</t>
+  </si>
+  <si>
+    <t>Pilar zeballez</t>
+  </si>
+  <si>
+    <t>Paula mancuello</t>
+  </si>
+  <si>
+    <t>Samuel salaza</t>
+  </si>
+  <si>
+    <t>Samuel salazar</t>
+  </si>
+  <si>
+    <t>Suares Gabriela</t>
+  </si>
+  <si>
+    <t>Lucero facundo</t>
+  </si>
+  <si>
+    <t>Zantino lucero</t>
+  </si>
+  <si>
+    <t>Gabriela suares</t>
+  </si>
+  <si>
+    <t>Susana Gutiérrez</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>Gisela Natalia Rebuffo</t>
+  </si>
+  <si>
+    <t>Martín Emma Lucia</t>
+  </si>
+  <si>
+    <t>Rocio Milagros Martín</t>
+  </si>
+  <si>
+    <t>Candela Abigail Martín</t>
+  </si>
+  <si>
+    <t>Emma Lucia Martin</t>
+  </si>
+  <si>
+    <t>Gloria peña</t>
   </si>
 </sst>
 </file>
@@ -3440,7 +4031,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -3763,11 +4354,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3918,6 +4539,30 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4214,7 +4859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -17614,6 +18259,2758 @@
         <v>47</v>
       </c>
     </row>
+    <row r="115" spans="1:47" ht="39" thickBot="1">
+      <c r="A115" s="45">
+        <v>46274.39230324074</v>
+      </c>
+      <c r="B115" s="46" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C115" s="46" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D115" s="47">
+        <v>29931800</v>
+      </c>
+      <c r="E115" s="46" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F115" s="46" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G115" s="46" t="s">
+        <v>957</v>
+      </c>
+      <c r="H115" s="46" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I115" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="J115" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="K115" s="46" t="s">
+        <v>471</v>
+      </c>
+      <c r="L115" s="46" t="s">
+        <v>471</v>
+      </c>
+      <c r="M115" s="46" t="s">
+        <v>790</v>
+      </c>
+      <c r="N115" s="46" t="s">
+        <v>1128</v>
+      </c>
+      <c r="O115" s="50">
+        <v>44896</v>
+      </c>
+      <c r="P115" s="47">
+        <v>44</v>
+      </c>
+      <c r="Q115" s="47">
+        <v>5</v>
+      </c>
+      <c r="R115" s="47">
+        <v>44</v>
+      </c>
+      <c r="S115" s="47">
+        <v>38</v>
+      </c>
+      <c r="T115" s="49"/>
+      <c r="U115" s="49"/>
+      <c r="V115" s="49"/>
+      <c r="W115" s="46" t="s">
+        <v>1245</v>
+      </c>
+      <c r="X115" s="50">
+        <v>39324</v>
+      </c>
+      <c r="Y115" s="47">
+        <v>47779502</v>
+      </c>
+      <c r="Z115" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA115" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB115" s="49"/>
+      <c r="AC115" s="46" t="s">
+        <v>1246</v>
+      </c>
+      <c r="AD115" s="50">
+        <v>39961</v>
+      </c>
+      <c r="AE115" s="47">
+        <v>49574874</v>
+      </c>
+      <c r="AF115" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG115" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH115" s="49"/>
+      <c r="AI115" s="46" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AJ115" s="50">
+        <v>40934</v>
+      </c>
+      <c r="AK115" s="47">
+        <v>52135722</v>
+      </c>
+      <c r="AL115" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM115" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN115" s="49"/>
+      <c r="AO115" s="46" t="s">
+        <v>1248</v>
+      </c>
+      <c r="AP115" s="47">
+        <v>29931800</v>
+      </c>
+      <c r="AQ115" s="49"/>
+      <c r="AR115" s="49"/>
+      <c r="AS115" s="49"/>
+      <c r="AT115" s="49"/>
+      <c r="AU115" s="51">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="116" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A116" s="6">
+        <v>46274.412824074076</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D116" s="8">
+        <v>32348294</v>
+      </c>
+      <c r="E116" s="7">
+        <v>1021987</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H116" s="8">
+        <v>3382461730</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K116" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="L116" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M116" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="N116" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="O116" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P116" s="8">
+        <v>48</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>5</v>
+      </c>
+      <c r="R116" s="8">
+        <v>48</v>
+      </c>
+      <c r="S116" s="8">
+        <v>39</v>
+      </c>
+      <c r="T116" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="U116" s="10">
+        <v>30858</v>
+      </c>
+      <c r="V116" s="8">
+        <v>30623227</v>
+      </c>
+      <c r="W116" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="X116" s="10">
+        <v>37994</v>
+      </c>
+      <c r="Y116" s="8">
+        <v>45414893</v>
+      </c>
+      <c r="Z116" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA116" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB116" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC116" s="7" t="s">
+        <v>1251</v>
+      </c>
+      <c r="AD116" s="10">
+        <v>38398</v>
+      </c>
+      <c r="AE116" s="8">
+        <v>46367988</v>
+      </c>
+      <c r="AF116" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG116" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH116" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI116" s="7" t="s">
+        <v>1252</v>
+      </c>
+      <c r="AJ116" s="10">
+        <v>46880</v>
+      </c>
+      <c r="AK116" s="8">
+        <v>56965014</v>
+      </c>
+      <c r="AL116" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM116" s="11"/>
+      <c r="AN116" s="11"/>
+      <c r="AO116" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="AP116" s="8">
+        <v>30623227</v>
+      </c>
+      <c r="AQ116" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AR116" s="8">
+        <v>56965014</v>
+      </c>
+      <c r="AS116" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="AT116" s="8">
+        <v>32348294</v>
+      </c>
+      <c r="AU116" s="28">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="117" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A117" s="21">
+        <v>46275.366157407407</v>
+      </c>
+      <c r="B117" s="22" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C117" s="22" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D117" s="23">
+        <v>25773900</v>
+      </c>
+      <c r="E117" s="24">
+        <v>28211</v>
+      </c>
+      <c r="F117" s="22" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G117" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H117" s="23">
+        <v>3382461745</v>
+      </c>
+      <c r="I117" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J117" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K117" s="26"/>
+      <c r="L117" s="22" t="s">
+        <v>1135</v>
+      </c>
+      <c r="M117" s="22" t="s">
+        <v>560</v>
+      </c>
+      <c r="N117" s="22" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O117" s="25">
+        <v>32632</v>
+      </c>
+      <c r="P117" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q117" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="R117" s="23">
+        <v>54</v>
+      </c>
+      <c r="S117" s="23">
+        <v>40</v>
+      </c>
+      <c r="T117" s="22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="U117" s="25">
+        <v>31565</v>
+      </c>
+      <c r="V117" s="23">
+        <v>31592049</v>
+      </c>
+      <c r="W117" s="22" t="s">
+        <v>1255</v>
+      </c>
+      <c r="X117" s="25">
+        <v>36516</v>
+      </c>
+      <c r="Y117" s="23">
+        <v>41654825</v>
+      </c>
+      <c r="Z117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA117" s="26"/>
+      <c r="AB117" s="26"/>
+      <c r="AC117" s="22" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AD117" s="25">
+        <v>37555</v>
+      </c>
+      <c r="AE117" s="23">
+        <v>44067889</v>
+      </c>
+      <c r="AF117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH117" s="26"/>
+      <c r="AI117" s="22" t="s">
+        <v>1257</v>
+      </c>
+      <c r="AJ117" s="25">
+        <v>38415</v>
+      </c>
+      <c r="AK117" s="23">
+        <v>46299656</v>
+      </c>
+      <c r="AL117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM117" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN117" s="26"/>
+      <c r="AO117" s="22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AP117" s="23">
+        <v>31592049</v>
+      </c>
+      <c r="AQ117" s="26"/>
+      <c r="AR117" s="26"/>
+      <c r="AS117" s="26"/>
+      <c r="AT117" s="26"/>
+      <c r="AU117" s="27">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="118" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A118" s="6">
+        <v>46275.410578703704</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D118" s="8">
+        <v>20703879</v>
+      </c>
+      <c r="E118" s="9">
+        <v>25551</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H118" s="8">
+        <v>3382456231</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L118" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M118" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="N118" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="O118" s="10">
+        <v>36647</v>
+      </c>
+      <c r="P118" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q118" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R118" s="8">
+        <v>46</v>
+      </c>
+      <c r="S118" s="8">
+        <v>43</v>
+      </c>
+      <c r="T118" s="7" t="s">
+        <v>1258</v>
+      </c>
+      <c r="U118" s="10">
+        <v>25009</v>
+      </c>
+      <c r="V118" s="8">
+        <v>20233114</v>
+      </c>
+      <c r="W118" s="7" t="s">
+        <v>1259</v>
+      </c>
+      <c r="X118" s="10">
+        <v>40297</v>
+      </c>
+      <c r="Y118" s="8">
+        <v>50060277</v>
+      </c>
+      <c r="Z118" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA118" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB118" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="AC118" s="11"/>
+      <c r="AD118" s="11"/>
+      <c r="AE118" s="11"/>
+      <c r="AF118" s="11"/>
+      <c r="AG118" s="11"/>
+      <c r="AH118" s="11"/>
+      <c r="AI118" s="11"/>
+      <c r="AJ118" s="11"/>
+      <c r="AK118" s="11"/>
+      <c r="AL118" s="11"/>
+      <c r="AM118" s="11"/>
+      <c r="AN118" s="11"/>
+      <c r="AO118" s="7" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AP118" s="8">
+        <v>20233114</v>
+      </c>
+      <c r="AQ118" s="11"/>
+      <c r="AR118" s="11"/>
+      <c r="AS118" s="11"/>
+      <c r="AT118" s="11"/>
+      <c r="AU118" s="28">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="119" spans="1:47" ht="39" thickBot="1">
+      <c r="A119" s="21">
+        <v>46275.850381944445</v>
+      </c>
+      <c r="B119" s="22" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C119" s="22" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D119" s="23">
+        <v>28720029</v>
+      </c>
+      <c r="E119" s="24">
+        <v>29636</v>
+      </c>
+      <c r="F119" s="22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G119" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H119" s="23">
+        <v>3382507129</v>
+      </c>
+      <c r="I119" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J119" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K119" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="L119" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M119" s="22" t="s">
+        <v>1144</v>
+      </c>
+      <c r="N119" s="22" t="s">
+        <v>1145</v>
+      </c>
+      <c r="O119" s="25">
+        <v>44896</v>
+      </c>
+      <c r="P119" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q119" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="R119" s="23">
+        <v>58</v>
+      </c>
+      <c r="S119" s="23">
+        <v>39</v>
+      </c>
+      <c r="T119" s="22" t="s">
+        <v>1261</v>
+      </c>
+      <c r="U119" s="25">
+        <v>30929</v>
+      </c>
+      <c r="V119" s="23">
+        <v>30623285</v>
+      </c>
+      <c r="W119" s="22" t="s">
+        <v>1262</v>
+      </c>
+      <c r="X119" s="25">
+        <v>39328</v>
+      </c>
+      <c r="Y119" s="23">
+        <v>48271373</v>
+      </c>
+      <c r="Z119" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA119" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB119" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC119" s="22" t="s">
+        <v>1263</v>
+      </c>
+      <c r="AD119" s="25">
+        <v>39391</v>
+      </c>
+      <c r="AE119" s="23">
+        <v>47779538</v>
+      </c>
+      <c r="AF119" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG119" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH119" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI119" s="22" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AJ119" s="25">
+        <v>42458</v>
+      </c>
+      <c r="AK119" s="23">
+        <v>55651701</v>
+      </c>
+      <c r="AL119" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM119" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN119" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AO119" s="22" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AP119" s="23">
+        <v>55651701</v>
+      </c>
+      <c r="AQ119" s="22" t="s">
+        <v>1262</v>
+      </c>
+      <c r="AR119" s="23">
+        <v>48271373</v>
+      </c>
+      <c r="AS119" s="22" t="s">
+        <v>1263</v>
+      </c>
+      <c r="AT119" s="23">
+        <v>47779538</v>
+      </c>
+      <c r="AU119" s="27">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="120" spans="1:47" ht="39" thickBot="1">
+      <c r="A120" s="6">
+        <v>46275.863703703704</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D120" s="8">
+        <v>34408600</v>
+      </c>
+      <c r="E120" s="52">
+        <v>32902</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H120" s="7">
+        <v>338215418045</v>
+      </c>
+      <c r="I120" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J120" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K120" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="L120" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M120" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="N120" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="O120" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P120" s="8">
+        <v>52</v>
+      </c>
+      <c r="Q120" s="8">
+        <v>7</v>
+      </c>
+      <c r="R120" s="8">
+        <v>54</v>
+      </c>
+      <c r="S120" s="8">
+        <v>42</v>
+      </c>
+      <c r="T120" s="11"/>
+      <c r="U120" s="11"/>
+      <c r="V120" s="11"/>
+      <c r="W120" s="11"/>
+      <c r="X120" s="11"/>
+      <c r="Y120" s="11"/>
+      <c r="Z120" s="11"/>
+      <c r="AA120" s="11"/>
+      <c r="AB120" s="11"/>
+      <c r="AC120" s="11"/>
+      <c r="AD120" s="11"/>
+      <c r="AE120" s="11"/>
+      <c r="AF120" s="11"/>
+      <c r="AG120" s="11"/>
+      <c r="AH120" s="11"/>
+      <c r="AI120" s="11"/>
+      <c r="AJ120" s="11"/>
+      <c r="AK120" s="11"/>
+      <c r="AL120" s="11"/>
+      <c r="AM120" s="11"/>
+      <c r="AN120" s="11"/>
+      <c r="AO120" s="7" t="s">
+        <v>1265</v>
+      </c>
+      <c r="AP120" s="8">
+        <v>30623003</v>
+      </c>
+      <c r="AQ120" s="11"/>
+      <c r="AR120" s="11"/>
+      <c r="AS120" s="11"/>
+      <c r="AT120" s="11"/>
+      <c r="AU120" s="28">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="121" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A121" s="21">
+        <v>46276.355474537035</v>
+      </c>
+      <c r="B121" s="22" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C121" s="22" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D121" s="23">
+        <v>40277626</v>
+      </c>
+      <c r="E121" s="24">
+        <v>35634</v>
+      </c>
+      <c r="F121" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G121" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H121" s="23">
+        <v>3382415379</v>
+      </c>
+      <c r="I121" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J121" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K121" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="L121" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M121" s="22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="N121" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="O121" s="25">
+        <v>42196</v>
+      </c>
+      <c r="P121" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q121" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R121" s="23">
+        <v>38</v>
+      </c>
+      <c r="S121" s="23">
+        <v>35</v>
+      </c>
+      <c r="T121" s="26"/>
+      <c r="U121" s="26"/>
+      <c r="V121" s="26"/>
+      <c r="W121" s="22" t="s">
+        <v>1266</v>
+      </c>
+      <c r="X121" s="25">
+        <v>44603</v>
+      </c>
+      <c r="Y121" s="23">
+        <v>53103767</v>
+      </c>
+      <c r="Z121" s="26"/>
+      <c r="AA121" s="26"/>
+      <c r="AB121" s="26"/>
+      <c r="AC121" s="26"/>
+      <c r="AD121" s="26"/>
+      <c r="AE121" s="26"/>
+      <c r="AF121" s="26"/>
+      <c r="AG121" s="26"/>
+      <c r="AH121" s="26"/>
+      <c r="AI121" s="26"/>
+      <c r="AJ121" s="26"/>
+      <c r="AK121" s="26"/>
+      <c r="AL121" s="26"/>
+      <c r="AM121" s="26"/>
+      <c r="AN121" s="26"/>
+      <c r="AO121" s="22" t="s">
+        <v>1266</v>
+      </c>
+      <c r="AP121" s="23">
+        <v>53103767</v>
+      </c>
+      <c r="AQ121" s="26"/>
+      <c r="AR121" s="26"/>
+      <c r="AS121" s="26"/>
+      <c r="AT121" s="26"/>
+      <c r="AU121" s="27">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="122" spans="1:47" ht="39" thickBot="1">
+      <c r="A122" s="6">
+        <v>46276.355624999997</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D122" s="8">
+        <v>27338131</v>
+      </c>
+      <c r="E122" s="9">
+        <v>29237</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H122" s="8">
+        <v>3382408863</v>
+      </c>
+      <c r="I122" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J122" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K122" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L122" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M122" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="N122" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="O122" s="10">
+        <v>38782</v>
+      </c>
+      <c r="P122" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q122" s="8">
+        <v>1</v>
+      </c>
+      <c r="R122" s="8">
+        <v>36</v>
+      </c>
+      <c r="S122" s="8">
+        <v>39</v>
+      </c>
+      <c r="T122" s="7" t="s">
+        <v>1267</v>
+      </c>
+      <c r="U122" s="10">
+        <v>24593</v>
+      </c>
+      <c r="V122" s="8">
+        <v>17983320</v>
+      </c>
+      <c r="W122" s="7" t="s">
+        <v>1268</v>
+      </c>
+      <c r="X122" s="10">
+        <v>36430</v>
+      </c>
+      <c r="Y122" s="8">
+        <v>41654793</v>
+      </c>
+      <c r="Z122" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA122" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB122" s="7" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AC122" s="7" t="s">
+        <v>1270</v>
+      </c>
+      <c r="AD122" s="10">
+        <v>37137</v>
+      </c>
+      <c r="AE122" s="8">
+        <v>43843251</v>
+      </c>
+      <c r="AF122" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG122" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH122" s="7" t="s">
+        <v>1271</v>
+      </c>
+      <c r="AI122" s="11"/>
+      <c r="AJ122" s="11"/>
+      <c r="AK122" s="11"/>
+      <c r="AL122" s="11"/>
+      <c r="AM122" s="11"/>
+      <c r="AN122" s="11"/>
+      <c r="AO122" s="7" t="s">
+        <v>1272</v>
+      </c>
+      <c r="AP122" s="8">
+        <v>17983320</v>
+      </c>
+      <c r="AQ122" s="7" t="s">
+        <v>1268</v>
+      </c>
+      <c r="AR122" s="8">
+        <v>41654793</v>
+      </c>
+      <c r="AS122" s="7" t="s">
+        <v>1273</v>
+      </c>
+      <c r="AT122" s="8">
+        <v>43843251</v>
+      </c>
+      <c r="AU122" s="28">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="123" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A123" s="21">
+        <v>46276.363136574073</v>
+      </c>
+      <c r="B123" s="22" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C123" s="22" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D123" s="23">
+        <v>20233018</v>
+      </c>
+      <c r="E123" s="24">
+        <v>24893</v>
+      </c>
+      <c r="F123" s="22" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G123" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H123" s="23">
+        <v>3382572638</v>
+      </c>
+      <c r="I123" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J123" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K123" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L123" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="M123" s="22" t="s">
+        <v>1162</v>
+      </c>
+      <c r="N123" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="O123" s="25">
+        <v>38825</v>
+      </c>
+      <c r="P123" s="23">
+        <v>4</v>
+      </c>
+      <c r="Q123" s="23">
+        <v>4</v>
+      </c>
+      <c r="R123" s="23">
+        <v>50</v>
+      </c>
+      <c r="S123" s="23">
+        <v>38</v>
+      </c>
+      <c r="T123" s="26"/>
+      <c r="U123" s="26"/>
+      <c r="V123" s="26"/>
+      <c r="W123" s="22" t="s">
+        <v>1274</v>
+      </c>
+      <c r="X123" s="25">
+        <v>37336</v>
+      </c>
+      <c r="Y123" s="23">
+        <v>43843213</v>
+      </c>
+      <c r="Z123" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA123" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB123" s="22" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AC123" s="26"/>
+      <c r="AD123" s="26"/>
+      <c r="AE123" s="26"/>
+      <c r="AF123" s="26"/>
+      <c r="AG123" s="26"/>
+      <c r="AH123" s="26"/>
+      <c r="AI123" s="26"/>
+      <c r="AJ123" s="26"/>
+      <c r="AK123" s="26"/>
+      <c r="AL123" s="26"/>
+      <c r="AM123" s="26"/>
+      <c r="AN123" s="26"/>
+      <c r="AO123" s="22" t="s">
+        <v>1276</v>
+      </c>
+      <c r="AP123" s="23">
+        <v>43843213</v>
+      </c>
+      <c r="AQ123" s="26"/>
+      <c r="AR123" s="26"/>
+      <c r="AS123" s="26"/>
+      <c r="AT123" s="26"/>
+      <c r="AU123" s="27">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="124" spans="1:47" ht="39" thickBot="1">
+      <c r="A124" s="6">
+        <v>46276.366111111114</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D124" s="8">
+        <v>36997208</v>
+      </c>
+      <c r="E124" s="9">
+        <v>33818</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H124" s="8">
+        <v>3382480860</v>
+      </c>
+      <c r="I124" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J124" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K124" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="L124" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M124" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="N124" s="7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="O124" s="10">
+        <v>44531</v>
+      </c>
+      <c r="P124" s="8">
+        <v>40</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>40</v>
+      </c>
+      <c r="R124" s="8">
+        <v>42</v>
+      </c>
+      <c r="S124" s="8">
+        <v>39</v>
+      </c>
+      <c r="T124" s="7" t="s">
+        <v>1277</v>
+      </c>
+      <c r="U124" s="11"/>
+      <c r="V124" s="11"/>
+      <c r="W124" s="7" t="s">
+        <v>1278</v>
+      </c>
+      <c r="X124" s="10">
+        <v>44663</v>
+      </c>
+      <c r="Y124" s="8">
+        <v>59305444</v>
+      </c>
+      <c r="Z124" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA124" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB124" s="11"/>
+      <c r="AC124" s="11"/>
+      <c r="AD124" s="11"/>
+      <c r="AE124" s="11"/>
+      <c r="AF124" s="11"/>
+      <c r="AG124" s="11"/>
+      <c r="AH124" s="11"/>
+      <c r="AI124" s="11"/>
+      <c r="AJ124" s="11"/>
+      <c r="AK124" s="11"/>
+      <c r="AL124" s="11"/>
+      <c r="AM124" s="11"/>
+      <c r="AN124" s="11"/>
+      <c r="AO124" s="7" t="s">
+        <v>1279</v>
+      </c>
+      <c r="AP124" s="8">
+        <v>59305444</v>
+      </c>
+      <c r="AQ124" s="11"/>
+      <c r="AR124" s="11"/>
+      <c r="AS124" s="11"/>
+      <c r="AT124" s="11"/>
+      <c r="AU124" s="28">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="125" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A125" s="21">
+        <v>46276.367407407408</v>
+      </c>
+      <c r="B125" s="22" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C125" s="22" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D125" s="23">
+        <v>23255061</v>
+      </c>
+      <c r="E125" s="24">
+        <v>26734</v>
+      </c>
+      <c r="F125" s="22" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G125" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H125" s="23">
+        <v>3382680837</v>
+      </c>
+      <c r="I125" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J125" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K125" s="22" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L125" s="22" t="s">
+        <v>1172</v>
+      </c>
+      <c r="M125" s="22" t="s">
+        <v>1173</v>
+      </c>
+      <c r="N125" s="22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="O125" s="25">
+        <v>33394</v>
+      </c>
+      <c r="P125" s="22" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q125" s="22" t="s">
+        <v>636</v>
+      </c>
+      <c r="R125" s="23">
+        <v>50</v>
+      </c>
+      <c r="S125" s="23">
+        <v>43</v>
+      </c>
+      <c r="T125" s="22" t="s">
+        <v>1280</v>
+      </c>
+      <c r="U125" s="25">
+        <v>28636</v>
+      </c>
+      <c r="V125" s="23">
+        <v>27538852</v>
+      </c>
+      <c r="W125" s="22" t="s">
+        <v>1281</v>
+      </c>
+      <c r="X125" s="25">
+        <v>36941</v>
+      </c>
+      <c r="Y125" s="23">
+        <v>42532575</v>
+      </c>
+      <c r="Z125" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA125" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB125" s="22" t="s">
+        <v>1282</v>
+      </c>
+      <c r="AC125" s="22" t="s">
+        <v>1283</v>
+      </c>
+      <c r="AD125" s="25">
+        <v>37694</v>
+      </c>
+      <c r="AE125" s="23">
+        <v>44654923</v>
+      </c>
+      <c r="AF125" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG125" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH125" s="26"/>
+      <c r="AI125" s="26"/>
+      <c r="AJ125" s="26"/>
+      <c r="AK125" s="26"/>
+      <c r="AL125" s="26"/>
+      <c r="AM125" s="26"/>
+      <c r="AN125" s="26"/>
+      <c r="AO125" s="22" t="s">
+        <v>1280</v>
+      </c>
+      <c r="AP125" s="23">
+        <v>27538852</v>
+      </c>
+      <c r="AQ125" s="22" t="s">
+        <v>1284</v>
+      </c>
+      <c r="AR125" s="23">
+        <v>42532575</v>
+      </c>
+      <c r="AS125" s="22" t="s">
+        <v>1285</v>
+      </c>
+      <c r="AT125" s="23">
+        <v>44654923</v>
+      </c>
+      <c r="AU125" s="27">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="126" spans="1:47" ht="39" thickBot="1">
+      <c r="A126" s="6">
+        <v>46276.367569444446</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D126" s="8">
+        <v>25292844</v>
+      </c>
+      <c r="E126" s="9">
+        <v>27900</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H126" s="8">
+        <v>3382458227</v>
+      </c>
+      <c r="I126" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J126" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="L126" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M126" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="N126" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="O126" s="10">
+        <v>35054</v>
+      </c>
+      <c r="P126" s="8">
+        <v>44</v>
+      </c>
+      <c r="Q126" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="R126" s="8">
+        <v>44</v>
+      </c>
+      <c r="S126" s="8">
+        <v>39</v>
+      </c>
+      <c r="T126" s="11"/>
+      <c r="U126" s="11"/>
+      <c r="V126" s="11"/>
+      <c r="W126" s="11"/>
+      <c r="X126" s="11"/>
+      <c r="Y126" s="11"/>
+      <c r="Z126" s="11"/>
+      <c r="AA126" s="11"/>
+      <c r="AB126" s="11"/>
+      <c r="AC126" s="11"/>
+      <c r="AD126" s="11"/>
+      <c r="AE126" s="11"/>
+      <c r="AF126" s="11"/>
+      <c r="AG126" s="11"/>
+      <c r="AH126" s="11"/>
+      <c r="AI126" s="11"/>
+      <c r="AJ126" s="11"/>
+      <c r="AK126" s="11"/>
+      <c r="AL126" s="11"/>
+      <c r="AM126" s="11"/>
+      <c r="AN126" s="11"/>
+      <c r="AO126" s="7" t="s">
+        <v>1277</v>
+      </c>
+      <c r="AP126" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="AQ126" s="11"/>
+      <c r="AR126" s="11"/>
+      <c r="AS126" s="11"/>
+      <c r="AT126" s="11"/>
+      <c r="AU126" s="28">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="127" spans="1:47" ht="39" thickBot="1">
+      <c r="A127" s="21">
+        <v>46276.368761574071</v>
+      </c>
+      <c r="B127" s="22" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C127" s="22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D127" s="23">
+        <v>2842027</v>
+      </c>
+      <c r="E127" s="24">
+        <v>29404</v>
+      </c>
+      <c r="F127" s="22" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G127" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H127" s="23">
+        <v>3382446771</v>
+      </c>
+      <c r="I127" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J127" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K127" s="22" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L127" s="22" t="s">
+        <v>1185</v>
+      </c>
+      <c r="M127" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="N127" s="22" t="s">
+        <v>1186</v>
+      </c>
+      <c r="O127" s="25">
+        <v>36164</v>
+      </c>
+      <c r="P127" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q127" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R127" s="23">
+        <v>46</v>
+      </c>
+      <c r="S127" s="23">
+        <v>42</v>
+      </c>
+      <c r="T127" s="26"/>
+      <c r="U127" s="25">
+        <v>46276</v>
+      </c>
+      <c r="V127" s="26"/>
+      <c r="W127" s="22" t="s">
+        <v>1287</v>
+      </c>
+      <c r="X127" s="25">
+        <v>38674</v>
+      </c>
+      <c r="Y127" s="23">
+        <v>46654520</v>
+      </c>
+      <c r="Z127" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA127" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB127" s="26"/>
+      <c r="AC127" s="26"/>
+      <c r="AD127" s="26"/>
+      <c r="AE127" s="26"/>
+      <c r="AF127" s="26"/>
+      <c r="AG127" s="26"/>
+      <c r="AH127" s="26"/>
+      <c r="AI127" s="26"/>
+      <c r="AJ127" s="26"/>
+      <c r="AK127" s="26"/>
+      <c r="AL127" s="26"/>
+      <c r="AM127" s="26"/>
+      <c r="AN127" s="26"/>
+      <c r="AO127" s="22" t="s">
+        <v>1288</v>
+      </c>
+      <c r="AP127" s="23">
+        <v>46654520</v>
+      </c>
+      <c r="AQ127" s="26"/>
+      <c r="AR127" s="26"/>
+      <c r="AS127" s="26"/>
+      <c r="AT127" s="26"/>
+      <c r="AU127" s="27">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="128" spans="1:47" ht="39" thickBot="1">
+      <c r="A128" s="6">
+        <v>46276.371782407405</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D128" s="8">
+        <v>35647684</v>
+      </c>
+      <c r="E128" s="9">
+        <v>33368</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H128" s="8">
+        <v>3382407716</v>
+      </c>
+      <c r="I128" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J128" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K128" s="11"/>
+      <c r="L128" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M128" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="N128" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="O128" s="10">
+        <v>40695</v>
+      </c>
+      <c r="P128" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q128" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="R128" s="8">
+        <v>42</v>
+      </c>
+      <c r="S128" s="8">
+        <v>40</v>
+      </c>
+      <c r="T128" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="U128" s="10">
+        <v>34244</v>
+      </c>
+      <c r="V128" s="8">
+        <v>37295637</v>
+      </c>
+      <c r="W128" s="7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="X128" s="10">
+        <v>45055</v>
+      </c>
+      <c r="Y128" s="8">
+        <v>59814049</v>
+      </c>
+      <c r="Z128" s="11"/>
+      <c r="AA128" s="11"/>
+      <c r="AB128" s="11"/>
+      <c r="AC128" s="11"/>
+      <c r="AD128" s="11"/>
+      <c r="AE128" s="11"/>
+      <c r="AF128" s="11"/>
+      <c r="AG128" s="11"/>
+      <c r="AH128" s="11"/>
+      <c r="AI128" s="11"/>
+      <c r="AJ128" s="11"/>
+      <c r="AK128" s="11"/>
+      <c r="AL128" s="11"/>
+      <c r="AM128" s="11"/>
+      <c r="AN128" s="11"/>
+      <c r="AO128" s="7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="AP128" s="8">
+        <v>59814049</v>
+      </c>
+      <c r="AQ128" s="7" t="s">
+        <v>1292</v>
+      </c>
+      <c r="AR128" s="8">
+        <v>37295637</v>
+      </c>
+      <c r="AS128" s="11"/>
+      <c r="AT128" s="11"/>
+      <c r="AU128" s="28">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="129" spans="1:47" ht="39" thickBot="1">
+      <c r="A129" s="21">
+        <v>46276.372164351851</v>
+      </c>
+      <c r="B129" s="22" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C129" s="22" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D129" s="23">
+        <v>26318952</v>
+      </c>
+      <c r="E129" s="24">
+        <v>28557</v>
+      </c>
+      <c r="F129" s="22" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G129" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H129" s="23">
+        <v>3382572470</v>
+      </c>
+      <c r="I129" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J129" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K129" s="22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L129" s="22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="M129" s="22" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N129" s="22" t="s">
+        <v>1197</v>
+      </c>
+      <c r="O129" s="25">
+        <v>36557</v>
+      </c>
+      <c r="P129" s="23">
+        <v>44</v>
+      </c>
+      <c r="Q129" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R129" s="23">
+        <v>44</v>
+      </c>
+      <c r="S129" s="23">
+        <v>35</v>
+      </c>
+      <c r="T129" s="22" t="s">
+        <v>1293</v>
+      </c>
+      <c r="U129" s="25">
+        <v>28847</v>
+      </c>
+      <c r="V129" s="23">
+        <v>26989541</v>
+      </c>
+      <c r="W129" s="22" t="s">
+        <v>1294</v>
+      </c>
+      <c r="X129" s="25">
+        <v>42352</v>
+      </c>
+      <c r="Y129" s="23">
+        <v>55214125</v>
+      </c>
+      <c r="Z129" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA129" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB129" s="22" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AC129" s="22" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AD129" s="25">
+        <v>44176</v>
+      </c>
+      <c r="AE129" s="23">
+        <v>58328374</v>
+      </c>
+      <c r="AF129" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG129" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH129" s="22" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AI129" s="26"/>
+      <c r="AJ129" s="26"/>
+      <c r="AK129" s="26"/>
+      <c r="AL129" s="26"/>
+      <c r="AM129" s="26"/>
+      <c r="AN129" s="26"/>
+      <c r="AO129" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AP129" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AQ129" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AR129" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AS129" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AT129" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AU129" s="27">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="130" spans="1:47" ht="102.75" thickBot="1">
+      <c r="A130" s="6">
+        <v>46276.372754629629</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D130" s="8">
+        <v>35919880</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H130" s="8">
+        <v>3382679273</v>
+      </c>
+      <c r="I130" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J130" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K130" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L130" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M130" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="N130" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="O130" s="10">
+        <v>41548</v>
+      </c>
+      <c r="P130" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q130" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="R130" s="8">
+        <v>40</v>
+      </c>
+      <c r="S130" s="8">
+        <v>38</v>
+      </c>
+      <c r="T130" s="7" t="s">
+        <v>1298</v>
+      </c>
+      <c r="U130" s="10">
+        <v>32957</v>
+      </c>
+      <c r="V130" s="8">
+        <v>32712834</v>
+      </c>
+      <c r="W130" s="7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="X130" s="10">
+        <v>43097</v>
+      </c>
+      <c r="Y130" s="8">
+        <v>56624119</v>
+      </c>
+      <c r="Z130" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA130" s="11"/>
+      <c r="AB130" s="11"/>
+      <c r="AC130" s="11"/>
+      <c r="AD130" s="11"/>
+      <c r="AE130" s="11"/>
+      <c r="AF130" s="11"/>
+      <c r="AG130" s="11"/>
+      <c r="AH130" s="11"/>
+      <c r="AI130" s="11"/>
+      <c r="AJ130" s="11"/>
+      <c r="AK130" s="11"/>
+      <c r="AL130" s="11"/>
+      <c r="AM130" s="11"/>
+      <c r="AN130" s="11"/>
+      <c r="AO130" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="AP130" s="8">
+        <v>35919880</v>
+      </c>
+      <c r="AQ130" s="7" t="s">
+        <v>1298</v>
+      </c>
+      <c r="AR130" s="8">
+        <v>32712834</v>
+      </c>
+      <c r="AS130" s="7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="AT130" s="8">
+        <v>56624119</v>
+      </c>
+      <c r="AU130" s="28">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131" spans="1:47" ht="39" thickBot="1">
+      <c r="A131" s="21">
+        <v>46276.374525462961</v>
+      </c>
+      <c r="B131" s="22" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C131" s="22" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D131" s="23">
+        <v>37902869</v>
+      </c>
+      <c r="E131" s="22" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F131" s="22" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G131" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H131" s="23">
+        <v>3382441425</v>
+      </c>
+      <c r="I131" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J131" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K131" s="26"/>
+      <c r="L131" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M131" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="N131" s="22" t="s">
+        <v>1208</v>
+      </c>
+      <c r="O131" s="25">
+        <v>43282</v>
+      </c>
+      <c r="P131" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q131" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="R131" s="23">
+        <v>48</v>
+      </c>
+      <c r="S131" s="23">
+        <v>43</v>
+      </c>
+      <c r="T131" s="22" t="s">
+        <v>1300</v>
+      </c>
+      <c r="U131" s="25">
+        <v>35742</v>
+      </c>
+      <c r="V131" s="23">
+        <v>40277700</v>
+      </c>
+      <c r="W131" s="22" t="s">
+        <v>1301</v>
+      </c>
+      <c r="X131" s="25">
+        <v>44640</v>
+      </c>
+      <c r="Y131" s="23">
+        <v>59286114</v>
+      </c>
+      <c r="Z131" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA131" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB131" s="26"/>
+      <c r="AC131" s="22" t="s">
+        <v>1302</v>
+      </c>
+      <c r="AD131" s="25">
+        <v>45743</v>
+      </c>
+      <c r="AE131" s="23">
+        <v>70507079</v>
+      </c>
+      <c r="AF131" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG131" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH131" s="26"/>
+      <c r="AI131" s="26"/>
+      <c r="AJ131" s="26"/>
+      <c r="AK131" s="26"/>
+      <c r="AL131" s="26"/>
+      <c r="AM131" s="26"/>
+      <c r="AN131" s="26"/>
+      <c r="AO131" s="22" t="s">
+        <v>1300</v>
+      </c>
+      <c r="AP131" s="23">
+        <v>40277700</v>
+      </c>
+      <c r="AQ131" s="22" t="s">
+        <v>1303</v>
+      </c>
+      <c r="AR131" s="23">
+        <v>59286114</v>
+      </c>
+      <c r="AS131" s="22" t="s">
+        <v>1304</v>
+      </c>
+      <c r="AT131" s="23">
+        <v>70507079</v>
+      </c>
+      <c r="AU131" s="27">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="132" spans="1:47" ht="39" thickBot="1">
+      <c r="A132" s="6">
+        <v>46276.376273148147</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D132" s="8">
+        <v>34408735</v>
+      </c>
+      <c r="E132" s="9">
+        <v>33000</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="H132" s="8">
+        <v>3382408160</v>
+      </c>
+      <c r="I132" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J132" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K132" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="L132" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="M132" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="N132" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="O132" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P132" s="8">
+        <v>40</v>
+      </c>
+      <c r="Q132" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="R132" s="8">
+        <v>42</v>
+      </c>
+      <c r="S132" s="7" t="s">
+        <v>1214</v>
+      </c>
+      <c r="T132" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="U132" s="10">
+        <v>33210</v>
+      </c>
+      <c r="V132" s="8">
+        <v>35295090</v>
+      </c>
+      <c r="W132" s="7" t="s">
+        <v>1306</v>
+      </c>
+      <c r="X132" s="10">
+        <v>44104</v>
+      </c>
+      <c r="Y132" s="11"/>
+      <c r="Z132" s="11"/>
+      <c r="AA132" s="11"/>
+      <c r="AB132" s="11"/>
+      <c r="AC132" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="AD132" s="10">
+        <v>44174</v>
+      </c>
+      <c r="AE132" s="11"/>
+      <c r="AF132" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG132" s="11"/>
+      <c r="AH132" s="11"/>
+      <c r="AI132" s="11"/>
+      <c r="AJ132" s="11"/>
+      <c r="AK132" s="11"/>
+      <c r="AL132" s="11"/>
+      <c r="AM132" s="11"/>
+      <c r="AN132" s="11"/>
+      <c r="AO132" s="7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="AP132" s="8">
+        <v>34408735</v>
+      </c>
+      <c r="AQ132" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="AR132" s="8">
+        <v>35295090</v>
+      </c>
+      <c r="AS132" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="AT132" s="8">
+        <v>58298306</v>
+      </c>
+      <c r="AU132" s="28">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="133" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A133" s="21">
+        <v>46276.380497685182</v>
+      </c>
+      <c r="B133" s="22" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C133" s="22" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D133" s="23">
+        <v>34408566</v>
+      </c>
+      <c r="E133" s="24">
+        <v>32771</v>
+      </c>
+      <c r="F133" s="22" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G133" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H133" s="23">
+        <v>3382415272</v>
+      </c>
+      <c r="I133" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J133" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K133" s="26"/>
+      <c r="L133" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M133" s="22" t="s">
+        <v>1218</v>
+      </c>
+      <c r="N133" s="22" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O133" s="25">
+        <v>46282</v>
+      </c>
+      <c r="P133" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q133" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="R133" s="23">
+        <v>41</v>
+      </c>
+      <c r="S133" s="23">
+        <v>42</v>
+      </c>
+      <c r="T133" s="22" t="s">
+        <v>1308</v>
+      </c>
+      <c r="U133" s="25">
+        <v>34881</v>
+      </c>
+      <c r="V133" s="23">
+        <v>37903081</v>
+      </c>
+      <c r="W133" s="22" t="s">
+        <v>1309</v>
+      </c>
+      <c r="X133" s="25">
+        <v>41459</v>
+      </c>
+      <c r="Y133" s="23">
+        <v>54269533</v>
+      </c>
+      <c r="Z133" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA133" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB133" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="AC133" s="22" t="s">
+        <v>1310</v>
+      </c>
+      <c r="AD133" s="25">
+        <v>42122</v>
+      </c>
+      <c r="AE133" s="23">
+        <v>54615984</v>
+      </c>
+      <c r="AF133" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG133" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH133" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="AI133" s="26"/>
+      <c r="AJ133" s="26"/>
+      <c r="AK133" s="26"/>
+      <c r="AL133" s="26"/>
+      <c r="AM133" s="26"/>
+      <c r="AN133" s="26"/>
+      <c r="AO133" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="AP133" s="23">
+        <v>37903081</v>
+      </c>
+      <c r="AQ133" s="26"/>
+      <c r="AR133" s="26"/>
+      <c r="AS133" s="26"/>
+      <c r="AT133" s="26"/>
+      <c r="AU133" s="27">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="134" spans="1:47" ht="39" thickBot="1">
+      <c r="A134" s="6">
+        <v>46276.399097222224</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D134" s="8">
+        <v>17622365</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H134" s="8">
+        <v>3382408029</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K134" s="11"/>
+      <c r="L134" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M134" s="7" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N134" s="7" t="s">
+        <v>1225</v>
+      </c>
+      <c r="O134" s="10">
+        <v>35445</v>
+      </c>
+      <c r="P134" s="8">
+        <v>44</v>
+      </c>
+      <c r="Q134" s="8">
+        <v>44</v>
+      </c>
+      <c r="R134" s="8">
+        <v>46</v>
+      </c>
+      <c r="S134" s="8">
+        <v>43</v>
+      </c>
+      <c r="T134" s="11"/>
+      <c r="U134" s="11"/>
+      <c r="V134" s="11"/>
+      <c r="W134" s="11"/>
+      <c r="X134" s="11"/>
+      <c r="Y134" s="11"/>
+      <c r="Z134" s="11"/>
+      <c r="AA134" s="11"/>
+      <c r="AB134" s="11"/>
+      <c r="AC134" s="11"/>
+      <c r="AD134" s="11"/>
+      <c r="AE134" s="11"/>
+      <c r="AF134" s="11"/>
+      <c r="AG134" s="11"/>
+      <c r="AH134" s="11"/>
+      <c r="AI134" s="11"/>
+      <c r="AJ134" s="11"/>
+      <c r="AK134" s="11"/>
+      <c r="AL134" s="11"/>
+      <c r="AM134" s="11"/>
+      <c r="AN134" s="11"/>
+      <c r="AO134" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AP134" s="8">
+        <v>17622365</v>
+      </c>
+      <c r="AQ134" s="11"/>
+      <c r="AR134" s="11"/>
+      <c r="AS134" s="11"/>
+      <c r="AT134" s="11"/>
+      <c r="AU134" s="28">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="135" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A135" s="21">
+        <v>46276.421956018516</v>
+      </c>
+      <c r="B135" s="22" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C135" s="22" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D135" s="23">
+        <v>25773953</v>
+      </c>
+      <c r="E135" s="24">
+        <v>28257</v>
+      </c>
+      <c r="F135" s="22" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G135" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H135" s="23">
+        <v>3382449232</v>
+      </c>
+      <c r="I135" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J135" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K135" s="22" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L135" s="22" t="s">
+        <v>1230</v>
+      </c>
+      <c r="M135" s="22" t="s">
+        <v>1231</v>
+      </c>
+      <c r="N135" s="22" t="s">
+        <v>1232</v>
+      </c>
+      <c r="O135" s="25">
+        <v>43282</v>
+      </c>
+      <c r="P135" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q135" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="R135" s="23">
+        <v>40</v>
+      </c>
+      <c r="S135" s="23">
+        <v>37</v>
+      </c>
+      <c r="T135" s="22" t="s">
+        <v>1312</v>
+      </c>
+      <c r="U135" s="25">
+        <v>28257</v>
+      </c>
+      <c r="V135" s="23">
+        <v>25773953</v>
+      </c>
+      <c r="W135" s="26"/>
+      <c r="X135" s="26"/>
+      <c r="Y135" s="22" t="s">
+        <v>1313</v>
+      </c>
+      <c r="Z135" s="26"/>
+      <c r="AA135" s="26"/>
+      <c r="AB135" s="26"/>
+      <c r="AC135" s="26"/>
+      <c r="AD135" s="26"/>
+      <c r="AE135" s="26"/>
+      <c r="AF135" s="26"/>
+      <c r="AG135" s="26"/>
+      <c r="AH135" s="26"/>
+      <c r="AI135" s="26"/>
+      <c r="AJ135" s="26"/>
+      <c r="AK135" s="26"/>
+      <c r="AL135" s="26"/>
+      <c r="AM135" s="26"/>
+      <c r="AN135" s="26"/>
+      <c r="AO135" s="22" t="s">
+        <v>1313</v>
+      </c>
+      <c r="AP135" s="22" t="s">
+        <v>1313</v>
+      </c>
+      <c r="AQ135" s="26"/>
+      <c r="AR135" s="26"/>
+      <c r="AS135" s="26"/>
+      <c r="AT135" s="26"/>
+      <c r="AU135" s="27">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="136" spans="1:47" ht="39" thickBot="1">
+      <c r="A136" s="6">
+        <v>46276.430127314816</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D136" s="8">
+        <v>30662615</v>
+      </c>
+      <c r="E136" s="9">
+        <v>30924</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="H136" s="8">
+        <v>3382504582</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J136" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K136" s="11"/>
+      <c r="L136" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="M136" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="N136" s="7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="O136" s="10">
+        <v>44531</v>
+      </c>
+      <c r="P136" s="8">
+        <v>48</v>
+      </c>
+      <c r="Q136" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="R136" s="8">
+        <v>50</v>
+      </c>
+      <c r="S136" s="8">
+        <v>43</v>
+      </c>
+      <c r="T136" s="7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="U136" s="10">
+        <v>31192</v>
+      </c>
+      <c r="V136" s="8">
+        <v>31592042</v>
+      </c>
+      <c r="W136" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="X136" s="10">
+        <v>43532</v>
+      </c>
+      <c r="Y136" s="8">
+        <v>57208953</v>
+      </c>
+      <c r="Z136" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA136" s="11"/>
+      <c r="AB136" s="11"/>
+      <c r="AC136" s="7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="AD136" s="10">
+        <v>41721</v>
+      </c>
+      <c r="AE136" s="8">
+        <v>53919428</v>
+      </c>
+      <c r="AF136" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG136" s="11"/>
+      <c r="AH136" s="11"/>
+      <c r="AI136" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AJ136" s="10">
+        <v>38284</v>
+      </c>
+      <c r="AK136" s="8">
+        <v>45987238</v>
+      </c>
+      <c r="AL136" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM136" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN136" s="11"/>
+      <c r="AO136" s="7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="AP136" s="8">
+        <v>31592042</v>
+      </c>
+      <c r="AQ136" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AR136" s="8">
+        <v>45987238</v>
+      </c>
+      <c r="AS136" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="AT136" s="8">
+        <v>57208953</v>
+      </c>
+      <c r="AU136" s="28">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="137" spans="1:47" ht="39" thickBot="1">
+      <c r="A137" s="21">
+        <v>46276.436145833337</v>
+      </c>
+      <c r="B137" s="22" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C137" s="22" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D137" s="23">
+        <v>26870688</v>
+      </c>
+      <c r="E137" s="24">
+        <v>28811</v>
+      </c>
+      <c r="F137" s="22" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G137" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H137" s="23">
+        <v>3382571689</v>
+      </c>
+      <c r="I137" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J137" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K137" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="L137" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M137" s="22" t="s">
+        <v>834</v>
+      </c>
+      <c r="N137" s="22" t="s">
+        <v>1240</v>
+      </c>
+      <c r="O137" s="25">
+        <v>39326</v>
+      </c>
+      <c r="P137" s="23">
+        <v>46</v>
+      </c>
+      <c r="Q137" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="R137" s="23">
+        <v>54</v>
+      </c>
+      <c r="S137" s="23">
+        <v>42</v>
+      </c>
+      <c r="T137" s="22" t="s">
+        <v>1319</v>
+      </c>
+      <c r="U137" s="25">
+        <v>26406</v>
+      </c>
+      <c r="V137" s="23">
+        <v>21767377</v>
+      </c>
+      <c r="W137" s="26"/>
+      <c r="X137" s="26"/>
+      <c r="Y137" s="26"/>
+      <c r="Z137" s="26"/>
+      <c r="AA137" s="26"/>
+      <c r="AB137" s="26"/>
+      <c r="AC137" s="26"/>
+      <c r="AD137" s="26"/>
+      <c r="AE137" s="26"/>
+      <c r="AF137" s="26"/>
+      <c r="AG137" s="26"/>
+      <c r="AH137" s="26"/>
+      <c r="AI137" s="26"/>
+      <c r="AJ137" s="26"/>
+      <c r="AK137" s="26"/>
+      <c r="AL137" s="26"/>
+      <c r="AM137" s="26"/>
+      <c r="AN137" s="26"/>
+      <c r="AO137" s="22" t="s">
+        <v>1319</v>
+      </c>
+      <c r="AP137" s="23">
+        <v>21767377</v>
+      </c>
+      <c r="AQ137" s="26"/>
+      <c r="AR137" s="26"/>
+      <c r="AS137" s="26"/>
+      <c r="AT137" s="26"/>
+      <c r="AU137" s="27">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="138" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A138" s="53">
+        <v>46276.457696759258</v>
+      </c>
+      <c r="B138" s="54" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C138" s="54" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D138" s="55">
+        <v>40277764</v>
+      </c>
+      <c r="E138" s="56">
+        <v>35823</v>
+      </c>
+      <c r="F138" s="54" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G138" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="H138" s="55">
+        <v>3382462643</v>
+      </c>
+      <c r="I138" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="J138" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="K138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="L138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="M138" s="54" t="s">
+        <v>834</v>
+      </c>
+      <c r="N138" s="54" t="s">
+        <v>1244</v>
+      </c>
+      <c r="O138" s="57">
+        <v>44531</v>
+      </c>
+      <c r="P138" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q138" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="R138" s="55">
+        <v>40</v>
+      </c>
+      <c r="S138" s="55">
+        <v>41</v>
+      </c>
+      <c r="T138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="U138" s="58"/>
+      <c r="V138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="W138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="X138" s="58"/>
+      <c r="Y138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="Z138" s="58"/>
+      <c r="AA138" s="58"/>
+      <c r="AB138" s="58"/>
+      <c r="AC138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AD138" s="58"/>
+      <c r="AE138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AF138" s="58"/>
+      <c r="AG138" s="58"/>
+      <c r="AH138" s="58"/>
+      <c r="AI138" s="58"/>
+      <c r="AJ138" s="58"/>
+      <c r="AK138" s="58"/>
+      <c r="AL138" s="58"/>
+      <c r="AM138" s="58"/>
+      <c r="AN138" s="58"/>
+      <c r="AO138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AP138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AQ138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AR138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AS138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AT138" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="AU138" s="59">
+        <v>527</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
